--- a/docs/pleth data log.xlsx
+++ b/docs/pleth data log.xlsx
@@ -5036,7 +5036,7 @@
       <c r="AI63" s="11"/>
       <c r="AJ63" s="11"/>
     </row>
-    <row r="64">
+    <row r="64" hidden="1">
       <c r="A64" s="7" t="s">
         <v>108</v>
       </c>
@@ -5094,7 +5094,7 @@
       <c r="AI64" s="11"/>
       <c r="AJ64" s="11"/>
     </row>
-    <row r="65">
+    <row r="65" hidden="1">
       <c r="A65" s="9" t="s">
         <v>111</v>
       </c>
@@ -5154,7 +5154,7 @@
       <c r="AI65" s="14"/>
       <c r="AJ65" s="14"/>
     </row>
-    <row r="66">
+    <row r="66" hidden="1">
       <c r="A66" s="9" t="s">
         <v>112</v>
       </c>
@@ -5216,7 +5216,7 @@
       <c r="AI66" s="14"/>
       <c r="AJ66" s="14"/>
     </row>
-    <row r="67">
+    <row r="67" hidden="1">
       <c r="A67" s="9" t="s">
         <v>114</v>
       </c>
@@ -5276,7 +5276,7 @@
       <c r="AI67" s="14"/>
       <c r="AJ67" s="14"/>
     </row>
-    <row r="68">
+    <row r="68" hidden="1">
       <c r="A68" s="7" t="s">
         <v>115</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="AI68" s="11"/>
       <c r="AJ68" s="11"/>
     </row>
-    <row r="69">
+    <row r="69" hidden="1">
       <c r="A69" s="9" t="s">
         <v>117</v>
       </c>
@@ -5398,7 +5398,7 @@
       <c r="AI69" s="14"/>
       <c r="AJ69" s="14"/>
     </row>
-    <row r="70">
+    <row r="70" hidden="1">
       <c r="A70" s="9" t="s">
         <v>119</v>
       </c>
@@ -5460,7 +5460,7 @@
       <c r="AI70" s="14"/>
       <c r="AJ70" s="14"/>
     </row>
-    <row r="71">
+    <row r="71" hidden="1">
       <c r="A71" s="9" t="s">
         <v>121</v>
       </c>
@@ -5522,7 +5522,7 @@
       <c r="AI71" s="14"/>
       <c r="AJ71" s="14"/>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" s="7" t="s">
         <v>122</v>
       </c>
@@ -5580,7 +5580,7 @@
       <c r="AI72" s="11"/>
       <c r="AJ72" s="11"/>
     </row>
-    <row r="73">
+    <row r="73" hidden="1">
       <c r="A73" s="9" t="s">
         <v>123</v>
       </c>
@@ -5642,7 +5642,7 @@
       <c r="AI73" s="14"/>
       <c r="AJ73" s="14"/>
     </row>
-    <row r="74">
+    <row r="74" hidden="1">
       <c r="A74" s="9" t="s">
         <v>124</v>
       </c>
@@ -5704,7 +5704,7 @@
       <c r="AI74" s="14"/>
       <c r="AJ74" s="14"/>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75" s="7" t="s">
         <v>125</v>
       </c>
@@ -5762,7 +5762,7 @@
       <c r="AI75" s="11"/>
       <c r="AJ75" s="11"/>
     </row>
-    <row r="76">
+    <row r="76" hidden="1">
       <c r="A76" s="9" t="s">
         <v>126</v>
       </c>
@@ -5822,7 +5822,7 @@
       <c r="AI76" s="14"/>
       <c r="AJ76" s="14"/>
     </row>
-    <row r="77">
+    <row r="77" hidden="1">
       <c r="A77" s="9" t="s">
         <v>127</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="AI77" s="14"/>
       <c r="AJ77" s="14"/>
     </row>
-    <row r="78">
+    <row r="78" hidden="1">
       <c r="A78" s="9" t="s">
         <v>128</v>
       </c>
@@ -5942,7 +5942,7 @@
       <c r="AI78" s="14"/>
       <c r="AJ78" s="14"/>
     </row>
-    <row r="79">
+    <row r="79" hidden="1">
       <c r="A79" s="7" t="s">
         <v>129</v>
       </c>
@@ -6000,7 +6000,7 @@
       <c r="AI79" s="11"/>
       <c r="AJ79" s="11"/>
     </row>
-    <row r="80">
+    <row r="80" hidden="1">
       <c r="A80" s="9" t="s">
         <v>130</v>
       </c>
@@ -6060,7 +6060,7 @@
       <c r="AI80" s="14"/>
       <c r="AJ80" s="14"/>
     </row>
-    <row r="81">
+    <row r="81" hidden="1">
       <c r="A81" s="9" t="s">
         <v>131</v>
       </c>
@@ -6120,7 +6120,7 @@
       <c r="AI81" s="14"/>
       <c r="AJ81" s="14"/>
     </row>
-    <row r="82">
+    <row r="82" hidden="1">
       <c r="A82" s="9" t="s">
         <v>132</v>
       </c>
@@ -6180,7 +6180,7 @@
       <c r="AI82" s="14"/>
       <c r="AJ82" s="14"/>
     </row>
-    <row r="83">
+    <row r="83" hidden="1">
       <c r="A83" s="7" t="s">
         <v>133</v>
       </c>
@@ -6238,7 +6238,7 @@
       <c r="AI83" s="11"/>
       <c r="AJ83" s="11"/>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84" s="9" t="s">
         <v>134</v>
       </c>
@@ -6298,7 +6298,7 @@
       <c r="AI84" s="14"/>
       <c r="AJ84" s="14"/>
     </row>
-    <row r="85">
+    <row r="85" hidden="1">
       <c r="A85" s="9" t="s">
         <v>135</v>
       </c>
@@ -6358,7 +6358,7 @@
       <c r="AI85" s="14"/>
       <c r="AJ85" s="14"/>
     </row>
-    <row r="86">
+    <row r="86" hidden="1">
       <c r="A86" s="7" t="s">
         <v>136</v>
       </c>
@@ -6416,7 +6416,7 @@
       <c r="AI86" s="11"/>
       <c r="AJ86" s="11"/>
     </row>
-    <row r="87">
+    <row r="87" hidden="1">
       <c r="A87" s="9" t="s">
         <v>137</v>
       </c>
@@ -6476,7 +6476,7 @@
       <c r="AI87" s="14"/>
       <c r="AJ87" s="14"/>
     </row>
-    <row r="88">
+    <row r="88" hidden="1">
       <c r="A88" s="9" t="s">
         <v>138</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="AI88" s="14"/>
       <c r="AJ88" s="14"/>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89" s="9" t="s">
         <v>139</v>
       </c>
@@ -6598,7 +6598,7 @@
       <c r="AI89" s="14"/>
       <c r="AJ89" s="14"/>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90" s="7" t="s">
         <v>140</v>
       </c>
@@ -6656,7 +6656,7 @@
       <c r="AI90" s="11"/>
       <c r="AJ90" s="11"/>
     </row>
-    <row r="91">
+    <row r="91" hidden="1">
       <c r="A91" s="9" t="s">
         <v>141</v>
       </c>
@@ -6716,7 +6716,7 @@
       <c r="AI91" s="14"/>
       <c r="AJ91" s="14"/>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92" s="9" t="s">
         <v>142</v>
       </c>
@@ -6776,7 +6776,7 @@
       <c r="AI92" s="14"/>
       <c r="AJ92" s="14"/>
     </row>
-    <row r="93">
+    <row r="93" hidden="1">
       <c r="A93" s="7" t="s">
         <v>143</v>
       </c>
@@ -6834,7 +6834,7 @@
       <c r="AI93" s="11"/>
       <c r="AJ93" s="11"/>
     </row>
-    <row r="94">
+    <row r="94" hidden="1">
       <c r="A94" s="7" t="s">
         <v>144</v>
       </c>
@@ -6892,7 +6892,7 @@
       <c r="AI94" s="11"/>
       <c r="AJ94" s="11"/>
     </row>
-    <row r="95">
+    <row r="95" hidden="1">
       <c r="A95" s="7" t="s">
         <v>145</v>
       </c>
@@ -6950,7 +6950,7 @@
       <c r="AI95" s="11"/>
       <c r="AJ95" s="11"/>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" s="9" t="s">
         <v>146</v>
       </c>
@@ -7010,7 +7010,7 @@
       <c r="AI96" s="14"/>
       <c r="AJ96" s="14"/>
     </row>
-    <row r="97">
+    <row r="97" hidden="1">
       <c r="A97" s="9" t="s">
         <v>147</v>
       </c>
@@ -7072,7 +7072,7 @@
       <c r="AI97" s="14"/>
       <c r="AJ97" s="14"/>
     </row>
-    <row r="98">
+    <row r="98" hidden="1">
       <c r="A98" s="9" t="s">
         <v>148</v>
       </c>
@@ -7132,7 +7132,7 @@
       <c r="AI98" s="14"/>
       <c r="AJ98" s="14"/>
     </row>
-    <row r="99">
+    <row r="99" hidden="1">
       <c r="A99" s="7" t="s">
         <v>150</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="AI99" s="11"/>
       <c r="AJ99" s="11"/>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" s="7" t="s">
         <v>151</v>
       </c>
@@ -7248,7 +7248,7 @@
       <c r="AI100" s="11"/>
       <c r="AJ100" s="11"/>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101" s="9" t="s">
         <v>152</v>
       </c>
@@ -7310,7 +7310,7 @@
       <c r="AI101" s="14"/>
       <c r="AJ101" s="14"/>
     </row>
-    <row r="102">
+    <row r="102" hidden="1">
       <c r="A102" s="9" t="s">
         <v>154</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="AI102" s="14"/>
       <c r="AJ102" s="14"/>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" s="7" t="s">
         <v>155</v>
       </c>
@@ -7428,7 +7428,7 @@
       <c r="AI103" s="11"/>
       <c r="AJ103" s="11"/>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" s="9" t="s">
         <v>156</v>
       </c>
@@ -7490,7 +7490,7 @@
       <c r="AI104" s="14"/>
       <c r="AJ104" s="14"/>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105" s="9" t="s">
         <v>157</v>
       </c>
@@ -7552,7 +7552,7 @@
       <c r="AI105" s="14"/>
       <c r="AJ105" s="14"/>
     </row>
-    <row r="106">
+    <row r="106" hidden="1">
       <c r="A106" s="9" t="s">
         <v>158</v>
       </c>
@@ -7614,7 +7614,7 @@
       <c r="AI106" s="14"/>
       <c r="AJ106" s="14"/>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107" s="19" t="s">
         <v>159</v>
       </c>
@@ -7676,7 +7676,7 @@
       <c r="AI107" s="14"/>
       <c r="AJ107" s="14"/>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" s="19" t="s">
         <v>161</v>
       </c>
@@ -7738,7 +7738,7 @@
       <c r="AI108" s="14"/>
       <c r="AJ108" s="14"/>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" s="19" t="s">
         <v>162</v>
       </c>
@@ -7800,7 +7800,7 @@
       <c r="AI109" s="14"/>
       <c r="AJ109" s="14"/>
     </row>
-    <row r="110">
+    <row r="110" hidden="1">
       <c r="A110" s="9" t="s">
         <v>163</v>
       </c>
@@ -7868,7 +7868,7 @@
       <c r="AI110" s="14"/>
       <c r="AJ110" s="14"/>
     </row>
-    <row r="111">
+    <row r="111" hidden="1">
       <c r="A111" s="9" t="s">
         <v>166</v>
       </c>
@@ -7928,7 +7928,7 @@
       <c r="AI111" s="14"/>
       <c r="AJ111" s="14"/>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112" s="9" t="s">
         <v>167</v>
       </c>
@@ -7990,7 +7990,7 @@
       <c r="AI112" s="14"/>
       <c r="AJ112" s="14"/>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113" s="9" t="s">
         <v>168</v>
       </c>
@@ -8052,7 +8052,7 @@
       <c r="AI113" s="14"/>
       <c r="AJ113" s="14"/>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" s="9" t="s">
         <v>170</v>
       </c>
@@ -8114,7 +8114,7 @@
       <c r="AI114" s="14"/>
       <c r="AJ114" s="14"/>
     </row>
-    <row r="115">
+    <row r="115" hidden="1">
       <c r="A115" s="27" t="s">
         <v>171</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="AI115" s="14"/>
       <c r="AJ115" s="14"/>
     </row>
-    <row r="116">
+    <row r="116" hidden="1">
       <c r="A116" s="28" t="s">
         <v>174</v>
       </c>
@@ -8232,7 +8232,7 @@
       <c r="AI116" s="11"/>
       <c r="AJ116" s="11"/>
     </row>
-    <row r="117">
+    <row r="117" hidden="1">
       <c r="A117" s="28" t="s">
         <v>175</v>
       </c>
@@ -8290,7 +8290,7 @@
       <c r="AI117" s="11"/>
       <c r="AJ117" s="11"/>
     </row>
-    <row r="118">
+    <row r="118" hidden="1">
       <c r="A118" s="28" t="s">
         <v>177</v>
       </c>
@@ -8348,7 +8348,7 @@
       <c r="AI118" s="11"/>
       <c r="AJ118" s="11"/>
     </row>
-    <row r="119">
+    <row r="119" hidden="1">
       <c r="A119" s="28" t="s">
         <v>178</v>
       </c>
@@ -8408,7 +8408,7 @@
       <c r="AI119" s="11"/>
       <c r="AJ119" s="11"/>
     </row>
-    <row r="120">
+    <row r="120" hidden="1">
       <c r="A120" s="27" t="s">
         <v>180</v>
       </c>
@@ -8470,7 +8470,7 @@
       <c r="AI120" s="14"/>
       <c r="AJ120" s="14"/>
     </row>
-    <row r="121">
+    <row r="121" hidden="1">
       <c r="A121" s="28" t="s">
         <v>182</v>
       </c>
@@ -8530,7 +8530,7 @@
       <c r="AI121" s="11"/>
       <c r="AJ121" s="11"/>
     </row>
-    <row r="122">
+    <row r="122" hidden="1">
       <c r="A122" s="28" t="s">
         <v>183</v>
       </c>
@@ -8590,7 +8590,7 @@
       <c r="AI122" s="11"/>
       <c r="AJ122" s="11"/>
     </row>
-    <row r="123">
+    <row r="123" hidden="1">
       <c r="A123" s="28" t="s">
         <v>184</v>
       </c>
@@ -8650,7 +8650,7 @@
       <c r="AI123" s="11"/>
       <c r="AJ123" s="11"/>
     </row>
-    <row r="124">
+    <row r="124" hidden="1">
       <c r="A124" s="28" t="s">
         <v>185</v>
       </c>
@@ -8714,7 +8714,7 @@
       <c r="AI124" s="14"/>
       <c r="AJ124" s="14"/>
     </row>
-    <row r="125">
+    <row r="125" hidden="1">
       <c r="A125" s="28" t="s">
         <v>186</v>
       </c>
@@ -8774,7 +8774,7 @@
       <c r="AI125" s="11"/>
       <c r="AJ125" s="11"/>
     </row>
-    <row r="126">
+    <row r="126" hidden="1">
       <c r="A126" s="28" t="s">
         <v>188</v>
       </c>
@@ -8832,7 +8832,7 @@
       <c r="AI126" s="11"/>
       <c r="AJ126" s="11"/>
     </row>
-    <row r="127">
+    <row r="127" hidden="1">
       <c r="A127" s="28" t="s">
         <v>189</v>
       </c>
@@ -8892,7 +8892,7 @@
       <c r="AI127" s="14"/>
       <c r="AJ127" s="14"/>
     </row>
-    <row r="128">
+    <row r="128" hidden="1">
       <c r="A128" s="28" t="s">
         <v>190</v>
       </c>
@@ -8950,7 +8950,7 @@
       <c r="AI128" s="11"/>
       <c r="AJ128" s="11"/>
     </row>
-    <row r="129">
+    <row r="129" hidden="1">
       <c r="A129" s="28" t="s">
         <v>191</v>
       </c>
@@ -9008,7 +9008,7 @@
       <c r="AI129" s="11"/>
       <c r="AJ129" s="11"/>
     </row>
-    <row r="130">
+    <row r="130" hidden="1">
       <c r="A130" s="28" t="s">
         <v>192</v>
       </c>
@@ -9066,7 +9066,7 @@
       <c r="AI130" s="11"/>
       <c r="AJ130" s="11"/>
     </row>
-    <row r="131">
+    <row r="131" hidden="1">
       <c r="A131" s="28" t="s">
         <v>193</v>
       </c>
@@ -9124,7 +9124,7 @@
       <c r="AI131" s="11"/>
       <c r="AJ131" s="11"/>
     </row>
-    <row r="132">
+    <row r="132" hidden="1">
       <c r="A132" s="28" t="s">
         <v>194</v>
       </c>
@@ -9182,7 +9182,7 @@
       <c r="AI132" s="11"/>
       <c r="AJ132" s="11"/>
     </row>
-    <row r="133">
+    <row r="133" hidden="1">
       <c r="A133" s="28" t="s">
         <v>195</v>
       </c>
@@ -9242,7 +9242,7 @@
       <c r="AI133" s="14"/>
       <c r="AJ133" s="14"/>
     </row>
-    <row r="134">
+    <row r="134" hidden="1">
       <c r="A134" s="9" t="s">
         <v>196</v>
       </c>
@@ -9302,7 +9302,7 @@
       <c r="AI134" s="14"/>
       <c r="AJ134" s="14"/>
     </row>
-    <row r="135">
+    <row r="135" hidden="1">
       <c r="A135" s="7" t="s">
         <v>197</v>
       </c>
@@ -9360,7 +9360,7 @@
       <c r="AI135" s="11"/>
       <c r="AJ135" s="11"/>
     </row>
-    <row r="136">
+    <row r="136" hidden="1">
       <c r="A136" s="9" t="s">
         <v>198</v>
       </c>
@@ -9420,7 +9420,7 @@
       <c r="AI136" s="14"/>
       <c r="AJ136" s="14"/>
     </row>
-    <row r="137">
+    <row r="137" hidden="1">
       <c r="A137" s="7" t="s">
         <v>199</v>
       </c>
@@ -9478,7 +9478,7 @@
       <c r="AI137" s="11"/>
       <c r="AJ137" s="11"/>
     </row>
-    <row r="138">
+    <row r="138" hidden="1">
       <c r="A138" s="9" t="s">
         <v>200</v>
       </c>
@@ -9538,7 +9538,7 @@
       <c r="AI138" s="14"/>
       <c r="AJ138" s="14"/>
     </row>
-    <row r="139">
+    <row r="139" hidden="1">
       <c r="A139" s="7" t="s">
         <v>201</v>
       </c>
@@ -9596,7 +9596,7 @@
       <c r="AI139" s="14"/>
       <c r="AJ139" s="14"/>
     </row>
-    <row r="140">
+    <row r="140" hidden="1">
       <c r="A140" s="7" t="s">
         <v>202</v>
       </c>
@@ -9650,7 +9650,7 @@
       <c r="AI140" s="14"/>
       <c r="AJ140" s="14"/>
     </row>
-    <row r="141">
+    <row r="141" hidden="1">
       <c r="A141" s="7" t="s">
         <v>203</v>
       </c>
@@ -9704,7 +9704,7 @@
       <c r="AI141" s="14"/>
       <c r="AJ141" s="14"/>
     </row>
-    <row r="142">
+    <row r="142" hidden="1">
       <c r="A142" s="7" t="s">
         <v>204</v>
       </c>
@@ -9758,7 +9758,7 @@
       <c r="AI142" s="14"/>
       <c r="AJ142" s="14"/>
     </row>
-    <row r="143">
+    <row r="143" hidden="1">
       <c r="A143" s="7" t="s">
         <v>205</v>
       </c>
@@ -9816,7 +9816,7 @@
       <c r="AI143" s="14"/>
       <c r="AJ143" s="14"/>
     </row>
-    <row r="144">
+    <row r="144" hidden="1">
       <c r="A144" s="7" t="s">
         <v>206</v>
       </c>
@@ -9872,7 +9872,7 @@
       <c r="AI144" s="14"/>
       <c r="AJ144" s="14"/>
     </row>
-    <row r="145">
+    <row r="145" hidden="1">
       <c r="A145" s="7" t="s">
         <v>207</v>
       </c>
@@ -9928,7 +9928,7 @@
       <c r="AI145" s="14"/>
       <c r="AJ145" s="14"/>
     </row>
-    <row r="146">
+    <row r="146" hidden="1">
       <c r="A146" s="7" t="s">
         <v>208</v>
       </c>
@@ -9986,7 +9986,7 @@
       <c r="AI146" s="14"/>
       <c r="AJ146" s="14"/>
     </row>
-    <row r="147">
+    <row r="147" hidden="1">
       <c r="A147" s="9" t="s">
         <v>209</v>
       </c>
@@ -10040,7 +10040,7 @@
       <c r="AI147" s="14"/>
       <c r="AJ147" s="14"/>
     </row>
-    <row r="148">
+    <row r="148" hidden="1">
       <c r="A148" s="9" t="s">
         <v>210</v>
       </c>
@@ -10096,7 +10096,7 @@
       <c r="AI148" s="14"/>
       <c r="AJ148" s="14"/>
     </row>
-    <row r="149">
+    <row r="149" hidden="1">
       <c r="A149" s="9" t="s">
         <v>211</v>
       </c>
@@ -10150,7 +10150,7 @@
       <c r="AI149" s="14"/>
       <c r="AJ149" s="14"/>
     </row>
-    <row r="150">
+    <row r="150" hidden="1">
       <c r="A150" s="9" t="s">
         <v>212</v>
       </c>
@@ -10204,7 +10204,7 @@
       <c r="AI150" s="14"/>
       <c r="AJ150" s="14"/>
     </row>
-    <row r="151">
+    <row r="151" hidden="1">
       <c r="A151" s="9" t="s">
         <v>213</v>
       </c>
@@ -10258,7 +10258,7 @@
       <c r="AI151" s="14"/>
       <c r="AJ151" s="14"/>
     </row>
-    <row r="152">
+    <row r="152" hidden="1">
       <c r="A152" s="9" t="s">
         <v>214</v>
       </c>
@@ -10314,7 +10314,7 @@
       <c r="AI152" s="14"/>
       <c r="AJ152" s="14"/>
     </row>
-    <row r="153">
+    <row r="153" hidden="1">
       <c r="A153" s="9" t="s">
         <v>215</v>
       </c>
@@ -10368,7 +10368,7 @@
       <c r="AI153" s="14"/>
       <c r="AJ153" s="14"/>
     </row>
-    <row r="154">
+    <row r="154" hidden="1">
       <c r="A154" s="9" t="s">
         <v>216</v>
       </c>
@@ -10424,7 +10424,7 @@
       <c r="AI154" s="14"/>
       <c r="AJ154" s="14"/>
     </row>
-    <row r="155">
+    <row r="155" hidden="1">
       <c r="A155" s="9" t="s">
         <v>217</v>
       </c>
@@ -10478,7 +10478,7 @@
       <c r="AI155" s="14"/>
       <c r="AJ155" s="14"/>
     </row>
-    <row r="156">
+    <row r="156" hidden="1">
       <c r="A156" s="9" t="s">
         <v>218</v>
       </c>
@@ -10532,7 +10532,7 @@
       <c r="AI156" s="14"/>
       <c r="AJ156" s="14"/>
     </row>
-    <row r="157">
+    <row r="157" hidden="1">
       <c r="A157" s="9" t="s">
         <v>219</v>
       </c>
@@ -10588,7 +10588,7 @@
       <c r="AI157" s="14"/>
       <c r="AJ157" s="14"/>
     </row>
-    <row r="158">
+    <row r="158" hidden="1">
       <c r="A158" s="9" t="s">
         <v>220</v>
       </c>
@@ -10642,7 +10642,7 @@
       <c r="AI158" s="14"/>
       <c r="AJ158" s="14"/>
     </row>
-    <row r="159">
+    <row r="159" hidden="1">
       <c r="A159" s="9" t="s">
         <v>221</v>
       </c>
@@ -10698,7 +10698,7 @@
       <c r="AI159" s="14"/>
       <c r="AJ159" s="14"/>
     </row>
-    <row r="160">
+    <row r="160" hidden="1">
       <c r="A160" s="9" t="s">
         <v>222</v>
       </c>
@@ -10754,7 +10754,7 @@
       <c r="AI160" s="14"/>
       <c r="AJ160" s="14"/>
     </row>
-    <row r="161">
+    <row r="161" hidden="1">
       <c r="A161" s="9" t="s">
         <v>223</v>
       </c>
@@ -10810,7 +10810,7 @@
       <c r="AI161" s="14"/>
       <c r="AJ161" s="14"/>
     </row>
-    <row r="162">
+    <row r="162" hidden="1">
       <c r="A162" s="9" t="s">
         <v>224</v>
       </c>
@@ -10866,7 +10866,7 @@
       <c r="AI162" s="14"/>
       <c r="AJ162" s="14"/>
     </row>
-    <row r="163">
+    <row r="163" hidden="1">
       <c r="A163" s="9" t="s">
         <v>225</v>
       </c>
@@ -10920,7 +10920,7 @@
       <c r="AI163" s="14"/>
       <c r="AJ163" s="14"/>
     </row>
-    <row r="164">
+    <row r="164" hidden="1">
       <c r="A164" s="9" t="s">
         <v>226</v>
       </c>
@@ -10974,7 +10974,7 @@
       <c r="AI164" s="14"/>
       <c r="AJ164" s="14"/>
     </row>
-    <row r="165">
+    <row r="165" hidden="1">
       <c r="A165" s="9" t="s">
         <v>227</v>
       </c>
@@ -11030,7 +11030,7 @@
       <c r="AI165" s="14"/>
       <c r="AJ165" s="14"/>
     </row>
-    <row r="166">
+    <row r="166" hidden="1">
       <c r="A166" s="9" t="s">
         <v>228</v>
       </c>
@@ -11084,7 +11084,7 @@
       <c r="AI166" s="14"/>
       <c r="AJ166" s="14"/>
     </row>
-    <row r="167">
+    <row r="167" hidden="1">
       <c r="A167" s="9" t="s">
         <v>229</v>
       </c>
@@ -11140,7 +11140,7 @@
       <c r="AI167" s="14"/>
       <c r="AJ167" s="14"/>
     </row>
-    <row r="168">
+    <row r="168" hidden="1">
       <c r="A168" s="9" t="s">
         <v>230</v>
       </c>
@@ -11196,7 +11196,7 @@
       <c r="AI168" s="14"/>
       <c r="AJ168" s="14"/>
     </row>
-    <row r="169">
+    <row r="169" hidden="1">
       <c r="A169" s="9" t="s">
         <v>231</v>
       </c>
@@ -11256,7 +11256,7 @@
       <c r="AI169" s="14"/>
       <c r="AJ169" s="14"/>
     </row>
-    <row r="170">
+    <row r="170" hidden="1">
       <c r="A170" s="9" t="s">
         <v>233</v>
       </c>
@@ -11312,7 +11312,7 @@
       <c r="AI170" s="14"/>
       <c r="AJ170" s="14"/>
     </row>
-    <row r="171">
+    <row r="171" hidden="1">
       <c r="A171" s="14"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -11350,7 +11350,7 @@
       <c r="AI171" s="14"/>
       <c r="AJ171" s="14"/>
     </row>
-    <row r="172">
+    <row r="172" hidden="1">
       <c r="A172" s="14"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -11388,7 +11388,7 @@
       <c r="AI172" s="14"/>
       <c r="AJ172" s="14"/>
     </row>
-    <row r="173">
+    <row r="173" hidden="1">
       <c r="A173" s="14"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -11426,7 +11426,7 @@
       <c r="AI173" s="14"/>
       <c r="AJ173" s="14"/>
     </row>
-    <row r="174">
+    <row r="174" hidden="1">
       <c r="A174" s="14"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -11464,7 +11464,7 @@
       <c r="AI174" s="14"/>
       <c r="AJ174" s="14"/>
     </row>
-    <row r="175">
+    <row r="175" hidden="1">
       <c r="A175" s="14"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -11502,7 +11502,7 @@
       <c r="AI175" s="14"/>
       <c r="AJ175" s="14"/>
     </row>
-    <row r="176">
+    <row r="176" hidden="1">
       <c r="A176" s="14"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -11540,7 +11540,7 @@
       <c r="AI176" s="14"/>
       <c r="AJ176" s="14"/>
     </row>
-    <row r="177">
+    <row r="177" hidden="1">
       <c r="A177" s="14"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -11578,7 +11578,7 @@
       <c r="AI177" s="14"/>
       <c r="AJ177" s="14"/>
     </row>
-    <row r="178">
+    <row r="178" hidden="1">
       <c r="A178" s="14"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -11616,7 +11616,7 @@
       <c r="AI178" s="14"/>
       <c r="AJ178" s="14"/>
     </row>
-    <row r="179">
+    <row r="179" hidden="1">
       <c r="A179" s="14"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -11654,7 +11654,7 @@
       <c r="AI179" s="14"/>
       <c r="AJ179" s="14"/>
     </row>
-    <row r="180">
+    <row r="180" hidden="1">
       <c r="A180" s="14"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -11692,7 +11692,7 @@
       <c r="AI180" s="14"/>
       <c r="AJ180" s="14"/>
     </row>
-    <row r="181">
+    <row r="181" hidden="1">
       <c r="A181" s="14"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -11730,7 +11730,7 @@
       <c r="AI181" s="14"/>
       <c r="AJ181" s="14"/>
     </row>
-    <row r="182">
+    <row r="182" hidden="1">
       <c r="A182" s="14"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -11768,7 +11768,7 @@
       <c r="AI182" s="14"/>
       <c r="AJ182" s="14"/>
     </row>
-    <row r="183">
+    <row r="183" hidden="1">
       <c r="A183" s="14"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -11806,7 +11806,7 @@
       <c r="AI183" s="14"/>
       <c r="AJ183" s="14"/>
     </row>
-    <row r="184">
+    <row r="184" hidden="1">
       <c r="A184" s="14"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -11844,7 +11844,7 @@
       <c r="AI184" s="14"/>
       <c r="AJ184" s="14"/>
     </row>
-    <row r="185">
+    <row r="185" hidden="1">
       <c r="A185" s="14"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -11882,7 +11882,7 @@
       <c r="AI185" s="14"/>
       <c r="AJ185" s="14"/>
     </row>
-    <row r="186">
+    <row r="186" hidden="1">
       <c r="A186" s="14"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -11920,7 +11920,7 @@
       <c r="AI186" s="14"/>
       <c r="AJ186" s="14"/>
     </row>
-    <row r="187">
+    <row r="187" hidden="1">
       <c r="A187" s="14"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -11958,7 +11958,7 @@
       <c r="AI187" s="14"/>
       <c r="AJ187" s="14"/>
     </row>
-    <row r="188">
+    <row r="188" hidden="1">
       <c r="A188" s="14"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -11996,7 +11996,7 @@
       <c r="AI188" s="14"/>
       <c r="AJ188" s="14"/>
     </row>
-    <row r="189">
+    <row r="189" hidden="1">
       <c r="A189" s="14"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -12034,7 +12034,7 @@
       <c r="AI189" s="14"/>
       <c r="AJ189" s="14"/>
     </row>
-    <row r="190">
+    <row r="190" hidden="1">
       <c r="A190" s="14"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -12072,7 +12072,7 @@
       <c r="AI190" s="14"/>
       <c r="AJ190" s="14"/>
     </row>
-    <row r="191">
+    <row r="191" hidden="1">
       <c r="A191" s="14"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -12110,7 +12110,7 @@
       <c r="AI191" s="14"/>
       <c r="AJ191" s="14"/>
     </row>
-    <row r="192">
+    <row r="192" hidden="1">
       <c r="A192" s="14"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -12148,7 +12148,7 @@
       <c r="AI192" s="14"/>
       <c r="AJ192" s="14"/>
     </row>
-    <row r="193">
+    <row r="193" hidden="1">
       <c r="A193" s="14"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -12186,7 +12186,7 @@
       <c r="AI193" s="14"/>
       <c r="AJ193" s="14"/>
     </row>
-    <row r="194">
+    <row r="194" hidden="1">
       <c r="A194" s="14"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -12224,7 +12224,7 @@
       <c r="AI194" s="14"/>
       <c r="AJ194" s="14"/>
     </row>
-    <row r="195">
+    <row r="195" hidden="1">
       <c r="A195" s="14"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -12262,7 +12262,7 @@
       <c r="AI195" s="14"/>
       <c r="AJ195" s="14"/>
     </row>
-    <row r="196">
+    <row r="196" hidden="1">
       <c r="A196" s="14"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -12300,7 +12300,7 @@
       <c r="AI196" s="14"/>
       <c r="AJ196" s="14"/>
     </row>
-    <row r="197">
+    <row r="197" hidden="1">
       <c r="A197" s="14"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -12338,7 +12338,7 @@
       <c r="AI197" s="14"/>
       <c r="AJ197" s="14"/>
     </row>
-    <row r="198">
+    <row r="198" hidden="1">
       <c r="A198" s="14"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -12376,7 +12376,7 @@
       <c r="AI198" s="14"/>
       <c r="AJ198" s="14"/>
     </row>
-    <row r="199">
+    <row r="199" hidden="1">
       <c r="A199" s="14"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -12414,7 +12414,7 @@
       <c r="AI199" s="14"/>
       <c r="AJ199" s="14"/>
     </row>
-    <row r="200">
+    <row r="200" hidden="1">
       <c r="A200" s="14"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -12452,7 +12452,7 @@
       <c r="AI200" s="14"/>
       <c r="AJ200" s="14"/>
     </row>
-    <row r="201">
+    <row r="201" hidden="1">
       <c r="A201" s="14"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -12490,7 +12490,7 @@
       <c r="AI201" s="14"/>
       <c r="AJ201" s="14"/>
     </row>
-    <row r="202">
+    <row r="202" hidden="1">
       <c r="A202" s="14"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -12528,7 +12528,7 @@
       <c r="AI202" s="14"/>
       <c r="AJ202" s="14"/>
     </row>
-    <row r="203">
+    <row r="203" hidden="1">
       <c r="A203" s="14"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -12566,7 +12566,7 @@
       <c r="AI203" s="14"/>
       <c r="AJ203" s="14"/>
     </row>
-    <row r="204">
+    <row r="204" hidden="1">
       <c r="A204" s="14"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -12604,7 +12604,7 @@
       <c r="AI204" s="14"/>
       <c r="AJ204" s="14"/>
     </row>
-    <row r="205">
+    <row r="205" hidden="1">
       <c r="A205" s="14"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -12642,7 +12642,7 @@
       <c r="AI205" s="14"/>
       <c r="AJ205" s="14"/>
     </row>
-    <row r="206">
+    <row r="206" hidden="1">
       <c r="A206" s="14"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -12680,7 +12680,7 @@
       <c r="AI206" s="14"/>
       <c r="AJ206" s="14"/>
     </row>
-    <row r="207">
+    <row r="207" hidden="1">
       <c r="A207" s="14"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -12718,7 +12718,7 @@
       <c r="AI207" s="14"/>
       <c r="AJ207" s="14"/>
     </row>
-    <row r="208">
+    <row r="208" hidden="1">
       <c r="A208" s="14"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -12756,7 +12756,7 @@
       <c r="AI208" s="14"/>
       <c r="AJ208" s="14"/>
     </row>
-    <row r="209">
+    <row r="209" hidden="1">
       <c r="A209" s="14"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -12794,7 +12794,7 @@
       <c r="AI209" s="14"/>
       <c r="AJ209" s="14"/>
     </row>
-    <row r="210">
+    <row r="210" hidden="1">
       <c r="A210" s="14"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -12832,7 +12832,7 @@
       <c r="AI210" s="14"/>
       <c r="AJ210" s="14"/>
     </row>
-    <row r="211">
+    <row r="211" hidden="1">
       <c r="A211" s="14"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -12870,7 +12870,7 @@
       <c r="AI211" s="14"/>
       <c r="AJ211" s="14"/>
     </row>
-    <row r="212">
+    <row r="212" hidden="1">
       <c r="A212" s="14"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -12908,7 +12908,7 @@
       <c r="AI212" s="14"/>
       <c r="AJ212" s="14"/>
     </row>
-    <row r="213">
+    <row r="213" hidden="1">
       <c r="A213" s="14"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -12946,7 +12946,7 @@
       <c r="AI213" s="14"/>
       <c r="AJ213" s="14"/>
     </row>
-    <row r="214">
+    <row r="214" hidden="1">
       <c r="A214" s="14"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -12984,7 +12984,7 @@
       <c r="AI214" s="14"/>
       <c r="AJ214" s="14"/>
     </row>
-    <row r="215">
+    <row r="215" hidden="1">
       <c r="A215" s="14"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -13022,7 +13022,7 @@
       <c r="AI215" s="14"/>
       <c r="AJ215" s="14"/>
     </row>
-    <row r="216">
+    <row r="216" hidden="1">
       <c r="A216" s="14"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -13060,7 +13060,7 @@
       <c r="AI216" s="14"/>
       <c r="AJ216" s="14"/>
     </row>
-    <row r="217">
+    <row r="217" hidden="1">
       <c r="A217" s="14"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -13098,7 +13098,7 @@
       <c r="AI217" s="14"/>
       <c r="AJ217" s="14"/>
     </row>
-    <row r="218">
+    <row r="218" hidden="1">
       <c r="A218" s="14"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -13136,7 +13136,7 @@
       <c r="AI218" s="14"/>
       <c r="AJ218" s="14"/>
     </row>
-    <row r="219">
+    <row r="219" hidden="1">
       <c r="A219" s="14"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -13174,7 +13174,7 @@
       <c r="AI219" s="14"/>
       <c r="AJ219" s="14"/>
     </row>
-    <row r="220">
+    <row r="220" hidden="1">
       <c r="A220" s="14"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -13212,7 +13212,7 @@
       <c r="AI220" s="14"/>
       <c r="AJ220" s="14"/>
     </row>
-    <row r="221">
+    <row r="221" hidden="1">
       <c r="A221" s="14"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -13250,7 +13250,7 @@
       <c r="AI221" s="14"/>
       <c r="AJ221" s="14"/>
     </row>
-    <row r="222">
+    <row r="222" hidden="1">
       <c r="A222" s="14"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -13288,7 +13288,7 @@
       <c r="AI222" s="14"/>
       <c r="AJ222" s="14"/>
     </row>
-    <row r="223">
+    <row r="223" hidden="1">
       <c r="A223" s="14"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -13326,7 +13326,7 @@
       <c r="AI223" s="14"/>
       <c r="AJ223" s="14"/>
     </row>
-    <row r="224">
+    <row r="224" hidden="1">
       <c r="A224" s="14"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -13364,7 +13364,7 @@
       <c r="AI224" s="14"/>
       <c r="AJ224" s="14"/>
     </row>
-    <row r="225">
+    <row r="225" hidden="1">
       <c r="A225" s="14"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -13402,7 +13402,7 @@
       <c r="AI225" s="14"/>
       <c r="AJ225" s="14"/>
     </row>
-    <row r="226">
+    <row r="226" hidden="1">
       <c r="A226" s="14"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -13440,7 +13440,7 @@
       <c r="AI226" s="14"/>
       <c r="AJ226" s="14"/>
     </row>
-    <row r="227">
+    <row r="227" hidden="1">
       <c r="A227" s="14"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -13478,7 +13478,7 @@
       <c r="AI227" s="14"/>
       <c r="AJ227" s="14"/>
     </row>
-    <row r="228">
+    <row r="228" hidden="1">
       <c r="A228" s="14"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -13516,7 +13516,7 @@
       <c r="AI228" s="14"/>
       <c r="AJ228" s="14"/>
     </row>
-    <row r="229">
+    <row r="229" hidden="1">
       <c r="A229" s="14"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -13554,7 +13554,7 @@
       <c r="AI229" s="14"/>
       <c r="AJ229" s="14"/>
     </row>
-    <row r="230">
+    <row r="230" hidden="1">
       <c r="A230" s="14"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -13592,7 +13592,7 @@
       <c r="AI230" s="14"/>
       <c r="AJ230" s="14"/>
     </row>
-    <row r="231">
+    <row r="231" hidden="1">
       <c r="A231" s="14"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -13630,7 +13630,7 @@
       <c r="AI231" s="14"/>
       <c r="AJ231" s="14"/>
     </row>
-    <row r="232">
+    <row r="232" hidden="1">
       <c r="A232" s="14"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -13668,7 +13668,7 @@
       <c r="AI232" s="14"/>
       <c r="AJ232" s="14"/>
     </row>
-    <row r="233">
+    <row r="233" hidden="1">
       <c r="A233" s="14"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -13706,7 +13706,7 @@
       <c r="AI233" s="14"/>
       <c r="AJ233" s="14"/>
     </row>
-    <row r="234">
+    <row r="234" hidden="1">
       <c r="A234" s="14"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -13744,7 +13744,7 @@
       <c r="AI234" s="14"/>
       <c r="AJ234" s="14"/>
     </row>
-    <row r="235">
+    <row r="235" hidden="1">
       <c r="A235" s="14"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -13782,7 +13782,7 @@
       <c r="AI235" s="14"/>
       <c r="AJ235" s="14"/>
     </row>
-    <row r="236">
+    <row r="236" hidden="1">
       <c r="A236" s="14"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -13820,7 +13820,7 @@
       <c r="AI236" s="14"/>
       <c r="AJ236" s="14"/>
     </row>
-    <row r="237">
+    <row r="237" hidden="1">
       <c r="A237" s="14"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -13858,7 +13858,7 @@
       <c r="AI237" s="14"/>
       <c r="AJ237" s="14"/>
     </row>
-    <row r="238">
+    <row r="238" hidden="1">
       <c r="A238" s="14"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -13896,7 +13896,7 @@
       <c r="AI238" s="14"/>
       <c r="AJ238" s="14"/>
     </row>
-    <row r="239">
+    <row r="239" hidden="1">
       <c r="A239" s="14"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -13934,7 +13934,7 @@
       <c r="AI239" s="14"/>
       <c r="AJ239" s="14"/>
     </row>
-    <row r="240">
+    <row r="240" hidden="1">
       <c r="A240" s="14"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -13972,7 +13972,7 @@
       <c r="AI240" s="14"/>
       <c r="AJ240" s="14"/>
     </row>
-    <row r="241">
+    <row r="241" hidden="1">
       <c r="A241" s="14"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -14010,7 +14010,7 @@
       <c r="AI241" s="14"/>
       <c r="AJ241" s="14"/>
     </row>
-    <row r="242">
+    <row r="242" hidden="1">
       <c r="A242" s="14"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -14048,7 +14048,7 @@
       <c r="AI242" s="14"/>
       <c r="AJ242" s="14"/>
     </row>
-    <row r="243">
+    <row r="243" hidden="1">
       <c r="A243" s="14"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -14086,7 +14086,7 @@
       <c r="AI243" s="14"/>
       <c r="AJ243" s="14"/>
     </row>
-    <row r="244">
+    <row r="244" hidden="1">
       <c r="A244" s="14"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -14124,7 +14124,7 @@
       <c r="AI244" s="14"/>
       <c r="AJ244" s="14"/>
     </row>
-    <row r="245">
+    <row r="245" hidden="1">
       <c r="A245" s="14"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -14162,7 +14162,7 @@
       <c r="AI245" s="14"/>
       <c r="AJ245" s="14"/>
     </row>
-    <row r="246">
+    <row r="246" hidden="1">
       <c r="A246" s="14"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -14200,7 +14200,7 @@
       <c r="AI246" s="14"/>
       <c r="AJ246" s="14"/>
     </row>
-    <row r="247">
+    <row r="247" hidden="1">
       <c r="A247" s="14"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -14238,7 +14238,7 @@
       <c r="AI247" s="14"/>
       <c r="AJ247" s="14"/>
     </row>
-    <row r="248">
+    <row r="248" hidden="1">
       <c r="A248" s="14"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -14276,7 +14276,7 @@
       <c r="AI248" s="14"/>
       <c r="AJ248" s="14"/>
     </row>
-    <row r="249">
+    <row r="249" hidden="1">
       <c r="A249" s="14"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -14314,7 +14314,7 @@
       <c r="AI249" s="14"/>
       <c r="AJ249" s="14"/>
     </row>
-    <row r="250">
+    <row r="250" hidden="1">
       <c r="A250" s="14"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -14352,7 +14352,7 @@
       <c r="AI250" s="14"/>
       <c r="AJ250" s="14"/>
     </row>
-    <row r="251">
+    <row r="251" hidden="1">
       <c r="A251" s="14"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -14390,7 +14390,7 @@
       <c r="AI251" s="14"/>
       <c r="AJ251" s="14"/>
     </row>
-    <row r="252">
+    <row r="252" hidden="1">
       <c r="A252" s="14"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -14428,7 +14428,7 @@
       <c r="AI252" s="14"/>
       <c r="AJ252" s="14"/>
     </row>
-    <row r="253">
+    <row r="253" hidden="1">
       <c r="A253" s="14"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -14466,7 +14466,7 @@
       <c r="AI253" s="14"/>
       <c r="AJ253" s="14"/>
     </row>
-    <row r="254">
+    <row r="254" hidden="1">
       <c r="A254" s="14"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -14504,7 +14504,7 @@
       <c r="AI254" s="14"/>
       <c r="AJ254" s="14"/>
     </row>
-    <row r="255">
+    <row r="255" hidden="1">
       <c r="A255" s="14"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -14542,7 +14542,7 @@
       <c r="AI255" s="14"/>
       <c r="AJ255" s="14"/>
     </row>
-    <row r="256">
+    <row r="256" hidden="1">
       <c r="A256" s="14"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -14580,7 +14580,7 @@
       <c r="AI256" s="14"/>
       <c r="AJ256" s="14"/>
     </row>
-    <row r="257">
+    <row r="257" hidden="1">
       <c r="A257" s="14"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -14618,7 +14618,7 @@
       <c r="AI257" s="14"/>
       <c r="AJ257" s="14"/>
     </row>
-    <row r="258">
+    <row r="258" hidden="1">
       <c r="A258" s="14"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -14656,7 +14656,7 @@
       <c r="AI258" s="14"/>
       <c r="AJ258" s="14"/>
     </row>
-    <row r="259">
+    <row r="259" hidden="1">
       <c r="A259" s="14"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -14694,7 +14694,7 @@
       <c r="AI259" s="14"/>
       <c r="AJ259" s="14"/>
     </row>
-    <row r="260">
+    <row r="260" hidden="1">
       <c r="A260" s="14"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -14732,7 +14732,7 @@
       <c r="AI260" s="14"/>
       <c r="AJ260" s="14"/>
     </row>
-    <row r="261">
+    <row r="261" hidden="1">
       <c r="A261" s="14"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -14770,7 +14770,7 @@
       <c r="AI261" s="14"/>
       <c r="AJ261" s="14"/>
     </row>
-    <row r="262">
+    <row r="262" hidden="1">
       <c r="A262" s="14"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -14808,7 +14808,7 @@
       <c r="AI262" s="14"/>
       <c r="AJ262" s="14"/>
     </row>
-    <row r="263">
+    <row r="263" hidden="1">
       <c r="A263" s="14"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -14846,7 +14846,7 @@
       <c r="AI263" s="14"/>
       <c r="AJ263" s="14"/>
     </row>
-    <row r="264">
+    <row r="264" hidden="1">
       <c r="A264" s="14"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -14884,7 +14884,7 @@
       <c r="AI264" s="14"/>
       <c r="AJ264" s="14"/>
     </row>
-    <row r="265">
+    <row r="265" hidden="1">
       <c r="A265" s="14"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -14922,7 +14922,7 @@
       <c r="AI265" s="14"/>
       <c r="AJ265" s="14"/>
     </row>
-    <row r="266">
+    <row r="266" hidden="1">
       <c r="A266" s="14"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -14960,7 +14960,7 @@
       <c r="AI266" s="14"/>
       <c r="AJ266" s="14"/>
     </row>
-    <row r="267">
+    <row r="267" hidden="1">
       <c r="A267" s="14"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -14998,7 +14998,7 @@
       <c r="AI267" s="14"/>
       <c r="AJ267" s="14"/>
     </row>
-    <row r="268">
+    <row r="268" hidden="1">
       <c r="A268" s="14"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -15036,7 +15036,7 @@
       <c r="AI268" s="14"/>
       <c r="AJ268" s="14"/>
     </row>
-    <row r="269">
+    <row r="269" hidden="1">
       <c r="A269" s="14"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -15074,7 +15074,7 @@
       <c r="AI269" s="14"/>
       <c r="AJ269" s="14"/>
     </row>
-    <row r="270">
+    <row r="270" hidden="1">
       <c r="A270" s="14"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -15112,7 +15112,7 @@
       <c r="AI270" s="14"/>
       <c r="AJ270" s="14"/>
     </row>
-    <row r="271">
+    <row r="271" hidden="1">
       <c r="A271" s="14"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -15150,7 +15150,7 @@
       <c r="AI271" s="14"/>
       <c r="AJ271" s="14"/>
     </row>
-    <row r="272">
+    <row r="272" hidden="1">
       <c r="A272" s="14"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -15188,7 +15188,7 @@
       <c r="AI272" s="14"/>
       <c r="AJ272" s="14"/>
     </row>
-    <row r="273">
+    <row r="273" hidden="1">
       <c r="A273" s="14"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -15226,7 +15226,7 @@
       <c r="AI273" s="14"/>
       <c r="AJ273" s="14"/>
     </row>
-    <row r="274">
+    <row r="274" hidden="1">
       <c r="A274" s="14"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -15264,7 +15264,7 @@
       <c r="AI274" s="14"/>
       <c r="AJ274" s="14"/>
     </row>
-    <row r="275">
+    <row r="275" hidden="1">
       <c r="A275" s="14"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -15302,7 +15302,7 @@
       <c r="AI275" s="14"/>
       <c r="AJ275" s="14"/>
     </row>
-    <row r="276">
+    <row r="276" hidden="1">
       <c r="A276" s="14"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -15340,7 +15340,7 @@
       <c r="AI276" s="14"/>
       <c r="AJ276" s="14"/>
     </row>
-    <row r="277">
+    <row r="277" hidden="1">
       <c r="A277" s="14"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -15378,7 +15378,7 @@
       <c r="AI277" s="14"/>
       <c r="AJ277" s="14"/>
     </row>
-    <row r="278">
+    <row r="278" hidden="1">
       <c r="A278" s="14"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -15416,7 +15416,7 @@
       <c r="AI278" s="14"/>
       <c r="AJ278" s="14"/>
     </row>
-    <row r="279">
+    <row r="279" hidden="1">
       <c r="A279" s="14"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -15454,7 +15454,7 @@
       <c r="AI279" s="14"/>
       <c r="AJ279" s="14"/>
     </row>
-    <row r="280">
+    <row r="280" hidden="1">
       <c r="A280" s="14"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -15492,7 +15492,7 @@
       <c r="AI280" s="14"/>
       <c r="AJ280" s="14"/>
     </row>
-    <row r="281">
+    <row r="281" hidden="1">
       <c r="A281" s="14"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -15530,7 +15530,7 @@
       <c r="AI281" s="14"/>
       <c r="AJ281" s="14"/>
     </row>
-    <row r="282">
+    <row r="282" hidden="1">
       <c r="A282" s="14"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -15568,7 +15568,7 @@
       <c r="AI282" s="14"/>
       <c r="AJ282" s="14"/>
     </row>
-    <row r="283">
+    <row r="283" hidden="1">
       <c r="A283" s="14"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -15606,7 +15606,7 @@
       <c r="AI283" s="14"/>
       <c r="AJ283" s="14"/>
     </row>
-    <row r="284">
+    <row r="284" hidden="1">
       <c r="A284" s="14"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -15644,7 +15644,7 @@
       <c r="AI284" s="14"/>
       <c r="AJ284" s="14"/>
     </row>
-    <row r="285">
+    <row r="285" hidden="1">
       <c r="A285" s="14"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -15682,7 +15682,7 @@
       <c r="AI285" s="14"/>
       <c r="AJ285" s="14"/>
     </row>
-    <row r="286">
+    <row r="286" hidden="1">
       <c r="A286" s="14"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -15720,7 +15720,7 @@
       <c r="AI286" s="14"/>
       <c r="AJ286" s="14"/>
     </row>
-    <row r="287">
+    <row r="287" hidden="1">
       <c r="A287" s="14"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -15758,7 +15758,7 @@
       <c r="AI287" s="14"/>
       <c r="AJ287" s="14"/>
     </row>
-    <row r="288">
+    <row r="288" hidden="1">
       <c r="A288" s="14"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -15796,7 +15796,7 @@
       <c r="AI288" s="14"/>
       <c r="AJ288" s="14"/>
     </row>
-    <row r="289">
+    <row r="289" hidden="1">
       <c r="A289" s="14"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -15834,7 +15834,7 @@
       <c r="AI289" s="14"/>
       <c r="AJ289" s="14"/>
     </row>
-    <row r="290">
+    <row r="290" hidden="1">
       <c r="A290" s="14"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -15872,7 +15872,7 @@
       <c r="AI290" s="14"/>
       <c r="AJ290" s="14"/>
     </row>
-    <row r="291">
+    <row r="291" hidden="1">
       <c r="A291" s="14"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -15910,7 +15910,7 @@
       <c r="AI291" s="14"/>
       <c r="AJ291" s="14"/>
     </row>
-    <row r="292">
+    <row r="292" hidden="1">
       <c r="A292" s="14"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -15948,7 +15948,7 @@
       <c r="AI292" s="14"/>
       <c r="AJ292" s="14"/>
     </row>
-    <row r="293">
+    <row r="293" hidden="1">
       <c r="A293" s="14"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -15986,7 +15986,7 @@
       <c r="AI293" s="14"/>
       <c r="AJ293" s="14"/>
     </row>
-    <row r="294">
+    <row r="294" hidden="1">
       <c r="A294" s="14"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -16024,7 +16024,7 @@
       <c r="AI294" s="14"/>
       <c r="AJ294" s="14"/>
     </row>
-    <row r="295">
+    <row r="295" hidden="1">
       <c r="A295" s="14"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -16062,7 +16062,7 @@
       <c r="AI295" s="14"/>
       <c r="AJ295" s="14"/>
     </row>
-    <row r="296">
+    <row r="296" hidden="1">
       <c r="A296" s="14"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -16100,7 +16100,7 @@
       <c r="AI296" s="14"/>
       <c r="AJ296" s="14"/>
     </row>
-    <row r="297">
+    <row r="297" hidden="1">
       <c r="A297" s="14"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -16138,7 +16138,7 @@
       <c r="AI297" s="14"/>
       <c r="AJ297" s="14"/>
     </row>
-    <row r="298">
+    <row r="298" hidden="1">
       <c r="A298" s="14"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -16176,7 +16176,7 @@
       <c r="AI298" s="14"/>
       <c r="AJ298" s="14"/>
     </row>
-    <row r="299">
+    <row r="299" hidden="1">
       <c r="A299" s="14"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -16214,7 +16214,7 @@
       <c r="AI299" s="14"/>
       <c r="AJ299" s="14"/>
     </row>
-    <row r="300">
+    <row r="300" hidden="1">
       <c r="A300" s="14"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -16252,7 +16252,7 @@
       <c r="AI300" s="14"/>
       <c r="AJ300" s="14"/>
     </row>
-    <row r="301">
+    <row r="301" hidden="1">
       <c r="A301" s="14"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -16290,7 +16290,7 @@
       <c r="AI301" s="14"/>
       <c r="AJ301" s="14"/>
     </row>
-    <row r="302">
+    <row r="302" hidden="1">
       <c r="A302" s="14"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -16328,7 +16328,7 @@
       <c r="AI302" s="14"/>
       <c r="AJ302" s="14"/>
     </row>
-    <row r="303">
+    <row r="303" hidden="1">
       <c r="A303" s="14"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -16366,7 +16366,7 @@
       <c r="AI303" s="14"/>
       <c r="AJ303" s="14"/>
     </row>
-    <row r="304">
+    <row r="304" hidden="1">
       <c r="A304" s="14"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -16404,7 +16404,7 @@
       <c r="AI304" s="14"/>
       <c r="AJ304" s="14"/>
     </row>
-    <row r="305">
+    <row r="305" hidden="1">
       <c r="A305" s="14"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -16442,7 +16442,7 @@
       <c r="AI305" s="14"/>
       <c r="AJ305" s="14"/>
     </row>
-    <row r="306">
+    <row r="306" hidden="1">
       <c r="A306" s="14"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -16480,7 +16480,7 @@
       <c r="AI306" s="14"/>
       <c r="AJ306" s="14"/>
     </row>
-    <row r="307">
+    <row r="307" hidden="1">
       <c r="A307" s="14"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -16518,7 +16518,7 @@
       <c r="AI307" s="14"/>
       <c r="AJ307" s="14"/>
     </row>
-    <row r="308">
+    <row r="308" hidden="1">
       <c r="A308" s="14"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -16556,7 +16556,7 @@
       <c r="AI308" s="14"/>
       <c r="AJ308" s="14"/>
     </row>
-    <row r="309">
+    <row r="309" hidden="1">
       <c r="A309" s="14"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -16594,7 +16594,7 @@
       <c r="AI309" s="14"/>
       <c r="AJ309" s="14"/>
     </row>
-    <row r="310">
+    <row r="310" hidden="1">
       <c r="A310" s="14"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -16632,7 +16632,7 @@
       <c r="AI310" s="14"/>
       <c r="AJ310" s="14"/>
     </row>
-    <row r="311">
+    <row r="311" hidden="1">
       <c r="A311" s="14"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -16670,7 +16670,7 @@
       <c r="AI311" s="14"/>
       <c r="AJ311" s="14"/>
     </row>
-    <row r="312">
+    <row r="312" hidden="1">
       <c r="A312" s="14"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -16708,7 +16708,7 @@
       <c r="AI312" s="14"/>
       <c r="AJ312" s="14"/>
     </row>
-    <row r="313">
+    <row r="313" hidden="1">
       <c r="A313" s="14"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -16746,7 +16746,7 @@
       <c r="AI313" s="14"/>
       <c r="AJ313" s="14"/>
     </row>
-    <row r="314">
+    <row r="314" hidden="1">
       <c r="A314" s="14"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -16784,7 +16784,7 @@
       <c r="AI314" s="14"/>
       <c r="AJ314" s="14"/>
     </row>
-    <row r="315">
+    <row r="315" hidden="1">
       <c r="A315" s="14"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -16822,7 +16822,7 @@
       <c r="AI315" s="14"/>
       <c r="AJ315" s="14"/>
     </row>
-    <row r="316">
+    <row r="316" hidden="1">
       <c r="A316" s="14"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -16860,7 +16860,7 @@
       <c r="AI316" s="14"/>
       <c r="AJ316" s="14"/>
     </row>
-    <row r="317">
+    <row r="317" hidden="1">
       <c r="A317" s="14"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -16898,7 +16898,7 @@
       <c r="AI317" s="14"/>
       <c r="AJ317" s="14"/>
     </row>
-    <row r="318">
+    <row r="318" hidden="1">
       <c r="A318" s="14"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -16936,7 +16936,7 @@
       <c r="AI318" s="14"/>
       <c r="AJ318" s="14"/>
     </row>
-    <row r="319">
+    <row r="319" hidden="1">
       <c r="A319" s="14"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -16974,7 +16974,7 @@
       <c r="AI319" s="14"/>
       <c r="AJ319" s="14"/>
     </row>
-    <row r="320">
+    <row r="320" hidden="1">
       <c r="A320" s="14"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -17012,7 +17012,7 @@
       <c r="AI320" s="14"/>
       <c r="AJ320" s="14"/>
     </row>
-    <row r="321">
+    <row r="321" hidden="1">
       <c r="A321" s="14"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -17050,7 +17050,7 @@
       <c r="AI321" s="14"/>
       <c r="AJ321" s="14"/>
     </row>
-    <row r="322">
+    <row r="322" hidden="1">
       <c r="A322" s="14"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -17088,7 +17088,7 @@
       <c r="AI322" s="14"/>
       <c r="AJ322" s="14"/>
     </row>
-    <row r="323">
+    <row r="323" hidden="1">
       <c r="A323" s="14"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -17126,7 +17126,7 @@
       <c r="AI323" s="14"/>
       <c r="AJ323" s="14"/>
     </row>
-    <row r="324">
+    <row r="324" hidden="1">
       <c r="A324" s="14"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -17164,7 +17164,7 @@
       <c r="AI324" s="14"/>
       <c r="AJ324" s="14"/>
     </row>
-    <row r="325">
+    <row r="325" hidden="1">
       <c r="A325" s="14"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -17202,7 +17202,7 @@
       <c r="AI325" s="14"/>
       <c r="AJ325" s="14"/>
     </row>
-    <row r="326">
+    <row r="326" hidden="1">
       <c r="A326" s="14"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -17240,7 +17240,7 @@
       <c r="AI326" s="14"/>
       <c r="AJ326" s="14"/>
     </row>
-    <row r="327">
+    <row r="327" hidden="1">
       <c r="A327" s="14"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -17278,7 +17278,7 @@
       <c r="AI327" s="14"/>
       <c r="AJ327" s="14"/>
     </row>
-    <row r="328">
+    <row r="328" hidden="1">
       <c r="A328" s="14"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -17316,7 +17316,7 @@
       <c r="AI328" s="14"/>
       <c r="AJ328" s="14"/>
     </row>
-    <row r="329">
+    <row r="329" hidden="1">
       <c r="A329" s="14"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -17354,7 +17354,7 @@
       <c r="AI329" s="14"/>
       <c r="AJ329" s="14"/>
     </row>
-    <row r="330">
+    <row r="330" hidden="1">
       <c r="A330" s="14"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -17392,7 +17392,7 @@
       <c r="AI330" s="14"/>
       <c r="AJ330" s="14"/>
     </row>
-    <row r="331">
+    <row r="331" hidden="1">
       <c r="A331" s="14"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -17430,7 +17430,7 @@
       <c r="AI331" s="14"/>
       <c r="AJ331" s="14"/>
     </row>
-    <row r="332">
+    <row r="332" hidden="1">
       <c r="A332" s="14"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -17468,7 +17468,7 @@
       <c r="AI332" s="14"/>
       <c r="AJ332" s="14"/>
     </row>
-    <row r="333">
+    <row r="333" hidden="1">
       <c r="A333" s="14"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -17506,7 +17506,7 @@
       <c r="AI333" s="14"/>
       <c r="AJ333" s="14"/>
     </row>
-    <row r="334">
+    <row r="334" hidden="1">
       <c r="A334" s="14"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -17544,7 +17544,7 @@
       <c r="AI334" s="14"/>
       <c r="AJ334" s="14"/>
     </row>
-    <row r="335">
+    <row r="335" hidden="1">
       <c r="A335" s="14"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -17582,7 +17582,7 @@
       <c r="AI335" s="14"/>
       <c r="AJ335" s="14"/>
     </row>
-    <row r="336">
+    <row r="336" hidden="1">
       <c r="A336" s="14"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -17620,7 +17620,7 @@
       <c r="AI336" s="14"/>
       <c r="AJ336" s="14"/>
     </row>
-    <row r="337">
+    <row r="337" hidden="1">
       <c r="A337" s="14"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -17658,7 +17658,7 @@
       <c r="AI337" s="14"/>
       <c r="AJ337" s="14"/>
     </row>
-    <row r="338">
+    <row r="338" hidden="1">
       <c r="A338" s="14"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -17696,7 +17696,7 @@
       <c r="AI338" s="14"/>
       <c r="AJ338" s="14"/>
     </row>
-    <row r="339">
+    <row r="339" hidden="1">
       <c r="A339" s="14"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -17734,7 +17734,7 @@
       <c r="AI339" s="14"/>
       <c r="AJ339" s="14"/>
     </row>
-    <row r="340">
+    <row r="340" hidden="1">
       <c r="A340" s="14"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -17772,7 +17772,7 @@
       <c r="AI340" s="14"/>
       <c r="AJ340" s="14"/>
     </row>
-    <row r="341">
+    <row r="341" hidden="1">
       <c r="A341" s="14"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -17810,7 +17810,7 @@
       <c r="AI341" s="14"/>
       <c r="AJ341" s="14"/>
     </row>
-    <row r="342">
+    <row r="342" hidden="1">
       <c r="A342" s="14"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -17848,7 +17848,7 @@
       <c r="AI342" s="14"/>
       <c r="AJ342" s="14"/>
     </row>
-    <row r="343">
+    <row r="343" hidden="1">
       <c r="A343" s="14"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -17886,7 +17886,7 @@
       <c r="AI343" s="14"/>
       <c r="AJ343" s="14"/>
     </row>
-    <row r="344">
+    <row r="344" hidden="1">
       <c r="A344" s="14"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -17924,7 +17924,7 @@
       <c r="AI344" s="14"/>
       <c r="AJ344" s="14"/>
     </row>
-    <row r="345">
+    <row r="345" hidden="1">
       <c r="A345" s="14"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -17962,7 +17962,7 @@
       <c r="AI345" s="14"/>
       <c r="AJ345" s="14"/>
     </row>
-    <row r="346">
+    <row r="346" hidden="1">
       <c r="A346" s="14"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -18000,7 +18000,7 @@
       <c r="AI346" s="14"/>
       <c r="AJ346" s="14"/>
     </row>
-    <row r="347">
+    <row r="347" hidden="1">
       <c r="A347" s="14"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -18038,7 +18038,7 @@
       <c r="AI347" s="14"/>
       <c r="AJ347" s="14"/>
     </row>
-    <row r="348">
+    <row r="348" hidden="1">
       <c r="A348" s="14"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -18076,7 +18076,7 @@
       <c r="AI348" s="14"/>
       <c r="AJ348" s="14"/>
     </row>
-    <row r="349">
+    <row r="349" hidden="1">
       <c r="A349" s="14"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -18114,7 +18114,7 @@
       <c r="AI349" s="14"/>
       <c r="AJ349" s="14"/>
     </row>
-    <row r="350">
+    <row r="350" hidden="1">
       <c r="A350" s="14"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -18152,7 +18152,7 @@
       <c r="AI350" s="14"/>
       <c r="AJ350" s="14"/>
     </row>
-    <row r="351">
+    <row r="351" hidden="1">
       <c r="A351" s="14"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -18190,7 +18190,7 @@
       <c r="AI351" s="14"/>
       <c r="AJ351" s="14"/>
     </row>
-    <row r="352">
+    <row r="352" hidden="1">
       <c r="A352" s="14"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -18228,7 +18228,7 @@
       <c r="AI352" s="14"/>
       <c r="AJ352" s="14"/>
     </row>
-    <row r="353">
+    <row r="353" hidden="1">
       <c r="A353" s="14"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -18266,7 +18266,7 @@
       <c r="AI353" s="14"/>
       <c r="AJ353" s="14"/>
     </row>
-    <row r="354">
+    <row r="354" hidden="1">
       <c r="A354" s="14"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -18304,7 +18304,7 @@
       <c r="AI354" s="14"/>
       <c r="AJ354" s="14"/>
     </row>
-    <row r="355">
+    <row r="355" hidden="1">
       <c r="A355" s="14"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -18342,7 +18342,7 @@
       <c r="AI355" s="14"/>
       <c r="AJ355" s="14"/>
     </row>
-    <row r="356">
+    <row r="356" hidden="1">
       <c r="A356" s="14"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -18380,7 +18380,7 @@
       <c r="AI356" s="14"/>
       <c r="AJ356" s="14"/>
     </row>
-    <row r="357">
+    <row r="357" hidden="1">
       <c r="A357" s="14"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -18418,7 +18418,7 @@
       <c r="AI357" s="14"/>
       <c r="AJ357" s="14"/>
     </row>
-    <row r="358">
+    <row r="358" hidden="1">
       <c r="A358" s="14"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -18456,7 +18456,7 @@
       <c r="AI358" s="14"/>
       <c r="AJ358" s="14"/>
     </row>
-    <row r="359">
+    <row r="359" hidden="1">
       <c r="A359" s="14"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -18494,7 +18494,7 @@
       <c r="AI359" s="14"/>
       <c r="AJ359" s="14"/>
     </row>
-    <row r="360">
+    <row r="360" hidden="1">
       <c r="A360" s="14"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -18532,7 +18532,7 @@
       <c r="AI360" s="14"/>
       <c r="AJ360" s="14"/>
     </row>
-    <row r="361">
+    <row r="361" hidden="1">
       <c r="A361" s="14"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -18570,7 +18570,7 @@
       <c r="AI361" s="14"/>
       <c r="AJ361" s="14"/>
     </row>
-    <row r="362">
+    <row r="362" hidden="1">
       <c r="A362" s="14"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -18608,7 +18608,7 @@
       <c r="AI362" s="14"/>
       <c r="AJ362" s="14"/>
     </row>
-    <row r="363">
+    <row r="363" hidden="1">
       <c r="A363" s="14"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -18646,7 +18646,7 @@
       <c r="AI363" s="14"/>
       <c r="AJ363" s="14"/>
     </row>
-    <row r="364">
+    <row r="364" hidden="1">
       <c r="A364" s="14"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -18684,7 +18684,7 @@
       <c r="AI364" s="14"/>
       <c r="AJ364" s="14"/>
     </row>
-    <row r="365">
+    <row r="365" hidden="1">
       <c r="A365" s="14"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -18722,7 +18722,7 @@
       <c r="AI365" s="14"/>
       <c r="AJ365" s="14"/>
     </row>
-    <row r="366">
+    <row r="366" hidden="1">
       <c r="A366" s="14"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -18760,7 +18760,7 @@
       <c r="AI366" s="14"/>
       <c r="AJ366" s="14"/>
     </row>
-    <row r="367">
+    <row r="367" hidden="1">
       <c r="A367" s="14"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -18798,7 +18798,7 @@
       <c r="AI367" s="14"/>
       <c r="AJ367" s="14"/>
     </row>
-    <row r="368">
+    <row r="368" hidden="1">
       <c r="A368" s="14"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -18836,7 +18836,7 @@
       <c r="AI368" s="14"/>
       <c r="AJ368" s="14"/>
     </row>
-    <row r="369">
+    <row r="369" hidden="1">
       <c r="A369" s="14"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -18874,7 +18874,7 @@
       <c r="AI369" s="14"/>
       <c r="AJ369" s="14"/>
     </row>
-    <row r="370">
+    <row r="370" hidden="1">
       <c r="A370" s="14"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -18912,7 +18912,7 @@
       <c r="AI370" s="14"/>
       <c r="AJ370" s="14"/>
     </row>
-    <row r="371">
+    <row r="371" hidden="1">
       <c r="A371" s="14"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -18950,7 +18950,7 @@
       <c r="AI371" s="14"/>
       <c r="AJ371" s="14"/>
     </row>
-    <row r="372">
+    <row r="372" hidden="1">
       <c r="A372" s="14"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -18988,7 +18988,7 @@
       <c r="AI372" s="14"/>
       <c r="AJ372" s="14"/>
     </row>
-    <row r="373">
+    <row r="373" hidden="1">
       <c r="A373" s="14"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -19026,7 +19026,7 @@
       <c r="AI373" s="14"/>
       <c r="AJ373" s="14"/>
     </row>
-    <row r="374">
+    <row r="374" hidden="1">
       <c r="A374" s="14"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -19064,7 +19064,7 @@
       <c r="AI374" s="14"/>
       <c r="AJ374" s="14"/>
     </row>
-    <row r="375">
+    <row r="375" hidden="1">
       <c r="A375" s="14"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -19102,7 +19102,7 @@
       <c r="AI375" s="14"/>
       <c r="AJ375" s="14"/>
     </row>
-    <row r="376">
+    <row r="376" hidden="1">
       <c r="A376" s="14"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -19140,7 +19140,7 @@
       <c r="AI376" s="14"/>
       <c r="AJ376" s="14"/>
     </row>
-    <row r="377">
+    <row r="377" hidden="1">
       <c r="A377" s="14"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -19178,7 +19178,7 @@
       <c r="AI377" s="14"/>
       <c r="AJ377" s="14"/>
     </row>
-    <row r="378">
+    <row r="378" hidden="1">
       <c r="A378" s="14"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -19216,7 +19216,7 @@
       <c r="AI378" s="14"/>
       <c r="AJ378" s="14"/>
     </row>
-    <row r="379">
+    <row r="379" hidden="1">
       <c r="A379" s="14"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -19254,7 +19254,7 @@
       <c r="AI379" s="14"/>
       <c r="AJ379" s="14"/>
     </row>
-    <row r="380">
+    <row r="380" hidden="1">
       <c r="A380" s="14"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -19292,7 +19292,7 @@
       <c r="AI380" s="14"/>
       <c r="AJ380" s="14"/>
     </row>
-    <row r="381">
+    <row r="381" hidden="1">
       <c r="A381" s="14"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -19330,7 +19330,7 @@
       <c r="AI381" s="14"/>
       <c r="AJ381" s="14"/>
     </row>
-    <row r="382">
+    <row r="382" hidden="1">
       <c r="A382" s="14"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -19368,7 +19368,7 @@
       <c r="AI382" s="14"/>
       <c r="AJ382" s="14"/>
     </row>
-    <row r="383">
+    <row r="383" hidden="1">
       <c r="A383" s="14"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -19406,7 +19406,7 @@
       <c r="AI383" s="14"/>
       <c r="AJ383" s="14"/>
     </row>
-    <row r="384">
+    <row r="384" hidden="1">
       <c r="A384" s="14"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -19444,7 +19444,7 @@
       <c r="AI384" s="14"/>
       <c r="AJ384" s="14"/>
     </row>
-    <row r="385">
+    <row r="385" hidden="1">
       <c r="A385" s="14"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -19482,7 +19482,7 @@
       <c r="AI385" s="14"/>
       <c r="AJ385" s="14"/>
     </row>
-    <row r="386">
+    <row r="386" hidden="1">
       <c r="A386" s="14"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -19520,7 +19520,7 @@
       <c r="AI386" s="14"/>
       <c r="AJ386" s="14"/>
     </row>
-    <row r="387">
+    <row r="387" hidden="1">
       <c r="A387" s="14"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -19558,7 +19558,7 @@
       <c r="AI387" s="14"/>
       <c r="AJ387" s="14"/>
     </row>
-    <row r="388">
+    <row r="388" hidden="1">
       <c r="A388" s="14"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -19596,7 +19596,7 @@
       <c r="AI388" s="14"/>
       <c r="AJ388" s="14"/>
     </row>
-    <row r="389">
+    <row r="389" hidden="1">
       <c r="A389" s="14"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -19634,7 +19634,7 @@
       <c r="AI389" s="14"/>
       <c r="AJ389" s="14"/>
     </row>
-    <row r="390">
+    <row r="390" hidden="1">
       <c r="A390" s="14"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -19672,7 +19672,7 @@
       <c r="AI390" s="14"/>
       <c r="AJ390" s="14"/>
     </row>
-    <row r="391">
+    <row r="391" hidden="1">
       <c r="A391" s="14"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -19710,7 +19710,7 @@
       <c r="AI391" s="14"/>
       <c r="AJ391" s="14"/>
     </row>
-    <row r="392">
+    <row r="392" hidden="1">
       <c r="A392" s="14"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -19748,7 +19748,7 @@
       <c r="AI392" s="14"/>
       <c r="AJ392" s="14"/>
     </row>
-    <row r="393">
+    <row r="393" hidden="1">
       <c r="A393" s="14"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -19786,7 +19786,7 @@
       <c r="AI393" s="14"/>
       <c r="AJ393" s="14"/>
     </row>
-    <row r="394">
+    <row r="394" hidden="1">
       <c r="A394" s="14"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -19824,7 +19824,7 @@
       <c r="AI394" s="14"/>
       <c r="AJ394" s="14"/>
     </row>
-    <row r="395">
+    <row r="395" hidden="1">
       <c r="A395" s="14"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -19862,7 +19862,7 @@
       <c r="AI395" s="14"/>
       <c r="AJ395" s="14"/>
     </row>
-    <row r="396">
+    <row r="396" hidden="1">
       <c r="A396" s="14"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -19900,7 +19900,7 @@
       <c r="AI396" s="14"/>
       <c r="AJ396" s="14"/>
     </row>
-    <row r="397">
+    <row r="397" hidden="1">
       <c r="A397" s="14"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -19938,7 +19938,7 @@
       <c r="AI397" s="14"/>
       <c r="AJ397" s="14"/>
     </row>
-    <row r="398">
+    <row r="398" hidden="1">
       <c r="A398" s="14"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -19976,7 +19976,7 @@
       <c r="AI398" s="14"/>
       <c r="AJ398" s="14"/>
     </row>
-    <row r="399">
+    <row r="399" hidden="1">
       <c r="A399" s="14"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -20014,7 +20014,7 @@
       <c r="AI399" s="14"/>
       <c r="AJ399" s="14"/>
     </row>
-    <row r="400">
+    <row r="400" hidden="1">
       <c r="A400" s="14"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -20052,7 +20052,7 @@
       <c r="AI400" s="14"/>
       <c r="AJ400" s="14"/>
     </row>
-    <row r="401">
+    <row r="401" hidden="1">
       <c r="A401" s="14"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
@@ -20090,7 +20090,7 @@
       <c r="AI401" s="14"/>
       <c r="AJ401" s="14"/>
     </row>
-    <row r="402">
+    <row r="402" hidden="1">
       <c r="A402" s="14"/>
       <c r="B402" s="14"/>
       <c r="C402" s="14"/>
@@ -20128,7 +20128,7 @@
       <c r="AI402" s="14"/>
       <c r="AJ402" s="14"/>
     </row>
-    <row r="403">
+    <row r="403" hidden="1">
       <c r="A403" s="14"/>
       <c r="B403" s="14"/>
       <c r="C403" s="14"/>
@@ -20166,7 +20166,7 @@
       <c r="AI403" s="14"/>
       <c r="AJ403" s="14"/>
     </row>
-    <row r="404">
+    <row r="404" hidden="1">
       <c r="A404" s="14"/>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
@@ -20204,7 +20204,7 @@
       <c r="AI404" s="14"/>
       <c r="AJ404" s="14"/>
     </row>
-    <row r="405">
+    <row r="405" hidden="1">
       <c r="A405" s="14"/>
       <c r="B405" s="14"/>
       <c r="C405" s="14"/>
@@ -20242,7 +20242,7 @@
       <c r="AI405" s="14"/>
       <c r="AJ405" s="14"/>
     </row>
-    <row r="406">
+    <row r="406" hidden="1">
       <c r="A406" s="14"/>
       <c r="B406" s="14"/>
       <c r="C406" s="14"/>
@@ -20280,7 +20280,7 @@
       <c r="AI406" s="14"/>
       <c r="AJ406" s="14"/>
     </row>
-    <row r="407">
+    <row r="407" hidden="1">
       <c r="A407" s="14"/>
       <c r="B407" s="14"/>
       <c r="C407" s="14"/>
@@ -20318,7 +20318,7 @@
       <c r="AI407" s="14"/>
       <c r="AJ407" s="14"/>
     </row>
-    <row r="408">
+    <row r="408" hidden="1">
       <c r="A408" s="14"/>
       <c r="B408" s="14"/>
       <c r="C408" s="14"/>
@@ -20356,7 +20356,7 @@
       <c r="AI408" s="14"/>
       <c r="AJ408" s="14"/>
     </row>
-    <row r="409">
+    <row r="409" hidden="1">
       <c r="A409" s="14"/>
       <c r="B409" s="14"/>
       <c r="C409" s="14"/>
@@ -20394,7 +20394,7 @@
       <c r="AI409" s="14"/>
       <c r="AJ409" s="14"/>
     </row>
-    <row r="410">
+    <row r="410" hidden="1">
       <c r="A410" s="14"/>
       <c r="B410" s="14"/>
       <c r="C410" s="14"/>
@@ -20432,7 +20432,7 @@
       <c r="AI410" s="14"/>
       <c r="AJ410" s="14"/>
     </row>
-    <row r="411">
+    <row r="411" hidden="1">
       <c r="A411" s="14"/>
       <c r="B411" s="14"/>
       <c r="C411" s="14"/>
@@ -20470,7 +20470,7 @@
       <c r="AI411" s="14"/>
       <c r="AJ411" s="14"/>
     </row>
-    <row r="412">
+    <row r="412" hidden="1">
       <c r="A412" s="14"/>
       <c r="B412" s="14"/>
       <c r="C412" s="14"/>
@@ -20508,7 +20508,7 @@
       <c r="AI412" s="14"/>
       <c r="AJ412" s="14"/>
     </row>
-    <row r="413">
+    <row r="413" hidden="1">
       <c r="A413" s="14"/>
       <c r="B413" s="14"/>
       <c r="C413" s="14"/>
@@ -20546,7 +20546,7 @@
       <c r="AI413" s="14"/>
       <c r="AJ413" s="14"/>
     </row>
-    <row r="414">
+    <row r="414" hidden="1">
       <c r="A414" s="14"/>
       <c r="B414" s="14"/>
       <c r="C414" s="14"/>
@@ -20584,7 +20584,7 @@
       <c r="AI414" s="14"/>
       <c r="AJ414" s="14"/>
     </row>
-    <row r="415">
+    <row r="415" hidden="1">
       <c r="A415" s="14"/>
       <c r="B415" s="14"/>
       <c r="C415" s="14"/>
@@ -20622,7 +20622,7 @@
       <c r="AI415" s="14"/>
       <c r="AJ415" s="14"/>
     </row>
-    <row r="416">
+    <row r="416" hidden="1">
       <c r="A416" s="14"/>
       <c r="B416" s="14"/>
       <c r="C416" s="14"/>
@@ -20660,7 +20660,7 @@
       <c r="AI416" s="14"/>
       <c r="AJ416" s="14"/>
     </row>
-    <row r="417">
+    <row r="417" hidden="1">
       <c r="A417" s="14"/>
       <c r="B417" s="14"/>
       <c r="C417" s="14"/>
@@ -20698,7 +20698,7 @@
       <c r="AI417" s="14"/>
       <c r="AJ417" s="14"/>
     </row>
-    <row r="418">
+    <row r="418" hidden="1">
       <c r="A418" s="14"/>
       <c r="B418" s="14"/>
       <c r="C418" s="14"/>
@@ -20736,7 +20736,7 @@
       <c r="AI418" s="14"/>
       <c r="AJ418" s="14"/>
     </row>
-    <row r="419">
+    <row r="419" hidden="1">
       <c r="A419" s="14"/>
       <c r="B419" s="14"/>
       <c r="C419" s="14"/>
@@ -20774,7 +20774,7 @@
       <c r="AI419" s="14"/>
       <c r="AJ419" s="14"/>
     </row>
-    <row r="420">
+    <row r="420" hidden="1">
       <c r="A420" s="14"/>
       <c r="B420" s="14"/>
       <c r="C420" s="14"/>
@@ -20812,7 +20812,7 @@
       <c r="AI420" s="14"/>
       <c r="AJ420" s="14"/>
     </row>
-    <row r="421">
+    <row r="421" hidden="1">
       <c r="A421" s="14"/>
       <c r="B421" s="14"/>
       <c r="C421" s="14"/>
@@ -20850,7 +20850,7 @@
       <c r="AI421" s="14"/>
       <c r="AJ421" s="14"/>
     </row>
-    <row r="422">
+    <row r="422" hidden="1">
       <c r="A422" s="14"/>
       <c r="B422" s="14"/>
       <c r="C422" s="14"/>
@@ -20888,7 +20888,7 @@
       <c r="AI422" s="14"/>
       <c r="AJ422" s="14"/>
     </row>
-    <row r="423">
+    <row r="423" hidden="1">
       <c r="A423" s="14"/>
       <c r="B423" s="14"/>
       <c r="C423" s="14"/>
@@ -20926,7 +20926,7 @@
       <c r="AI423" s="14"/>
       <c r="AJ423" s="14"/>
     </row>
-    <row r="424">
+    <row r="424" hidden="1">
       <c r="A424" s="14"/>
       <c r="B424" s="14"/>
       <c r="C424" s="14"/>
@@ -20964,7 +20964,7 @@
       <c r="AI424" s="14"/>
       <c r="AJ424" s="14"/>
     </row>
-    <row r="425">
+    <row r="425" hidden="1">
       <c r="A425" s="14"/>
       <c r="B425" s="14"/>
       <c r="C425" s="14"/>
@@ -21002,7 +21002,7 @@
       <c r="AI425" s="14"/>
       <c r="AJ425" s="14"/>
     </row>
-    <row r="426">
+    <row r="426" hidden="1">
       <c r="A426" s="14"/>
       <c r="B426" s="14"/>
       <c r="C426" s="14"/>
@@ -21040,7 +21040,7 @@
       <c r="AI426" s="14"/>
       <c r="AJ426" s="14"/>
     </row>
-    <row r="427">
+    <row r="427" hidden="1">
       <c r="A427" s="14"/>
       <c r="B427" s="14"/>
       <c r="C427" s="14"/>
@@ -21078,7 +21078,7 @@
       <c r="AI427" s="14"/>
       <c r="AJ427" s="14"/>
     </row>
-    <row r="428">
+    <row r="428" hidden="1">
       <c r="A428" s="14"/>
       <c r="B428" s="14"/>
       <c r="C428" s="14"/>
@@ -21116,7 +21116,7 @@
       <c r="AI428" s="14"/>
       <c r="AJ428" s="14"/>
     </row>
-    <row r="429">
+    <row r="429" hidden="1">
       <c r="A429" s="14"/>
       <c r="B429" s="14"/>
       <c r="C429" s="14"/>
@@ -21154,7 +21154,7 @@
       <c r="AI429" s="14"/>
       <c r="AJ429" s="14"/>
     </row>
-    <row r="430">
+    <row r="430" hidden="1">
       <c r="A430" s="14"/>
       <c r="B430" s="14"/>
       <c r="C430" s="14"/>
@@ -21192,7 +21192,7 @@
       <c r="AI430" s="14"/>
       <c r="AJ430" s="14"/>
     </row>
-    <row r="431">
+    <row r="431" hidden="1">
       <c r="A431" s="14"/>
       <c r="B431" s="14"/>
       <c r="C431" s="14"/>
@@ -21230,7 +21230,7 @@
       <c r="AI431" s="14"/>
       <c r="AJ431" s="14"/>
     </row>
-    <row r="432">
+    <row r="432" hidden="1">
       <c r="A432" s="14"/>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -21268,7 +21268,7 @@
       <c r="AI432" s="14"/>
       <c r="AJ432" s="14"/>
     </row>
-    <row r="433">
+    <row r="433" hidden="1">
       <c r="A433" s="14"/>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -21306,7 +21306,7 @@
       <c r="AI433" s="14"/>
       <c r="AJ433" s="14"/>
     </row>
-    <row r="434">
+    <row r="434" hidden="1">
       <c r="A434" s="14"/>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -21344,7 +21344,7 @@
       <c r="AI434" s="14"/>
       <c r="AJ434" s="14"/>
     </row>
-    <row r="435">
+    <row r="435" hidden="1">
       <c r="A435" s="14"/>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
@@ -21382,7 +21382,7 @@
       <c r="AI435" s="14"/>
       <c r="AJ435" s="14"/>
     </row>
-    <row r="436">
+    <row r="436" hidden="1">
       <c r="A436" s="14"/>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -21420,7 +21420,7 @@
       <c r="AI436" s="14"/>
       <c r="AJ436" s="14"/>
     </row>
-    <row r="437">
+    <row r="437" hidden="1">
       <c r="A437" s="14"/>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -21458,7 +21458,7 @@
       <c r="AI437" s="14"/>
       <c r="AJ437" s="14"/>
     </row>
-    <row r="438">
+    <row r="438" hidden="1">
       <c r="A438" s="14"/>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -21496,7 +21496,7 @@
       <c r="AI438" s="14"/>
       <c r="AJ438" s="14"/>
     </row>
-    <row r="439">
+    <row r="439" hidden="1">
       <c r="A439" s="14"/>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -21534,7 +21534,7 @@
       <c r="AI439" s="14"/>
       <c r="AJ439" s="14"/>
     </row>
-    <row r="440">
+    <row r="440" hidden="1">
       <c r="A440" s="14"/>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -21572,7 +21572,7 @@
       <c r="AI440" s="14"/>
       <c r="AJ440" s="14"/>
     </row>
-    <row r="441">
+    <row r="441" hidden="1">
       <c r="A441" s="14"/>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -21610,7 +21610,7 @@
       <c r="AI441" s="14"/>
       <c r="AJ441" s="14"/>
     </row>
-    <row r="442">
+    <row r="442" hidden="1">
       <c r="A442" s="14"/>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -21648,7 +21648,7 @@
       <c r="AI442" s="14"/>
       <c r="AJ442" s="14"/>
     </row>
-    <row r="443">
+    <row r="443" hidden="1">
       <c r="A443" s="14"/>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
@@ -21686,7 +21686,7 @@
       <c r="AI443" s="14"/>
       <c r="AJ443" s="14"/>
     </row>
-    <row r="444">
+    <row r="444" hidden="1">
       <c r="A444" s="14"/>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
@@ -21724,7 +21724,7 @@
       <c r="AI444" s="14"/>
       <c r="AJ444" s="14"/>
     </row>
-    <row r="445">
+    <row r="445" hidden="1">
       <c r="A445" s="14"/>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
@@ -21762,7 +21762,7 @@
       <c r="AI445" s="14"/>
       <c r="AJ445" s="14"/>
     </row>
-    <row r="446">
+    <row r="446" hidden="1">
       <c r="A446" s="14"/>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
@@ -21800,7 +21800,7 @@
       <c r="AI446" s="14"/>
       <c r="AJ446" s="14"/>
     </row>
-    <row r="447">
+    <row r="447" hidden="1">
       <c r="A447" s="14"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -21838,7 +21838,7 @@
       <c r="AI447" s="14"/>
       <c r="AJ447" s="14"/>
     </row>
-    <row r="448">
+    <row r="448" hidden="1">
       <c r="A448" s="14"/>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -21876,7 +21876,7 @@
       <c r="AI448" s="14"/>
       <c r="AJ448" s="14"/>
     </row>
-    <row r="449">
+    <row r="449" hidden="1">
       <c r="A449" s="14"/>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -21914,7 +21914,7 @@
       <c r="AI449" s="14"/>
       <c r="AJ449" s="14"/>
     </row>
-    <row r="450">
+    <row r="450" hidden="1">
       <c r="A450" s="14"/>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -21952,7 +21952,7 @@
       <c r="AI450" s="14"/>
       <c r="AJ450" s="14"/>
     </row>
-    <row r="451">
+    <row r="451" hidden="1">
       <c r="A451" s="14"/>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -21990,7 +21990,7 @@
       <c r="AI451" s="14"/>
       <c r="AJ451" s="14"/>
     </row>
-    <row r="452">
+    <row r="452" hidden="1">
       <c r="A452" s="14"/>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -22028,7 +22028,7 @@
       <c r="AI452" s="14"/>
       <c r="AJ452" s="14"/>
     </row>
-    <row r="453">
+    <row r="453" hidden="1">
       <c r="A453" s="14"/>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -22066,7 +22066,7 @@
       <c r="AI453" s="14"/>
       <c r="AJ453" s="14"/>
     </row>
-    <row r="454">
+    <row r="454" hidden="1">
       <c r="A454" s="14"/>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -22104,7 +22104,7 @@
       <c r="AI454" s="14"/>
       <c r="AJ454" s="14"/>
     </row>
-    <row r="455">
+    <row r="455" hidden="1">
       <c r="A455" s="14"/>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -22142,7 +22142,7 @@
       <c r="AI455" s="14"/>
       <c r="AJ455" s="14"/>
     </row>
-    <row r="456">
+    <row r="456" hidden="1">
       <c r="A456" s="14"/>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -22180,7 +22180,7 @@
       <c r="AI456" s="14"/>
       <c r="AJ456" s="14"/>
     </row>
-    <row r="457">
+    <row r="457" hidden="1">
       <c r="A457" s="14"/>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -22218,7 +22218,7 @@
       <c r="AI457" s="14"/>
       <c r="AJ457" s="14"/>
     </row>
-    <row r="458">
+    <row r="458" hidden="1">
       <c r="A458" s="14"/>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
@@ -22256,7 +22256,7 @@
       <c r="AI458" s="14"/>
       <c r="AJ458" s="14"/>
     </row>
-    <row r="459">
+    <row r="459" hidden="1">
       <c r="A459" s="14"/>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
@@ -22294,7 +22294,7 @@
       <c r="AI459" s="14"/>
       <c r="AJ459" s="14"/>
     </row>
-    <row r="460">
+    <row r="460" hidden="1">
       <c r="A460" s="14"/>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
@@ -22332,7 +22332,7 @@
       <c r="AI460" s="14"/>
       <c r="AJ460" s="14"/>
     </row>
-    <row r="461">
+    <row r="461" hidden="1">
       <c r="A461" s="14"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -22370,7 +22370,7 @@
       <c r="AI461" s="14"/>
       <c r="AJ461" s="14"/>
     </row>
-    <row r="462">
+    <row r="462" hidden="1">
       <c r="A462" s="14"/>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -22408,7 +22408,7 @@
       <c r="AI462" s="14"/>
       <c r="AJ462" s="14"/>
     </row>
-    <row r="463">
+    <row r="463" hidden="1">
       <c r="A463" s="14"/>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -22446,7 +22446,7 @@
       <c r="AI463" s="14"/>
       <c r="AJ463" s="14"/>
     </row>
-    <row r="464">
+    <row r="464" hidden="1">
       <c r="A464" s="14"/>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -22484,7 +22484,7 @@
       <c r="AI464" s="14"/>
       <c r="AJ464" s="14"/>
     </row>
-    <row r="465">
+    <row r="465" hidden="1">
       <c r="A465" s="14"/>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -22522,7 +22522,7 @@
       <c r="AI465" s="14"/>
       <c r="AJ465" s="14"/>
     </row>
-    <row r="466">
+    <row r="466" hidden="1">
       <c r="A466" s="14"/>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -22560,7 +22560,7 @@
       <c r="AI466" s="14"/>
       <c r="AJ466" s="14"/>
     </row>
-    <row r="467">
+    <row r="467" hidden="1">
       <c r="A467" s="14"/>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -22598,7 +22598,7 @@
       <c r="AI467" s="14"/>
       <c r="AJ467" s="14"/>
     </row>
-    <row r="468">
+    <row r="468" hidden="1">
       <c r="A468" s="14"/>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
@@ -22636,7 +22636,7 @@
       <c r="AI468" s="14"/>
       <c r="AJ468" s="14"/>
     </row>
-    <row r="469">
+    <row r="469" hidden="1">
       <c r="A469" s="14"/>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
@@ -22674,7 +22674,7 @@
       <c r="AI469" s="14"/>
       <c r="AJ469" s="14"/>
     </row>
-    <row r="470">
+    <row r="470" hidden="1">
       <c r="A470" s="14"/>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
@@ -22712,7 +22712,7 @@
       <c r="AI470" s="14"/>
       <c r="AJ470" s="14"/>
     </row>
-    <row r="471">
+    <row r="471" hidden="1">
       <c r="A471" s="14"/>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
@@ -22750,7 +22750,7 @@
       <c r="AI471" s="14"/>
       <c r="AJ471" s="14"/>
     </row>
-    <row r="472">
+    <row r="472" hidden="1">
       <c r="A472" s="14"/>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
@@ -22788,7 +22788,7 @@
       <c r="AI472" s="14"/>
       <c r="AJ472" s="14"/>
     </row>
-    <row r="473">
+    <row r="473" hidden="1">
       <c r="A473" s="14"/>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
@@ -22826,7 +22826,7 @@
       <c r="AI473" s="14"/>
       <c r="AJ473" s="14"/>
     </row>
-    <row r="474">
+    <row r="474" hidden="1">
       <c r="A474" s="14"/>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -22864,7 +22864,7 @@
       <c r="AI474" s="14"/>
       <c r="AJ474" s="14"/>
     </row>
-    <row r="475">
+    <row r="475" hidden="1">
       <c r="A475" s="14"/>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
@@ -22902,7 +22902,7 @@
       <c r="AI475" s="14"/>
       <c r="AJ475" s="14"/>
     </row>
-    <row r="476">
+    <row r="476" hidden="1">
       <c r="A476" s="14"/>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -22940,7 +22940,7 @@
       <c r="AI476" s="14"/>
       <c r="AJ476" s="14"/>
     </row>
-    <row r="477">
+    <row r="477" hidden="1">
       <c r="A477" s="14"/>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -22978,7 +22978,7 @@
       <c r="AI477" s="14"/>
       <c r="AJ477" s="14"/>
     </row>
-    <row r="478">
+    <row r="478" hidden="1">
       <c r="A478" s="14"/>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -23016,7 +23016,7 @@
       <c r="AI478" s="14"/>
       <c r="AJ478" s="14"/>
     </row>
-    <row r="479">
+    <row r="479" hidden="1">
       <c r="A479" s="14"/>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -23054,7 +23054,7 @@
       <c r="AI479" s="14"/>
       <c r="AJ479" s="14"/>
     </row>
-    <row r="480">
+    <row r="480" hidden="1">
       <c r="A480" s="14"/>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
@@ -23092,7 +23092,7 @@
       <c r="AI480" s="14"/>
       <c r="AJ480" s="14"/>
     </row>
-    <row r="481">
+    <row r="481" hidden="1">
       <c r="A481" s="14"/>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -23130,7 +23130,7 @@
       <c r="AI481" s="14"/>
       <c r="AJ481" s="14"/>
     </row>
-    <row r="482">
+    <row r="482" hidden="1">
       <c r="A482" s="14"/>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -23168,7 +23168,7 @@
       <c r="AI482" s="14"/>
       <c r="AJ482" s="14"/>
     </row>
-    <row r="483">
+    <row r="483" hidden="1">
       <c r="A483" s="14"/>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -23206,7 +23206,7 @@
       <c r="AI483" s="14"/>
       <c r="AJ483" s="14"/>
     </row>
-    <row r="484">
+    <row r="484" hidden="1">
       <c r="A484" s="14"/>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
@@ -23244,7 +23244,7 @@
       <c r="AI484" s="14"/>
       <c r="AJ484" s="14"/>
     </row>
-    <row r="485">
+    <row r="485" hidden="1">
       <c r="A485" s="14"/>
       <c r="B485" s="14"/>
       <c r="C485" s="14"/>
@@ -23282,7 +23282,7 @@
       <c r="AI485" s="14"/>
       <c r="AJ485" s="14"/>
     </row>
-    <row r="486">
+    <row r="486" hidden="1">
       <c r="A486" s="14"/>
       <c r="B486" s="14"/>
       <c r="C486" s="14"/>
@@ -23320,7 +23320,7 @@
       <c r="AI486" s="14"/>
       <c r="AJ486" s="14"/>
     </row>
-    <row r="487">
+    <row r="487" hidden="1">
       <c r="A487" s="14"/>
       <c r="B487" s="14"/>
       <c r="C487" s="14"/>
@@ -23358,7 +23358,7 @@
       <c r="AI487" s="14"/>
       <c r="AJ487" s="14"/>
     </row>
-    <row r="488">
+    <row r="488" hidden="1">
       <c r="A488" s="14"/>
       <c r="B488" s="14"/>
       <c r="C488" s="14"/>
@@ -23396,7 +23396,7 @@
       <c r="AI488" s="14"/>
       <c r="AJ488" s="14"/>
     </row>
-    <row r="489">
+    <row r="489" hidden="1">
       <c r="A489" s="14"/>
       <c r="B489" s="14"/>
       <c r="C489" s="14"/>
@@ -23434,7 +23434,7 @@
       <c r="AI489" s="14"/>
       <c r="AJ489" s="14"/>
     </row>
-    <row r="490">
+    <row r="490" hidden="1">
       <c r="A490" s="14"/>
       <c r="B490" s="14"/>
       <c r="C490" s="14"/>
@@ -23472,7 +23472,7 @@
       <c r="AI490" s="14"/>
       <c r="AJ490" s="14"/>
     </row>
-    <row r="491">
+    <row r="491" hidden="1">
       <c r="A491" s="14"/>
       <c r="B491" s="14"/>
       <c r="C491" s="14"/>
@@ -23510,7 +23510,7 @@
       <c r="AI491" s="14"/>
       <c r="AJ491" s="14"/>
     </row>
-    <row r="492">
+    <row r="492" hidden="1">
       <c r="A492" s="14"/>
       <c r="B492" s="14"/>
       <c r="C492" s="14"/>
@@ -23548,7 +23548,7 @@
       <c r="AI492" s="14"/>
       <c r="AJ492" s="14"/>
     </row>
-    <row r="493">
+    <row r="493" hidden="1">
       <c r="A493" s="14"/>
       <c r="B493" s="14"/>
       <c r="C493" s="14"/>
@@ -23586,7 +23586,7 @@
       <c r="AI493" s="14"/>
       <c r="AJ493" s="14"/>
     </row>
-    <row r="494">
+    <row r="494" hidden="1">
       <c r="A494" s="14"/>
       <c r="B494" s="14"/>
       <c r="C494" s="14"/>
@@ -23624,7 +23624,7 @@
       <c r="AI494" s="14"/>
       <c r="AJ494" s="14"/>
     </row>
-    <row r="495">
+    <row r="495" hidden="1">
       <c r="A495" s="14"/>
       <c r="B495" s="14"/>
       <c r="C495" s="14"/>
@@ -23662,7 +23662,7 @@
       <c r="AI495" s="14"/>
       <c r="AJ495" s="14"/>
     </row>
-    <row r="496">
+    <row r="496" hidden="1">
       <c r="A496" s="14"/>
       <c r="B496" s="14"/>
       <c r="C496" s="14"/>
@@ -23700,7 +23700,7 @@
       <c r="AI496" s="14"/>
       <c r="AJ496" s="14"/>
     </row>
-    <row r="497">
+    <row r="497" hidden="1">
       <c r="A497" s="14"/>
       <c r="B497" s="14"/>
       <c r="C497" s="14"/>
@@ -23738,7 +23738,7 @@
       <c r="AI497" s="14"/>
       <c r="AJ497" s="14"/>
     </row>
-    <row r="498">
+    <row r="498" hidden="1">
       <c r="A498" s="14"/>
       <c r="B498" s="14"/>
       <c r="C498" s="14"/>
@@ -23776,7 +23776,7 @@
       <c r="AI498" s="14"/>
       <c r="AJ498" s="14"/>
     </row>
-    <row r="499">
+    <row r="499" hidden="1">
       <c r="A499" s="14"/>
       <c r="B499" s="14"/>
       <c r="C499" s="14"/>
@@ -23814,7 +23814,7 @@
       <c r="AI499" s="14"/>
       <c r="AJ499" s="14"/>
     </row>
-    <row r="500">
+    <row r="500" hidden="1">
       <c r="A500" s="14"/>
       <c r="B500" s="14"/>
       <c r="C500" s="14"/>
@@ -23852,7 +23852,7 @@
       <c r="AI500" s="14"/>
       <c r="AJ500" s="14"/>
     </row>
-    <row r="501">
+    <row r="501" hidden="1">
       <c r="A501" s="14"/>
       <c r="B501" s="14"/>
       <c r="C501" s="14"/>
@@ -23890,7 +23890,7 @@
       <c r="AI501" s="14"/>
       <c r="AJ501" s="14"/>
     </row>
-    <row r="502">
+    <row r="502" hidden="1">
       <c r="A502" s="14"/>
       <c r="B502" s="14"/>
       <c r="C502" s="14"/>
@@ -23928,7 +23928,7 @@
       <c r="AI502" s="14"/>
       <c r="AJ502" s="14"/>
     </row>
-    <row r="503">
+    <row r="503" hidden="1">
       <c r="A503" s="14"/>
       <c r="B503" s="14"/>
       <c r="C503" s="14"/>
@@ -23966,7 +23966,7 @@
       <c r="AI503" s="14"/>
       <c r="AJ503" s="14"/>
     </row>
-    <row r="504">
+    <row r="504" hidden="1">
       <c r="A504" s="14"/>
       <c r="B504" s="14"/>
       <c r="C504" s="14"/>
@@ -24004,7 +24004,7 @@
       <c r="AI504" s="14"/>
       <c r="AJ504" s="14"/>
     </row>
-    <row r="505">
+    <row r="505" hidden="1">
       <c r="A505" s="14"/>
       <c r="B505" s="14"/>
       <c r="C505" s="14"/>
@@ -24042,7 +24042,7 @@
       <c r="AI505" s="14"/>
       <c r="AJ505" s="14"/>
     </row>
-    <row r="506">
+    <row r="506" hidden="1">
       <c r="A506" s="14"/>
       <c r="B506" s="14"/>
       <c r="C506" s="14"/>
@@ -24080,7 +24080,7 @@
       <c r="AI506" s="14"/>
       <c r="AJ506" s="14"/>
     </row>
-    <row r="507">
+    <row r="507" hidden="1">
       <c r="A507" s="14"/>
       <c r="B507" s="14"/>
       <c r="C507" s="14"/>
@@ -24118,7 +24118,7 @@
       <c r="AI507" s="14"/>
       <c r="AJ507" s="14"/>
     </row>
-    <row r="508">
+    <row r="508" hidden="1">
       <c r="A508" s="14"/>
       <c r="B508" s="14"/>
       <c r="C508" s="14"/>
@@ -24156,7 +24156,7 @@
       <c r="AI508" s="14"/>
       <c r="AJ508" s="14"/>
     </row>
-    <row r="509">
+    <row r="509" hidden="1">
       <c r="A509" s="14"/>
       <c r="B509" s="14"/>
       <c r="C509" s="14"/>
@@ -24194,7 +24194,7 @@
       <c r="AI509" s="14"/>
       <c r="AJ509" s="14"/>
     </row>
-    <row r="510">
+    <row r="510" hidden="1">
       <c r="A510" s="14"/>
       <c r="B510" s="14"/>
       <c r="C510" s="14"/>
@@ -24232,7 +24232,7 @@
       <c r="AI510" s="14"/>
       <c r="AJ510" s="14"/>
     </row>
-    <row r="511">
+    <row r="511" hidden="1">
       <c r="A511" s="14"/>
       <c r="B511" s="14"/>
       <c r="C511" s="14"/>
@@ -24270,7 +24270,7 @@
       <c r="AI511" s="14"/>
       <c r="AJ511" s="14"/>
     </row>
-    <row r="512">
+    <row r="512" hidden="1">
       <c r="A512" s="14"/>
       <c r="B512" s="14"/>
       <c r="C512" s="14"/>
@@ -24308,7 +24308,7 @@
       <c r="AI512" s="14"/>
       <c r="AJ512" s="14"/>
     </row>
-    <row r="513">
+    <row r="513" hidden="1">
       <c r="A513" s="14"/>
       <c r="B513" s="14"/>
       <c r="C513" s="14"/>
@@ -24346,7 +24346,7 @@
       <c r="AI513" s="14"/>
       <c r="AJ513" s="14"/>
     </row>
-    <row r="514">
+    <row r="514" hidden="1">
       <c r="A514" s="14"/>
       <c r="B514" s="14"/>
       <c r="C514" s="14"/>
@@ -24384,7 +24384,7 @@
       <c r="AI514" s="14"/>
       <c r="AJ514" s="14"/>
     </row>
-    <row r="515">
+    <row r="515" hidden="1">
       <c r="A515" s="14"/>
       <c r="B515" s="14"/>
       <c r="C515" s="14"/>
@@ -24422,7 +24422,7 @@
       <c r="AI515" s="14"/>
       <c r="AJ515" s="14"/>
     </row>
-    <row r="516">
+    <row r="516" hidden="1">
       <c r="A516" s="14"/>
       <c r="B516" s="14"/>
       <c r="C516" s="14"/>
@@ -24460,7 +24460,7 @@
       <c r="AI516" s="14"/>
       <c r="AJ516" s="14"/>
     </row>
-    <row r="517">
+    <row r="517" hidden="1">
       <c r="A517" s="14"/>
       <c r="B517" s="14"/>
       <c r="C517" s="14"/>
@@ -24498,7 +24498,7 @@
       <c r="AI517" s="14"/>
       <c r="AJ517" s="14"/>
     </row>
-    <row r="518">
+    <row r="518" hidden="1">
       <c r="A518" s="14"/>
       <c r="B518" s="14"/>
       <c r="C518" s="14"/>
@@ -24536,7 +24536,7 @@
       <c r="AI518" s="14"/>
       <c r="AJ518" s="14"/>
     </row>
-    <row r="519">
+    <row r="519" hidden="1">
       <c r="A519" s="14"/>
       <c r="B519" s="14"/>
       <c r="C519" s="14"/>
@@ -24574,7 +24574,7 @@
       <c r="AI519" s="14"/>
       <c r="AJ519" s="14"/>
     </row>
-    <row r="520">
+    <row r="520" hidden="1">
       <c r="A520" s="14"/>
       <c r="B520" s="14"/>
       <c r="C520" s="14"/>
@@ -24612,7 +24612,7 @@
       <c r="AI520" s="14"/>
       <c r="AJ520" s="14"/>
     </row>
-    <row r="521">
+    <row r="521" hidden="1">
       <c r="A521" s="14"/>
       <c r="B521" s="14"/>
       <c r="C521" s="14"/>
@@ -24650,7 +24650,7 @@
       <c r="AI521" s="14"/>
       <c r="AJ521" s="14"/>
     </row>
-    <row r="522">
+    <row r="522" hidden="1">
       <c r="A522" s="14"/>
       <c r="B522" s="14"/>
       <c r="C522" s="14"/>
@@ -24688,7 +24688,7 @@
       <c r="AI522" s="14"/>
       <c r="AJ522" s="14"/>
     </row>
-    <row r="523">
+    <row r="523" hidden="1">
       <c r="A523" s="14"/>
       <c r="B523" s="14"/>
       <c r="C523" s="14"/>
@@ -24726,7 +24726,7 @@
       <c r="AI523" s="14"/>
       <c r="AJ523" s="14"/>
     </row>
-    <row r="524">
+    <row r="524" hidden="1">
       <c r="A524" s="14"/>
       <c r="B524" s="14"/>
       <c r="C524" s="14"/>
@@ -24764,7 +24764,7 @@
       <c r="AI524" s="14"/>
       <c r="AJ524" s="14"/>
     </row>
-    <row r="525">
+    <row r="525" hidden="1">
       <c r="A525" s="14"/>
       <c r="B525" s="14"/>
       <c r="C525" s="14"/>
@@ -24802,7 +24802,7 @@
       <c r="AI525" s="14"/>
       <c r="AJ525" s="14"/>
     </row>
-    <row r="526">
+    <row r="526" hidden="1">
       <c r="A526" s="14"/>
       <c r="B526" s="14"/>
       <c r="C526" s="14"/>
@@ -24840,7 +24840,7 @@
       <c r="AI526" s="14"/>
       <c r="AJ526" s="14"/>
     </row>
-    <row r="527">
+    <row r="527" hidden="1">
       <c r="A527" s="14"/>
       <c r="B527" s="14"/>
       <c r="C527" s="14"/>
@@ -24878,7 +24878,7 @@
       <c r="AI527" s="14"/>
       <c r="AJ527" s="14"/>
     </row>
-    <row r="528">
+    <row r="528" hidden="1">
       <c r="A528" s="14"/>
       <c r="B528" s="14"/>
       <c r="C528" s="14"/>
@@ -24916,7 +24916,7 @@
       <c r="AI528" s="14"/>
       <c r="AJ528" s="14"/>
     </row>
-    <row r="529">
+    <row r="529" hidden="1">
       <c r="A529" s="14"/>
       <c r="B529" s="14"/>
       <c r="C529" s="14"/>
@@ -24954,7 +24954,7 @@
       <c r="AI529" s="14"/>
       <c r="AJ529" s="14"/>
     </row>
-    <row r="530">
+    <row r="530" hidden="1">
       <c r="A530" s="14"/>
       <c r="B530" s="14"/>
       <c r="C530" s="14"/>
@@ -24992,7 +24992,7 @@
       <c r="AI530" s="14"/>
       <c r="AJ530" s="14"/>
     </row>
-    <row r="531">
+    <row r="531" hidden="1">
       <c r="A531" s="14"/>
       <c r="B531" s="14"/>
       <c r="C531" s="14"/>
@@ -25030,7 +25030,7 @@
       <c r="AI531" s="14"/>
       <c r="AJ531" s="14"/>
     </row>
-    <row r="532">
+    <row r="532" hidden="1">
       <c r="A532" s="14"/>
       <c r="B532" s="14"/>
       <c r="C532" s="14"/>
@@ -25068,7 +25068,7 @@
       <c r="AI532" s="14"/>
       <c r="AJ532" s="14"/>
     </row>
-    <row r="533">
+    <row r="533" hidden="1">
       <c r="A533" s="14"/>
       <c r="B533" s="14"/>
       <c r="C533" s="14"/>
@@ -25106,7 +25106,7 @@
       <c r="AI533" s="14"/>
       <c r="AJ533" s="14"/>
     </row>
-    <row r="534">
+    <row r="534" hidden="1">
       <c r="A534" s="14"/>
       <c r="B534" s="14"/>
       <c r="C534" s="14"/>
@@ -25144,7 +25144,7 @@
       <c r="AI534" s="14"/>
       <c r="AJ534" s="14"/>
     </row>
-    <row r="535">
+    <row r="535" hidden="1">
       <c r="A535" s="14"/>
       <c r="B535" s="14"/>
       <c r="C535" s="14"/>
@@ -25182,7 +25182,7 @@
       <c r="AI535" s="14"/>
       <c r="AJ535" s="14"/>
     </row>
-    <row r="536">
+    <row r="536" hidden="1">
       <c r="A536" s="14"/>
       <c r="B536" s="14"/>
       <c r="C536" s="14"/>
@@ -25220,7 +25220,7 @@
       <c r="AI536" s="14"/>
       <c r="AJ536" s="14"/>
     </row>
-    <row r="537">
+    <row r="537" hidden="1">
       <c r="A537" s="14"/>
       <c r="B537" s="14"/>
       <c r="C537" s="14"/>
@@ -25258,7 +25258,7 @@
       <c r="AI537" s="14"/>
       <c r="AJ537" s="14"/>
     </row>
-    <row r="538">
+    <row r="538" hidden="1">
       <c r="A538" s="14"/>
       <c r="B538" s="14"/>
       <c r="C538" s="14"/>
@@ -25296,7 +25296,7 @@
       <c r="AI538" s="14"/>
       <c r="AJ538" s="14"/>
     </row>
-    <row r="539">
+    <row r="539" hidden="1">
       <c r="A539" s="14"/>
       <c r="B539" s="14"/>
       <c r="C539" s="14"/>
@@ -25334,7 +25334,7 @@
       <c r="AI539" s="14"/>
       <c r="AJ539" s="14"/>
     </row>
-    <row r="540">
+    <row r="540" hidden="1">
       <c r="A540" s="14"/>
       <c r="B540" s="14"/>
       <c r="C540" s="14"/>
@@ -25372,7 +25372,7 @@
       <c r="AI540" s="14"/>
       <c r="AJ540" s="14"/>
     </row>
-    <row r="541">
+    <row r="541" hidden="1">
       <c r="A541" s="14"/>
       <c r="B541" s="14"/>
       <c r="C541" s="14"/>
@@ -25410,7 +25410,7 @@
       <c r="AI541" s="14"/>
       <c r="AJ541" s="14"/>
     </row>
-    <row r="542">
+    <row r="542" hidden="1">
       <c r="A542" s="14"/>
       <c r="B542" s="14"/>
       <c r="C542" s="14"/>
@@ -25448,7 +25448,7 @@
       <c r="AI542" s="14"/>
       <c r="AJ542" s="14"/>
     </row>
-    <row r="543">
+    <row r="543" hidden="1">
       <c r="A543" s="14"/>
       <c r="B543" s="14"/>
       <c r="C543" s="14"/>
@@ -25486,7 +25486,7 @@
       <c r="AI543" s="14"/>
       <c r="AJ543" s="14"/>
     </row>
-    <row r="544">
+    <row r="544" hidden="1">
       <c r="A544" s="14"/>
       <c r="B544" s="14"/>
       <c r="C544" s="14"/>
@@ -25524,7 +25524,7 @@
       <c r="AI544" s="14"/>
       <c r="AJ544" s="14"/>
     </row>
-    <row r="545">
+    <row r="545" hidden="1">
       <c r="A545" s="14"/>
       <c r="B545" s="14"/>
       <c r="C545" s="14"/>
@@ -25562,7 +25562,7 @@
       <c r="AI545" s="14"/>
       <c r="AJ545" s="14"/>
     </row>
-    <row r="546">
+    <row r="546" hidden="1">
       <c r="A546" s="14"/>
       <c r="B546" s="14"/>
       <c r="C546" s="14"/>
@@ -25600,7 +25600,7 @@
       <c r="AI546" s="14"/>
       <c r="AJ546" s="14"/>
     </row>
-    <row r="547">
+    <row r="547" hidden="1">
       <c r="A547" s="14"/>
       <c r="B547" s="14"/>
       <c r="C547" s="14"/>
@@ -25638,7 +25638,7 @@
       <c r="AI547" s="14"/>
       <c r="AJ547" s="14"/>
     </row>
-    <row r="548">
+    <row r="548" hidden="1">
       <c r="A548" s="14"/>
       <c r="B548" s="14"/>
       <c r="C548" s="14"/>
@@ -25676,7 +25676,7 @@
       <c r="AI548" s="14"/>
       <c r="AJ548" s="14"/>
     </row>
-    <row r="549">
+    <row r="549" hidden="1">
       <c r="A549" s="14"/>
       <c r="B549" s="14"/>
       <c r="C549" s="14"/>
@@ -25714,7 +25714,7 @@
       <c r="AI549" s="14"/>
       <c r="AJ549" s="14"/>
     </row>
-    <row r="550">
+    <row r="550" hidden="1">
       <c r="A550" s="14"/>
       <c r="B550" s="14"/>
       <c r="C550" s="14"/>
@@ -25752,7 +25752,7 @@
       <c r="AI550" s="14"/>
       <c r="AJ550" s="14"/>
     </row>
-    <row r="551">
+    <row r="551" hidden="1">
       <c r="A551" s="14"/>
       <c r="B551" s="14"/>
       <c r="C551" s="14"/>
@@ -25790,7 +25790,7 @@
       <c r="AI551" s="14"/>
       <c r="AJ551" s="14"/>
     </row>
-    <row r="552">
+    <row r="552" hidden="1">
       <c r="A552" s="14"/>
       <c r="B552" s="14"/>
       <c r="C552" s="14"/>
@@ -25828,7 +25828,7 @@
       <c r="AI552" s="14"/>
       <c r="AJ552" s="14"/>
     </row>
-    <row r="553">
+    <row r="553" hidden="1">
       <c r="A553" s="14"/>
       <c r="B553" s="14"/>
       <c r="C553" s="14"/>
@@ -25866,7 +25866,7 @@
       <c r="AI553" s="14"/>
       <c r="AJ553" s="14"/>
     </row>
-    <row r="554">
+    <row r="554" hidden="1">
       <c r="A554" s="14"/>
       <c r="B554" s="14"/>
       <c r="C554" s="14"/>
@@ -25904,7 +25904,7 @@
       <c r="AI554" s="14"/>
       <c r="AJ554" s="14"/>
     </row>
-    <row r="555">
+    <row r="555" hidden="1">
       <c r="A555" s="14"/>
       <c r="B555" s="14"/>
       <c r="C555" s="14"/>
@@ -25942,7 +25942,7 @@
       <c r="AI555" s="14"/>
       <c r="AJ555" s="14"/>
     </row>
-    <row r="556">
+    <row r="556" hidden="1">
       <c r="A556" s="14"/>
       <c r="B556" s="14"/>
       <c r="C556" s="14"/>
@@ -25980,7 +25980,7 @@
       <c r="AI556" s="14"/>
       <c r="AJ556" s="14"/>
     </row>
-    <row r="557">
+    <row r="557" hidden="1">
       <c r="A557" s="14"/>
       <c r="B557" s="14"/>
       <c r="C557" s="14"/>
@@ -26018,7 +26018,7 @@
       <c r="AI557" s="14"/>
       <c r="AJ557" s="14"/>
     </row>
-    <row r="558">
+    <row r="558" hidden="1">
       <c r="A558" s="14"/>
       <c r="B558" s="14"/>
       <c r="C558" s="14"/>
@@ -26056,7 +26056,7 @@
       <c r="AI558" s="14"/>
       <c r="AJ558" s="14"/>
     </row>
-    <row r="559">
+    <row r="559" hidden="1">
       <c r="A559" s="14"/>
       <c r="B559" s="14"/>
       <c r="C559" s="14"/>
@@ -26094,7 +26094,7 @@
       <c r="AI559" s="14"/>
       <c r="AJ559" s="14"/>
     </row>
-    <row r="560">
+    <row r="560" hidden="1">
       <c r="A560" s="14"/>
       <c r="B560" s="14"/>
       <c r="C560" s="14"/>
@@ -26132,7 +26132,7 @@
       <c r="AI560" s="14"/>
       <c r="AJ560" s="14"/>
     </row>
-    <row r="561">
+    <row r="561" hidden="1">
       <c r="A561" s="14"/>
       <c r="B561" s="14"/>
       <c r="C561" s="14"/>
@@ -26170,7 +26170,7 @@
       <c r="AI561" s="14"/>
       <c r="AJ561" s="14"/>
     </row>
-    <row r="562">
+    <row r="562" hidden="1">
       <c r="A562" s="14"/>
       <c r="B562" s="14"/>
       <c r="C562" s="14"/>
@@ -26208,7 +26208,7 @@
       <c r="AI562" s="14"/>
       <c r="AJ562" s="14"/>
     </row>
-    <row r="563">
+    <row r="563" hidden="1">
       <c r="A563" s="14"/>
       <c r="B563" s="14"/>
       <c r="C563" s="14"/>
@@ -26246,7 +26246,7 @@
       <c r="AI563" s="14"/>
       <c r="AJ563" s="14"/>
     </row>
-    <row r="564">
+    <row r="564" hidden="1">
       <c r="A564" s="14"/>
       <c r="B564" s="14"/>
       <c r="C564" s="14"/>
@@ -26284,7 +26284,7 @@
       <c r="AI564" s="14"/>
       <c r="AJ564" s="14"/>
     </row>
-    <row r="565">
+    <row r="565" hidden="1">
       <c r="A565" s="14"/>
       <c r="B565" s="14"/>
       <c r="C565" s="14"/>
@@ -26322,7 +26322,7 @@
       <c r="AI565" s="14"/>
       <c r="AJ565" s="14"/>
     </row>
-    <row r="566">
+    <row r="566" hidden="1">
       <c r="A566" s="14"/>
       <c r="B566" s="14"/>
       <c r="C566" s="14"/>
@@ -26360,7 +26360,7 @@
       <c r="AI566" s="14"/>
       <c r="AJ566" s="14"/>
     </row>
-    <row r="567">
+    <row r="567" hidden="1">
       <c r="A567" s="14"/>
       <c r="B567" s="14"/>
       <c r="C567" s="14"/>
@@ -26398,7 +26398,7 @@
       <c r="AI567" s="14"/>
       <c r="AJ567" s="14"/>
     </row>
-    <row r="568">
+    <row r="568" hidden="1">
       <c r="A568" s="14"/>
       <c r="B568" s="14"/>
       <c r="C568" s="14"/>
@@ -26436,7 +26436,7 @@
       <c r="AI568" s="14"/>
       <c r="AJ568" s="14"/>
     </row>
-    <row r="569">
+    <row r="569" hidden="1">
       <c r="A569" s="14"/>
       <c r="B569" s="14"/>
       <c r="C569" s="14"/>
@@ -26474,7 +26474,7 @@
       <c r="AI569" s="14"/>
       <c r="AJ569" s="14"/>
     </row>
-    <row r="570">
+    <row r="570" hidden="1">
       <c r="A570" s="14"/>
       <c r="B570" s="14"/>
       <c r="C570" s="14"/>
@@ -26512,7 +26512,7 @@
       <c r="AI570" s="14"/>
       <c r="AJ570" s="14"/>
     </row>
-    <row r="571">
+    <row r="571" hidden="1">
       <c r="A571" s="14"/>
       <c r="B571" s="14"/>
       <c r="C571" s="14"/>
@@ -26550,7 +26550,7 @@
       <c r="AI571" s="14"/>
       <c r="AJ571" s="14"/>
     </row>
-    <row r="572">
+    <row r="572" hidden="1">
       <c r="A572" s="14"/>
       <c r="B572" s="14"/>
       <c r="C572" s="14"/>
@@ -26588,7 +26588,7 @@
       <c r="AI572" s="14"/>
       <c r="AJ572" s="14"/>
     </row>
-    <row r="573">
+    <row r="573" hidden="1">
       <c r="A573" s="14"/>
       <c r="B573" s="14"/>
       <c r="C573" s="14"/>
@@ -26626,7 +26626,7 @@
       <c r="AI573" s="14"/>
       <c r="AJ573" s="14"/>
     </row>
-    <row r="574">
+    <row r="574" hidden="1">
       <c r="A574" s="14"/>
       <c r="B574" s="14"/>
       <c r="C574" s="14"/>
@@ -26664,7 +26664,7 @@
       <c r="AI574" s="14"/>
       <c r="AJ574" s="14"/>
     </row>
-    <row r="575">
+    <row r="575" hidden="1">
       <c r="A575" s="14"/>
       <c r="B575" s="14"/>
       <c r="C575" s="14"/>
@@ -26702,7 +26702,7 @@
       <c r="AI575" s="14"/>
       <c r="AJ575" s="14"/>
     </row>
-    <row r="576">
+    <row r="576" hidden="1">
       <c r="A576" s="14"/>
       <c r="B576" s="14"/>
       <c r="C576" s="14"/>
@@ -26740,7 +26740,7 @@
       <c r="AI576" s="14"/>
       <c r="AJ576" s="14"/>
     </row>
-    <row r="577">
+    <row r="577" hidden="1">
       <c r="A577" s="14"/>
       <c r="B577" s="14"/>
       <c r="C577" s="14"/>
@@ -26778,7 +26778,7 @@
       <c r="AI577" s="14"/>
       <c r="AJ577" s="14"/>
     </row>
-    <row r="578">
+    <row r="578" hidden="1">
       <c r="A578" s="14"/>
       <c r="B578" s="14"/>
       <c r="C578" s="14"/>
@@ -26816,7 +26816,7 @@
       <c r="AI578" s="14"/>
       <c r="AJ578" s="14"/>
     </row>
-    <row r="579">
+    <row r="579" hidden="1">
       <c r="A579" s="14"/>
       <c r="B579" s="14"/>
       <c r="C579" s="14"/>
@@ -26854,7 +26854,7 @@
       <c r="AI579" s="14"/>
       <c r="AJ579" s="14"/>
     </row>
-    <row r="580">
+    <row r="580" hidden="1">
       <c r="A580" s="14"/>
       <c r="B580" s="14"/>
       <c r="C580" s="14"/>
@@ -26892,7 +26892,7 @@
       <c r="AI580" s="14"/>
       <c r="AJ580" s="14"/>
     </row>
-    <row r="581">
+    <row r="581" hidden="1">
       <c r="A581" s="14"/>
       <c r="B581" s="14"/>
       <c r="C581" s="14"/>
@@ -26930,7 +26930,7 @@
       <c r="AI581" s="14"/>
       <c r="AJ581" s="14"/>
     </row>
-    <row r="582">
+    <row r="582" hidden="1">
       <c r="A582" s="14"/>
       <c r="B582" s="14"/>
       <c r="C582" s="14"/>
@@ -26968,7 +26968,7 @@
       <c r="AI582" s="14"/>
       <c r="AJ582" s="14"/>
     </row>
-    <row r="583">
+    <row r="583" hidden="1">
       <c r="A583" s="14"/>
       <c r="B583" s="14"/>
       <c r="C583" s="14"/>
@@ -27006,7 +27006,7 @@
       <c r="AI583" s="14"/>
       <c r="AJ583" s="14"/>
     </row>
-    <row r="584">
+    <row r="584" hidden="1">
       <c r="A584" s="14"/>
       <c r="B584" s="14"/>
       <c r="C584" s="14"/>
@@ -27044,7 +27044,7 @@
       <c r="AI584" s="14"/>
       <c r="AJ584" s="14"/>
     </row>
-    <row r="585">
+    <row r="585" hidden="1">
       <c r="A585" s="14"/>
       <c r="B585" s="14"/>
       <c r="C585" s="14"/>
@@ -27082,7 +27082,7 @@
       <c r="AI585" s="14"/>
       <c r="AJ585" s="14"/>
     </row>
-    <row r="586">
+    <row r="586" hidden="1">
       <c r="A586" s="14"/>
       <c r="B586" s="14"/>
       <c r="C586" s="14"/>
@@ -27120,7 +27120,7 @@
       <c r="AI586" s="14"/>
       <c r="AJ586" s="14"/>
     </row>
-    <row r="587">
+    <row r="587" hidden="1">
       <c r="A587" s="14"/>
       <c r="B587" s="14"/>
       <c r="C587" s="14"/>
@@ -27158,7 +27158,7 @@
       <c r="AI587" s="14"/>
       <c r="AJ587" s="14"/>
     </row>
-    <row r="588">
+    <row r="588" hidden="1">
       <c r="A588" s="14"/>
       <c r="B588" s="14"/>
       <c r="C588" s="14"/>
@@ -27196,7 +27196,7 @@
       <c r="AI588" s="14"/>
       <c r="AJ588" s="14"/>
     </row>
-    <row r="589">
+    <row r="589" hidden="1">
       <c r="A589" s="14"/>
       <c r="B589" s="14"/>
       <c r="C589" s="14"/>
@@ -27234,7 +27234,7 @@
       <c r="AI589" s="14"/>
       <c r="AJ589" s="14"/>
     </row>
-    <row r="590">
+    <row r="590" hidden="1">
       <c r="A590" s="14"/>
       <c r="B590" s="14"/>
       <c r="C590" s="14"/>
@@ -27272,7 +27272,7 @@
       <c r="AI590" s="14"/>
       <c r="AJ590" s="14"/>
     </row>
-    <row r="591">
+    <row r="591" hidden="1">
       <c r="A591" s="14"/>
       <c r="B591" s="14"/>
       <c r="C591" s="14"/>
@@ -27310,7 +27310,7 @@
       <c r="AI591" s="14"/>
       <c r="AJ591" s="14"/>
     </row>
-    <row r="592">
+    <row r="592" hidden="1">
       <c r="A592" s="14"/>
       <c r="B592" s="14"/>
       <c r="C592" s="14"/>
@@ -27348,7 +27348,7 @@
       <c r="AI592" s="14"/>
       <c r="AJ592" s="14"/>
     </row>
-    <row r="593">
+    <row r="593" hidden="1">
       <c r="A593" s="14"/>
       <c r="B593" s="14"/>
       <c r="C593" s="14"/>
@@ -27386,7 +27386,7 @@
       <c r="AI593" s="14"/>
       <c r="AJ593" s="14"/>
     </row>
-    <row r="594">
+    <row r="594" hidden="1">
       <c r="A594" s="14"/>
       <c r="B594" s="14"/>
       <c r="C594" s="14"/>
@@ -27424,7 +27424,7 @@
       <c r="AI594" s="14"/>
       <c r="AJ594" s="14"/>
     </row>
-    <row r="595">
+    <row r="595" hidden="1">
       <c r="A595" s="14"/>
       <c r="B595" s="14"/>
       <c r="C595" s="14"/>
@@ -27462,7 +27462,7 @@
       <c r="AI595" s="14"/>
       <c r="AJ595" s="14"/>
     </row>
-    <row r="596">
+    <row r="596" hidden="1">
       <c r="A596" s="14"/>
       <c r="B596" s="14"/>
       <c r="C596" s="14"/>
@@ -27500,7 +27500,7 @@
       <c r="AI596" s="14"/>
       <c r="AJ596" s="14"/>
     </row>
-    <row r="597">
+    <row r="597" hidden="1">
       <c r="A597" s="14"/>
       <c r="B597" s="14"/>
       <c r="C597" s="14"/>
@@ -27538,7 +27538,7 @@
       <c r="AI597" s="14"/>
       <c r="AJ597" s="14"/>
     </row>
-    <row r="598">
+    <row r="598" hidden="1">
       <c r="A598" s="14"/>
       <c r="B598" s="14"/>
       <c r="C598" s="14"/>
@@ -27576,7 +27576,7 @@
       <c r="AI598" s="14"/>
       <c r="AJ598" s="14"/>
     </row>
-    <row r="599">
+    <row r="599" hidden="1">
       <c r="A599" s="14"/>
       <c r="B599" s="14"/>
       <c r="C599" s="14"/>
@@ -27614,7 +27614,7 @@
       <c r="AI599" s="14"/>
       <c r="AJ599" s="14"/>
     </row>
-    <row r="600">
+    <row r="600" hidden="1">
       <c r="A600" s="14"/>
       <c r="B600" s="14"/>
       <c r="C600" s="14"/>
@@ -27652,7 +27652,7 @@
       <c r="AI600" s="14"/>
       <c r="AJ600" s="14"/>
     </row>
-    <row r="601">
+    <row r="601" hidden="1">
       <c r="A601" s="14"/>
       <c r="B601" s="14"/>
       <c r="C601" s="14"/>
@@ -27690,7 +27690,7 @@
       <c r="AI601" s="14"/>
       <c r="AJ601" s="14"/>
     </row>
-    <row r="602">
+    <row r="602" hidden="1">
       <c r="A602" s="14"/>
       <c r="B602" s="14"/>
       <c r="C602" s="14"/>
@@ -27728,7 +27728,7 @@
       <c r="AI602" s="14"/>
       <c r="AJ602" s="14"/>
     </row>
-    <row r="603">
+    <row r="603" hidden="1">
       <c r="A603" s="14"/>
       <c r="B603" s="14"/>
       <c r="C603" s="14"/>
@@ -27766,7 +27766,7 @@
       <c r="AI603" s="14"/>
       <c r="AJ603" s="14"/>
     </row>
-    <row r="604">
+    <row r="604" hidden="1">
       <c r="A604" s="14"/>
       <c r="B604" s="14"/>
       <c r="C604" s="14"/>
@@ -27804,7 +27804,7 @@
       <c r="AI604" s="14"/>
       <c r="AJ604" s="14"/>
     </row>
-    <row r="605">
+    <row r="605" hidden="1">
       <c r="A605" s="14"/>
       <c r="B605" s="14"/>
       <c r="C605" s="14"/>
@@ -27842,7 +27842,7 @@
       <c r="AI605" s="14"/>
       <c r="AJ605" s="14"/>
     </row>
-    <row r="606">
+    <row r="606" hidden="1">
       <c r="A606" s="14"/>
       <c r="B606" s="14"/>
       <c r="C606" s="14"/>
@@ -27880,7 +27880,7 @@
       <c r="AI606" s="14"/>
       <c r="AJ606" s="14"/>
     </row>
-    <row r="607">
+    <row r="607" hidden="1">
       <c r="A607" s="14"/>
       <c r="B607" s="14"/>
       <c r="C607" s="14"/>
@@ -27918,7 +27918,7 @@
       <c r="AI607" s="14"/>
       <c r="AJ607" s="14"/>
     </row>
-    <row r="608">
+    <row r="608" hidden="1">
       <c r="A608" s="14"/>
       <c r="B608" s="14"/>
       <c r="C608" s="14"/>
@@ -27956,7 +27956,7 @@
       <c r="AI608" s="14"/>
       <c r="AJ608" s="14"/>
     </row>
-    <row r="609">
+    <row r="609" hidden="1">
       <c r="A609" s="14"/>
       <c r="B609" s="14"/>
       <c r="C609" s="14"/>
@@ -27994,7 +27994,7 @@
       <c r="AI609" s="14"/>
       <c r="AJ609" s="14"/>
     </row>
-    <row r="610">
+    <row r="610" hidden="1">
       <c r="A610" s="14"/>
       <c r="B610" s="14"/>
       <c r="C610" s="14"/>
@@ -28032,7 +28032,7 @@
       <c r="AI610" s="14"/>
       <c r="AJ610" s="14"/>
     </row>
-    <row r="611">
+    <row r="611" hidden="1">
       <c r="A611" s="14"/>
       <c r="B611" s="14"/>
       <c r="C611" s="14"/>
@@ -28070,7 +28070,7 @@
       <c r="AI611" s="14"/>
       <c r="AJ611" s="14"/>
     </row>
-    <row r="612">
+    <row r="612" hidden="1">
       <c r="A612" s="14"/>
       <c r="B612" s="14"/>
       <c r="C612" s="14"/>
@@ -28108,7 +28108,7 @@
       <c r="AI612" s="14"/>
       <c r="AJ612" s="14"/>
     </row>
-    <row r="613">
+    <row r="613" hidden="1">
       <c r="A613" s="14"/>
       <c r="B613" s="14"/>
       <c r="C613" s="14"/>
@@ -28146,7 +28146,7 @@
       <c r="AI613" s="14"/>
       <c r="AJ613" s="14"/>
     </row>
-    <row r="614">
+    <row r="614" hidden="1">
       <c r="A614" s="14"/>
       <c r="B614" s="14"/>
       <c r="C614" s="14"/>
@@ -28184,7 +28184,7 @@
       <c r="AI614" s="14"/>
       <c r="AJ614" s="14"/>
     </row>
-    <row r="615">
+    <row r="615" hidden="1">
       <c r="A615" s="14"/>
       <c r="B615" s="14"/>
       <c r="C615" s="14"/>
@@ -28222,7 +28222,7 @@
       <c r="AI615" s="14"/>
       <c r="AJ615" s="14"/>
     </row>
-    <row r="616">
+    <row r="616" hidden="1">
       <c r="A616" s="14"/>
       <c r="B616" s="14"/>
       <c r="C616" s="14"/>
@@ -28260,7 +28260,7 @@
       <c r="AI616" s="14"/>
       <c r="AJ616" s="14"/>
     </row>
-    <row r="617">
+    <row r="617" hidden="1">
       <c r="A617" s="14"/>
       <c r="B617" s="14"/>
       <c r="C617" s="14"/>
@@ -28298,7 +28298,7 @@
       <c r="AI617" s="14"/>
       <c r="AJ617" s="14"/>
     </row>
-    <row r="618">
+    <row r="618" hidden="1">
       <c r="A618" s="14"/>
       <c r="B618" s="14"/>
       <c r="C618" s="14"/>
@@ -28336,7 +28336,7 @@
       <c r="AI618" s="14"/>
       <c r="AJ618" s="14"/>
     </row>
-    <row r="619">
+    <row r="619" hidden="1">
       <c r="A619" s="14"/>
       <c r="B619" s="14"/>
       <c r="C619" s="14"/>
@@ -28374,7 +28374,7 @@
       <c r="AI619" s="14"/>
       <c r="AJ619" s="14"/>
     </row>
-    <row r="620">
+    <row r="620" hidden="1">
       <c r="A620" s="14"/>
       <c r="B620" s="14"/>
       <c r="C620" s="14"/>
@@ -28412,7 +28412,7 @@
       <c r="AI620" s="14"/>
       <c r="AJ620" s="14"/>
     </row>
-    <row r="621">
+    <row r="621" hidden="1">
       <c r="A621" s="14"/>
       <c r="B621" s="14"/>
       <c r="C621" s="14"/>
@@ -28450,7 +28450,7 @@
       <c r="AI621" s="14"/>
       <c r="AJ621" s="14"/>
     </row>
-    <row r="622">
+    <row r="622" hidden="1">
       <c r="A622" s="14"/>
       <c r="B622" s="14"/>
       <c r="C622" s="14"/>
@@ -28488,7 +28488,7 @@
       <c r="AI622" s="14"/>
       <c r="AJ622" s="14"/>
     </row>
-    <row r="623">
+    <row r="623" hidden="1">
       <c r="A623" s="14"/>
       <c r="B623" s="14"/>
       <c r="C623" s="14"/>
@@ -28526,7 +28526,7 @@
       <c r="AI623" s="14"/>
       <c r="AJ623" s="14"/>
     </row>
-    <row r="624">
+    <row r="624" hidden="1">
       <c r="A624" s="14"/>
       <c r="B624" s="14"/>
       <c r="C624" s="14"/>
@@ -28564,7 +28564,7 @@
       <c r="AI624" s="14"/>
       <c r="AJ624" s="14"/>
     </row>
-    <row r="625">
+    <row r="625" hidden="1">
       <c r="A625" s="14"/>
       <c r="B625" s="14"/>
       <c r="C625" s="14"/>
@@ -28602,7 +28602,7 @@
       <c r="AI625" s="14"/>
       <c r="AJ625" s="14"/>
     </row>
-    <row r="626">
+    <row r="626" hidden="1">
       <c r="A626" s="14"/>
       <c r="B626" s="14"/>
       <c r="C626" s="14"/>
@@ -28640,7 +28640,7 @@
       <c r="AI626" s="14"/>
       <c r="AJ626" s="14"/>
     </row>
-    <row r="627">
+    <row r="627" hidden="1">
       <c r="A627" s="14"/>
       <c r="B627" s="14"/>
       <c r="C627" s="14"/>
@@ -28678,7 +28678,7 @@
       <c r="AI627" s="14"/>
       <c r="AJ627" s="14"/>
     </row>
-    <row r="628">
+    <row r="628" hidden="1">
       <c r="A628" s="14"/>
       <c r="B628" s="14"/>
       <c r="C628" s="14"/>
@@ -28716,7 +28716,7 @@
       <c r="AI628" s="14"/>
       <c r="AJ628" s="14"/>
     </row>
-    <row r="629">
+    <row r="629" hidden="1">
       <c r="A629" s="14"/>
       <c r="B629" s="14"/>
       <c r="C629" s="14"/>
@@ -28754,7 +28754,7 @@
       <c r="AI629" s="14"/>
       <c r="AJ629" s="14"/>
     </row>
-    <row r="630">
+    <row r="630" hidden="1">
       <c r="A630" s="14"/>
       <c r="B630" s="14"/>
       <c r="C630" s="14"/>
@@ -28792,7 +28792,7 @@
       <c r="AI630" s="14"/>
       <c r="AJ630" s="14"/>
     </row>
-    <row r="631">
+    <row r="631" hidden="1">
       <c r="A631" s="14"/>
       <c r="B631" s="14"/>
       <c r="C631" s="14"/>
@@ -28830,7 +28830,7 @@
       <c r="AI631" s="14"/>
       <c r="AJ631" s="14"/>
     </row>
-    <row r="632">
+    <row r="632" hidden="1">
       <c r="A632" s="14"/>
       <c r="B632" s="14"/>
       <c r="C632" s="14"/>
@@ -28868,7 +28868,7 @@
       <c r="AI632" s="14"/>
       <c r="AJ632" s="14"/>
     </row>
-    <row r="633">
+    <row r="633" hidden="1">
       <c r="A633" s="14"/>
       <c r="B633" s="14"/>
       <c r="C633" s="14"/>
@@ -28906,7 +28906,7 @@
       <c r="AI633" s="14"/>
       <c r="AJ633" s="14"/>
     </row>
-    <row r="634">
+    <row r="634" hidden="1">
       <c r="A634" s="14"/>
       <c r="B634" s="14"/>
       <c r="C634" s="14"/>
@@ -28944,7 +28944,7 @@
       <c r="AI634" s="14"/>
       <c r="AJ634" s="14"/>
     </row>
-    <row r="635">
+    <row r="635" hidden="1">
       <c r="A635" s="14"/>
       <c r="B635" s="14"/>
       <c r="C635" s="14"/>
@@ -28982,7 +28982,7 @@
       <c r="AI635" s="14"/>
       <c r="AJ635" s="14"/>
     </row>
-    <row r="636">
+    <row r="636" hidden="1">
       <c r="A636" s="14"/>
       <c r="B636" s="14"/>
       <c r="C636" s="14"/>
@@ -29020,7 +29020,7 @@
       <c r="AI636" s="14"/>
       <c r="AJ636" s="14"/>
     </row>
-    <row r="637">
+    <row r="637" hidden="1">
       <c r="A637" s="14"/>
       <c r="B637" s="14"/>
       <c r="C637" s="14"/>
@@ -29058,7 +29058,7 @@
       <c r="AI637" s="14"/>
       <c r="AJ637" s="14"/>
     </row>
-    <row r="638">
+    <row r="638" hidden="1">
       <c r="A638" s="14"/>
       <c r="B638" s="14"/>
       <c r="C638" s="14"/>
@@ -29096,7 +29096,7 @@
       <c r="AI638" s="14"/>
       <c r="AJ638" s="14"/>
     </row>
-    <row r="639">
+    <row r="639" hidden="1">
       <c r="A639" s="14"/>
       <c r="B639" s="14"/>
       <c r="C639" s="14"/>
@@ -29134,7 +29134,7 @@
       <c r="AI639" s="14"/>
       <c r="AJ639" s="14"/>
     </row>
-    <row r="640">
+    <row r="640" hidden="1">
       <c r="A640" s="14"/>
       <c r="B640" s="14"/>
       <c r="C640" s="14"/>
@@ -29172,7 +29172,7 @@
       <c r="AI640" s="14"/>
       <c r="AJ640" s="14"/>
     </row>
-    <row r="641">
+    <row r="641" hidden="1">
       <c r="A641" s="14"/>
       <c r="B641" s="14"/>
       <c r="C641" s="14"/>
@@ -29210,7 +29210,7 @@
       <c r="AI641" s="14"/>
       <c r="AJ641" s="14"/>
     </row>
-    <row r="642">
+    <row r="642" hidden="1">
       <c r="A642" s="14"/>
       <c r="B642" s="14"/>
       <c r="C642" s="14"/>
@@ -29248,7 +29248,7 @@
       <c r="AI642" s="14"/>
       <c r="AJ642" s="14"/>
     </row>
-    <row r="643">
+    <row r="643" hidden="1">
       <c r="A643" s="14"/>
       <c r="B643" s="14"/>
       <c r="C643" s="14"/>
@@ -29286,7 +29286,7 @@
       <c r="AI643" s="14"/>
       <c r="AJ643" s="14"/>
     </row>
-    <row r="644">
+    <row r="644" hidden="1">
       <c r="A644" s="14"/>
       <c r="B644" s="14"/>
       <c r="C644" s="14"/>
@@ -29324,7 +29324,7 @@
       <c r="AI644" s="14"/>
       <c r="AJ644" s="14"/>
     </row>
-    <row r="645">
+    <row r="645" hidden="1">
       <c r="A645" s="14"/>
       <c r="B645" s="14"/>
       <c r="C645" s="14"/>
@@ -29362,7 +29362,7 @@
       <c r="AI645" s="14"/>
       <c r="AJ645" s="14"/>
     </row>
-    <row r="646">
+    <row r="646" hidden="1">
       <c r="A646" s="14"/>
       <c r="B646" s="14"/>
       <c r="C646" s="14"/>
@@ -29400,7 +29400,7 @@
       <c r="AI646" s="14"/>
       <c r="AJ646" s="14"/>
     </row>
-    <row r="647">
+    <row r="647" hidden="1">
       <c r="A647" s="14"/>
       <c r="B647" s="14"/>
       <c r="C647" s="14"/>
@@ -29438,7 +29438,7 @@
       <c r="AI647" s="14"/>
       <c r="AJ647" s="14"/>
     </row>
-    <row r="648">
+    <row r="648" hidden="1">
       <c r="A648" s="14"/>
       <c r="B648" s="14"/>
       <c r="C648" s="14"/>
@@ -29476,7 +29476,7 @@
       <c r="AI648" s="14"/>
       <c r="AJ648" s="14"/>
     </row>
-    <row r="649">
+    <row r="649" hidden="1">
       <c r="A649" s="14"/>
       <c r="B649" s="14"/>
       <c r="C649" s="14"/>
@@ -29514,7 +29514,7 @@
       <c r="AI649" s="14"/>
       <c r="AJ649" s="14"/>
     </row>
-    <row r="650">
+    <row r="650" hidden="1">
       <c r="A650" s="14"/>
       <c r="B650" s="14"/>
       <c r="C650" s="14"/>
@@ -29552,7 +29552,7 @@
       <c r="AI650" s="14"/>
       <c r="AJ650" s="14"/>
     </row>
-    <row r="651">
+    <row r="651" hidden="1">
       <c r="A651" s="14"/>
       <c r="B651" s="14"/>
       <c r="C651" s="14"/>
@@ -29590,7 +29590,7 @@
       <c r="AI651" s="14"/>
       <c r="AJ651" s="14"/>
     </row>
-    <row r="652">
+    <row r="652" hidden="1">
       <c r="A652" s="14"/>
       <c r="B652" s="14"/>
       <c r="C652" s="14"/>
@@ -29628,7 +29628,7 @@
       <c r="AI652" s="14"/>
       <c r="AJ652" s="14"/>
     </row>
-    <row r="653">
+    <row r="653" hidden="1">
       <c r="A653" s="14"/>
       <c r="B653" s="14"/>
       <c r="C653" s="14"/>
@@ -29666,7 +29666,7 @@
       <c r="AI653" s="14"/>
       <c r="AJ653" s="14"/>
     </row>
-    <row r="654">
+    <row r="654" hidden="1">
       <c r="A654" s="14"/>
       <c r="B654" s="14"/>
       <c r="C654" s="14"/>
@@ -29704,7 +29704,7 @@
       <c r="AI654" s="14"/>
       <c r="AJ654" s="14"/>
     </row>
-    <row r="655">
+    <row r="655" hidden="1">
       <c r="A655" s="14"/>
       <c r="B655" s="14"/>
       <c r="C655" s="14"/>
@@ -29742,7 +29742,7 @@
       <c r="AI655" s="14"/>
       <c r="AJ655" s="14"/>
     </row>
-    <row r="656">
+    <row r="656" hidden="1">
       <c r="A656" s="14"/>
       <c r="B656" s="14"/>
       <c r="C656" s="14"/>
@@ -29780,7 +29780,7 @@
       <c r="AI656" s="14"/>
       <c r="AJ656" s="14"/>
     </row>
-    <row r="657">
+    <row r="657" hidden="1">
       <c r="A657" s="14"/>
       <c r="B657" s="14"/>
       <c r="C657" s="14"/>
@@ -29818,7 +29818,7 @@
       <c r="AI657" s="14"/>
       <c r="AJ657" s="14"/>
     </row>
-    <row r="658">
+    <row r="658" hidden="1">
       <c r="A658" s="14"/>
       <c r="B658" s="14"/>
       <c r="C658" s="14"/>
@@ -29856,7 +29856,7 @@
       <c r="AI658" s="14"/>
       <c r="AJ658" s="14"/>
     </row>
-    <row r="659">
+    <row r="659" hidden="1">
       <c r="A659" s="14"/>
       <c r="B659" s="14"/>
       <c r="C659" s="14"/>
@@ -29894,7 +29894,7 @@
       <c r="AI659" s="14"/>
       <c r="AJ659" s="14"/>
     </row>
-    <row r="660">
+    <row r="660" hidden="1">
       <c r="A660" s="14"/>
       <c r="B660" s="14"/>
       <c r="C660" s="14"/>
@@ -29932,7 +29932,7 @@
       <c r="AI660" s="14"/>
       <c r="AJ660" s="14"/>
     </row>
-    <row r="661">
+    <row r="661" hidden="1">
       <c r="A661" s="14"/>
       <c r="B661" s="14"/>
       <c r="C661" s="14"/>
@@ -29970,7 +29970,7 @@
       <c r="AI661" s="14"/>
       <c r="AJ661" s="14"/>
     </row>
-    <row r="662">
+    <row r="662" hidden="1">
       <c r="A662" s="14"/>
       <c r="B662" s="14"/>
       <c r="C662" s="14"/>
@@ -30008,7 +30008,7 @@
       <c r="AI662" s="14"/>
       <c r="AJ662" s="14"/>
     </row>
-    <row r="663">
+    <row r="663" hidden="1">
       <c r="A663" s="14"/>
       <c r="B663" s="14"/>
       <c r="C663" s="14"/>
@@ -30046,7 +30046,7 @@
       <c r="AI663" s="14"/>
       <c r="AJ663" s="14"/>
     </row>
-    <row r="664">
+    <row r="664" hidden="1">
       <c r="A664" s="14"/>
       <c r="B664" s="14"/>
       <c r="C664" s="14"/>
@@ -30084,7 +30084,7 @@
       <c r="AI664" s="14"/>
       <c r="AJ664" s="14"/>
     </row>
-    <row r="665">
+    <row r="665" hidden="1">
       <c r="A665" s="14"/>
       <c r="B665" s="14"/>
       <c r="C665" s="14"/>
@@ -30122,7 +30122,7 @@
       <c r="AI665" s="14"/>
       <c r="AJ665" s="14"/>
     </row>
-    <row r="666">
+    <row r="666" hidden="1">
       <c r="A666" s="14"/>
       <c r="B666" s="14"/>
       <c r="C666" s="14"/>
@@ -30160,7 +30160,7 @@
       <c r="AI666" s="14"/>
       <c r="AJ666" s="14"/>
     </row>
-    <row r="667">
+    <row r="667" hidden="1">
       <c r="A667" s="14"/>
       <c r="B667" s="14"/>
       <c r="C667" s="14"/>
@@ -30198,7 +30198,7 @@
       <c r="AI667" s="14"/>
       <c r="AJ667" s="14"/>
     </row>
-    <row r="668">
+    <row r="668" hidden="1">
       <c r="A668" s="14"/>
       <c r="B668" s="14"/>
       <c r="C668" s="14"/>
@@ -30236,7 +30236,7 @@
       <c r="AI668" s="14"/>
       <c r="AJ668" s="14"/>
     </row>
-    <row r="669">
+    <row r="669" hidden="1">
       <c r="A669" s="14"/>
       <c r="B669" s="14"/>
       <c r="C669" s="14"/>
@@ -30274,7 +30274,7 @@
       <c r="AI669" s="14"/>
       <c r="AJ669" s="14"/>
     </row>
-    <row r="670">
+    <row r="670" hidden="1">
       <c r="A670" s="14"/>
       <c r="B670" s="14"/>
       <c r="C670" s="14"/>
@@ -30312,7 +30312,7 @@
       <c r="AI670" s="14"/>
       <c r="AJ670" s="14"/>
     </row>
-    <row r="671">
+    <row r="671" hidden="1">
       <c r="A671" s="14"/>
       <c r="B671" s="14"/>
       <c r="C671" s="14"/>
@@ -30350,7 +30350,7 @@
       <c r="AI671" s="14"/>
       <c r="AJ671" s="14"/>
     </row>
-    <row r="672">
+    <row r="672" hidden="1">
       <c r="A672" s="14"/>
       <c r="B672" s="14"/>
       <c r="C672" s="14"/>
@@ -30388,7 +30388,7 @@
       <c r="AI672" s="14"/>
       <c r="AJ672" s="14"/>
     </row>
-    <row r="673">
+    <row r="673" hidden="1">
       <c r="A673" s="14"/>
       <c r="B673" s="14"/>
       <c r="C673" s="14"/>
@@ -30426,7 +30426,7 @@
       <c r="AI673" s="14"/>
       <c r="AJ673" s="14"/>
     </row>
-    <row r="674">
+    <row r="674" hidden="1">
       <c r="A674" s="14"/>
       <c r="B674" s="14"/>
       <c r="C674" s="14"/>
@@ -30464,7 +30464,7 @@
       <c r="AI674" s="14"/>
       <c r="AJ674" s="14"/>
     </row>
-    <row r="675">
+    <row r="675" hidden="1">
       <c r="A675" s="14"/>
       <c r="B675" s="14"/>
       <c r="C675" s="14"/>
@@ -30502,7 +30502,7 @@
       <c r="AI675" s="14"/>
       <c r="AJ675" s="14"/>
     </row>
-    <row r="676">
+    <row r="676" hidden="1">
       <c r="A676" s="14"/>
       <c r="B676" s="14"/>
       <c r="C676" s="14"/>
@@ -30540,7 +30540,7 @@
       <c r="AI676" s="14"/>
       <c r="AJ676" s="14"/>
     </row>
-    <row r="677">
+    <row r="677" hidden="1">
       <c r="A677" s="14"/>
       <c r="B677" s="14"/>
       <c r="C677" s="14"/>
@@ -30578,7 +30578,7 @@
       <c r="AI677" s="14"/>
       <c r="AJ677" s="14"/>
     </row>
-    <row r="678">
+    <row r="678" hidden="1">
       <c r="A678" s="14"/>
       <c r="B678" s="14"/>
       <c r="C678" s="14"/>
@@ -30616,7 +30616,7 @@
       <c r="AI678" s="14"/>
       <c r="AJ678" s="14"/>
     </row>
-    <row r="679">
+    <row r="679" hidden="1">
       <c r="A679" s="14"/>
       <c r="B679" s="14"/>
       <c r="C679" s="14"/>
@@ -30654,7 +30654,7 @@
       <c r="AI679" s="14"/>
       <c r="AJ679" s="14"/>
     </row>
-    <row r="680">
+    <row r="680" hidden="1">
       <c r="A680" s="14"/>
       <c r="B680" s="14"/>
       <c r="C680" s="14"/>
@@ -30692,7 +30692,7 @@
       <c r="AI680" s="14"/>
       <c r="AJ680" s="14"/>
     </row>
-    <row r="681">
+    <row r="681" hidden="1">
       <c r="A681" s="14"/>
       <c r="B681" s="14"/>
       <c r="C681" s="14"/>
@@ -30730,7 +30730,7 @@
       <c r="AI681" s="14"/>
       <c r="AJ681" s="14"/>
     </row>
-    <row r="682">
+    <row r="682" hidden="1">
       <c r="A682" s="14"/>
       <c r="B682" s="14"/>
       <c r="C682" s="14"/>
@@ -30768,7 +30768,7 @@
       <c r="AI682" s="14"/>
       <c r="AJ682" s="14"/>
     </row>
-    <row r="683">
+    <row r="683" hidden="1">
       <c r="A683" s="14"/>
       <c r="B683" s="14"/>
       <c r="C683" s="14"/>
@@ -30806,7 +30806,7 @@
       <c r="AI683" s="14"/>
       <c r="AJ683" s="14"/>
     </row>
-    <row r="684">
+    <row r="684" hidden="1">
       <c r="A684" s="14"/>
       <c r="B684" s="14"/>
       <c r="C684" s="14"/>
@@ -30844,7 +30844,7 @@
       <c r="AI684" s="14"/>
       <c r="AJ684" s="14"/>
     </row>
-    <row r="685">
+    <row r="685" hidden="1">
       <c r="A685" s="14"/>
       <c r="B685" s="14"/>
       <c r="C685" s="14"/>
@@ -30882,7 +30882,7 @@
       <c r="AI685" s="14"/>
       <c r="AJ685" s="14"/>
     </row>
-    <row r="686">
+    <row r="686" hidden="1">
       <c r="A686" s="14"/>
       <c r="B686" s="14"/>
       <c r="C686" s="14"/>
@@ -30920,7 +30920,7 @@
       <c r="AI686" s="14"/>
       <c r="AJ686" s="14"/>
     </row>
-    <row r="687">
+    <row r="687" hidden="1">
       <c r="A687" s="14"/>
       <c r="B687" s="14"/>
       <c r="C687" s="14"/>
@@ -30958,7 +30958,7 @@
       <c r="AI687" s="14"/>
       <c r="AJ687" s="14"/>
     </row>
-    <row r="688">
+    <row r="688" hidden="1">
       <c r="A688" s="14"/>
       <c r="B688" s="14"/>
       <c r="C688" s="14"/>
@@ -30996,7 +30996,7 @@
       <c r="AI688" s="14"/>
       <c r="AJ688" s="14"/>
     </row>
-    <row r="689">
+    <row r="689" hidden="1">
       <c r="A689" s="14"/>
       <c r="B689" s="14"/>
       <c r="C689" s="14"/>
@@ -31034,7 +31034,7 @@
       <c r="AI689" s="14"/>
       <c r="AJ689" s="14"/>
     </row>
-    <row r="690">
+    <row r="690" hidden="1">
       <c r="A690" s="14"/>
       <c r="B690" s="14"/>
       <c r="C690" s="14"/>
@@ -31072,7 +31072,7 @@
       <c r="AI690" s="14"/>
       <c r="AJ690" s="14"/>
     </row>
-    <row r="691">
+    <row r="691" hidden="1">
       <c r="A691" s="14"/>
       <c r="B691" s="14"/>
       <c r="C691" s="14"/>
@@ -31110,7 +31110,7 @@
       <c r="AI691" s="14"/>
       <c r="AJ691" s="14"/>
     </row>
-    <row r="692">
+    <row r="692" hidden="1">
       <c r="A692" s="14"/>
       <c r="B692" s="14"/>
       <c r="C692" s="14"/>
@@ -31148,7 +31148,7 @@
       <c r="AI692" s="14"/>
       <c r="AJ692" s="14"/>
     </row>
-    <row r="693">
+    <row r="693" hidden="1">
       <c r="A693" s="14"/>
       <c r="B693" s="14"/>
       <c r="C693" s="14"/>
@@ -31186,7 +31186,7 @@
       <c r="AI693" s="14"/>
       <c r="AJ693" s="14"/>
     </row>
-    <row r="694">
+    <row r="694" hidden="1">
       <c r="A694" s="14"/>
       <c r="B694" s="14"/>
       <c r="C694" s="14"/>
@@ -31224,7 +31224,7 @@
       <c r="AI694" s="14"/>
       <c r="AJ694" s="14"/>
     </row>
-    <row r="695">
+    <row r="695" hidden="1">
       <c r="A695" s="14"/>
       <c r="B695" s="14"/>
       <c r="C695" s="14"/>
@@ -31262,7 +31262,7 @@
       <c r="AI695" s="14"/>
       <c r="AJ695" s="14"/>
     </row>
-    <row r="696">
+    <row r="696" hidden="1">
       <c r="A696" s="14"/>
       <c r="B696" s="14"/>
       <c r="C696" s="14"/>
@@ -31300,7 +31300,7 @@
       <c r="AI696" s="14"/>
       <c r="AJ696" s="14"/>
     </row>
-    <row r="697">
+    <row r="697" hidden="1">
       <c r="A697" s="14"/>
       <c r="B697" s="14"/>
       <c r="C697" s="14"/>
@@ -31338,7 +31338,7 @@
       <c r="AI697" s="14"/>
       <c r="AJ697" s="14"/>
     </row>
-    <row r="698">
+    <row r="698" hidden="1">
       <c r="A698" s="14"/>
       <c r="B698" s="14"/>
       <c r="C698" s="14"/>
@@ -31376,7 +31376,7 @@
       <c r="AI698" s="14"/>
       <c r="AJ698" s="14"/>
     </row>
-    <row r="699">
+    <row r="699" hidden="1">
       <c r="A699" s="14"/>
       <c r="B699" s="14"/>
       <c r="C699" s="14"/>
@@ -31414,7 +31414,7 @@
       <c r="AI699" s="14"/>
       <c r="AJ699" s="14"/>
     </row>
-    <row r="700">
+    <row r="700" hidden="1">
       <c r="A700" s="14"/>
       <c r="B700" s="14"/>
       <c r="C700" s="14"/>
@@ -31452,7 +31452,7 @@
       <c r="AI700" s="14"/>
       <c r="AJ700" s="14"/>
     </row>
-    <row r="701">
+    <row r="701" hidden="1">
       <c r="A701" s="14"/>
       <c r="B701" s="14"/>
       <c r="C701" s="14"/>
@@ -31490,7 +31490,7 @@
       <c r="AI701" s="14"/>
       <c r="AJ701" s="14"/>
     </row>
-    <row r="702">
+    <row r="702" hidden="1">
       <c r="A702" s="14"/>
       <c r="B702" s="14"/>
       <c r="C702" s="14"/>
@@ -31528,7 +31528,7 @@
       <c r="AI702" s="14"/>
       <c r="AJ702" s="14"/>
     </row>
-    <row r="703">
+    <row r="703" hidden="1">
       <c r="A703" s="14"/>
       <c r="B703" s="14"/>
       <c r="C703" s="14"/>
@@ -31566,7 +31566,7 @@
       <c r="AI703" s="14"/>
       <c r="AJ703" s="14"/>
     </row>
-    <row r="704">
+    <row r="704" hidden="1">
       <c r="A704" s="14"/>
       <c r="B704" s="14"/>
       <c r="C704" s="14"/>
@@ -31604,7 +31604,7 @@
       <c r="AI704" s="14"/>
       <c r="AJ704" s="14"/>
     </row>
-    <row r="705">
+    <row r="705" hidden="1">
       <c r="A705" s="14"/>
       <c r="B705" s="14"/>
       <c r="C705" s="14"/>
@@ -31642,7 +31642,7 @@
       <c r="AI705" s="14"/>
       <c r="AJ705" s="14"/>
     </row>
-    <row r="706">
+    <row r="706" hidden="1">
       <c r="A706" s="14"/>
       <c r="B706" s="14"/>
       <c r="C706" s="14"/>
@@ -31680,7 +31680,7 @@
       <c r="AI706" s="14"/>
       <c r="AJ706" s="14"/>
     </row>
-    <row r="707">
+    <row r="707" hidden="1">
       <c r="A707" s="14"/>
       <c r="B707" s="14"/>
       <c r="C707" s="14"/>
@@ -31718,7 +31718,7 @@
       <c r="AI707" s="14"/>
       <c r="AJ707" s="14"/>
     </row>
-    <row r="708">
+    <row r="708" hidden="1">
       <c r="A708" s="14"/>
       <c r="B708" s="14"/>
       <c r="C708" s="14"/>
@@ -31756,7 +31756,7 @@
       <c r="AI708" s="14"/>
       <c r="AJ708" s="14"/>
     </row>
-    <row r="709">
+    <row r="709" hidden="1">
       <c r="A709" s="14"/>
       <c r="B709" s="14"/>
       <c r="C709" s="14"/>
@@ -31794,7 +31794,7 @@
       <c r="AI709" s="14"/>
       <c r="AJ709" s="14"/>
     </row>
-    <row r="710">
+    <row r="710" hidden="1">
       <c r="A710" s="14"/>
       <c r="B710" s="14"/>
       <c r="C710" s="14"/>
@@ -31832,7 +31832,7 @@
       <c r="AI710" s="14"/>
       <c r="AJ710" s="14"/>
     </row>
-    <row r="711">
+    <row r="711" hidden="1">
       <c r="A711" s="14"/>
       <c r="B711" s="14"/>
       <c r="C711" s="14"/>
@@ -31870,7 +31870,7 @@
       <c r="AI711" s="14"/>
       <c r="AJ711" s="14"/>
     </row>
-    <row r="712">
+    <row r="712" hidden="1">
       <c r="A712" s="14"/>
       <c r="B712" s="14"/>
       <c r="C712" s="14"/>
@@ -31908,7 +31908,7 @@
       <c r="AI712" s="14"/>
       <c r="AJ712" s="14"/>
     </row>
-    <row r="713">
+    <row r="713" hidden="1">
       <c r="A713" s="14"/>
       <c r="B713" s="14"/>
       <c r="C713" s="14"/>
@@ -31946,7 +31946,7 @@
       <c r="AI713" s="14"/>
       <c r="AJ713" s="14"/>
     </row>
-    <row r="714">
+    <row r="714" hidden="1">
       <c r="A714" s="14"/>
       <c r="B714" s="14"/>
       <c r="C714" s="14"/>
@@ -31984,7 +31984,7 @@
       <c r="AI714" s="14"/>
       <c r="AJ714" s="14"/>
     </row>
-    <row r="715">
+    <row r="715" hidden="1">
       <c r="A715" s="14"/>
       <c r="B715" s="14"/>
       <c r="C715" s="14"/>
@@ -32022,7 +32022,7 @@
       <c r="AI715" s="14"/>
       <c r="AJ715" s="14"/>
     </row>
-    <row r="716">
+    <row r="716" hidden="1">
       <c r="A716" s="14"/>
       <c r="B716" s="14"/>
       <c r="C716" s="14"/>
@@ -32060,7 +32060,7 @@
       <c r="AI716" s="14"/>
       <c r="AJ716" s="14"/>
     </row>
-    <row r="717">
+    <row r="717" hidden="1">
       <c r="A717" s="14"/>
       <c r="B717" s="14"/>
       <c r="C717" s="14"/>
@@ -32098,7 +32098,7 @@
       <c r="AI717" s="14"/>
       <c r="AJ717" s="14"/>
     </row>
-    <row r="718">
+    <row r="718" hidden="1">
       <c r="A718" s="14"/>
       <c r="B718" s="14"/>
       <c r="C718" s="14"/>
@@ -32136,7 +32136,7 @@
       <c r="AI718" s="14"/>
       <c r="AJ718" s="14"/>
     </row>
-    <row r="719">
+    <row r="719" hidden="1">
       <c r="A719" s="14"/>
       <c r="B719" s="14"/>
       <c r="C719" s="14"/>
@@ -32174,7 +32174,7 @@
       <c r="AI719" s="14"/>
       <c r="AJ719" s="14"/>
     </row>
-    <row r="720">
+    <row r="720" hidden="1">
       <c r="A720" s="14"/>
       <c r="B720" s="14"/>
       <c r="C720" s="14"/>
@@ -32212,7 +32212,7 @@
       <c r="AI720" s="14"/>
       <c r="AJ720" s="14"/>
     </row>
-    <row r="721">
+    <row r="721" hidden="1">
       <c r="A721" s="14"/>
       <c r="B721" s="14"/>
       <c r="C721" s="14"/>
@@ -32250,7 +32250,7 @@
       <c r="AI721" s="14"/>
       <c r="AJ721" s="14"/>
     </row>
-    <row r="722">
+    <row r="722" hidden="1">
       <c r="A722" s="14"/>
       <c r="B722" s="14"/>
       <c r="C722" s="14"/>
@@ -32288,7 +32288,7 @@
       <c r="AI722" s="14"/>
       <c r="AJ722" s="14"/>
     </row>
-    <row r="723">
+    <row r="723" hidden="1">
       <c r="A723" s="14"/>
       <c r="B723" s="14"/>
       <c r="C723" s="14"/>
@@ -32326,7 +32326,7 @@
       <c r="AI723" s="14"/>
       <c r="AJ723" s="14"/>
     </row>
-    <row r="724">
+    <row r="724" hidden="1">
       <c r="A724" s="14"/>
       <c r="B724" s="14"/>
       <c r="C724" s="14"/>
@@ -32364,7 +32364,7 @@
       <c r="AI724" s="14"/>
       <c r="AJ724" s="14"/>
     </row>
-    <row r="725">
+    <row r="725" hidden="1">
       <c r="A725" s="14"/>
       <c r="B725" s="14"/>
       <c r="C725" s="14"/>
@@ -32402,7 +32402,7 @@
       <c r="AI725" s="14"/>
       <c r="AJ725" s="14"/>
     </row>
-    <row r="726">
+    <row r="726" hidden="1">
       <c r="A726" s="14"/>
       <c r="B726" s="14"/>
       <c r="C726" s="14"/>
@@ -32440,7 +32440,7 @@
       <c r="AI726" s="14"/>
       <c r="AJ726" s="14"/>
     </row>
-    <row r="727">
+    <row r="727" hidden="1">
       <c r="A727" s="14"/>
       <c r="B727" s="14"/>
       <c r="C727" s="14"/>
@@ -32478,7 +32478,7 @@
       <c r="AI727" s="14"/>
       <c r="AJ727" s="14"/>
     </row>
-    <row r="728">
+    <row r="728" hidden="1">
       <c r="A728" s="14"/>
       <c r="B728" s="14"/>
       <c r="C728" s="14"/>
@@ -32516,7 +32516,7 @@
       <c r="AI728" s="14"/>
       <c r="AJ728" s="14"/>
     </row>
-    <row r="729">
+    <row r="729" hidden="1">
       <c r="A729" s="14"/>
       <c r="B729" s="14"/>
       <c r="C729" s="14"/>
@@ -32554,7 +32554,7 @@
       <c r="AI729" s="14"/>
       <c r="AJ729" s="14"/>
     </row>
-    <row r="730">
+    <row r="730" hidden="1">
       <c r="A730" s="14"/>
       <c r="B730" s="14"/>
       <c r="C730" s="14"/>
@@ -32592,7 +32592,7 @@
       <c r="AI730" s="14"/>
       <c r="AJ730" s="14"/>
     </row>
-    <row r="731">
+    <row r="731" hidden="1">
       <c r="A731" s="14"/>
       <c r="B731" s="14"/>
       <c r="C731" s="14"/>
@@ -32630,7 +32630,7 @@
       <c r="AI731" s="14"/>
       <c r="AJ731" s="14"/>
     </row>
-    <row r="732">
+    <row r="732" hidden="1">
       <c r="A732" s="14"/>
       <c r="B732" s="14"/>
       <c r="C732" s="14"/>
@@ -32668,7 +32668,7 @@
       <c r="AI732" s="14"/>
       <c r="AJ732" s="14"/>
     </row>
-    <row r="733">
+    <row r="733" hidden="1">
       <c r="A733" s="14"/>
       <c r="B733" s="14"/>
       <c r="C733" s="14"/>
@@ -32706,7 +32706,7 @@
       <c r="AI733" s="14"/>
       <c r="AJ733" s="14"/>
     </row>
-    <row r="734">
+    <row r="734" hidden="1">
       <c r="A734" s="14"/>
       <c r="B734" s="14"/>
       <c r="C734" s="14"/>
@@ -32744,7 +32744,7 @@
       <c r="AI734" s="14"/>
       <c r="AJ734" s="14"/>
     </row>
-    <row r="735">
+    <row r="735" hidden="1">
       <c r="A735" s="14"/>
       <c r="B735" s="14"/>
       <c r="C735" s="14"/>
@@ -32782,7 +32782,7 @@
       <c r="AI735" s="14"/>
       <c r="AJ735" s="14"/>
     </row>
-    <row r="736">
+    <row r="736" hidden="1">
       <c r="A736" s="14"/>
       <c r="B736" s="14"/>
       <c r="C736" s="14"/>
@@ -32820,7 +32820,7 @@
       <c r="AI736" s="14"/>
       <c r="AJ736" s="14"/>
     </row>
-    <row r="737">
+    <row r="737" hidden="1">
       <c r="A737" s="14"/>
       <c r="B737" s="14"/>
       <c r="C737" s="14"/>
@@ -32858,7 +32858,7 @@
       <c r="AI737" s="14"/>
       <c r="AJ737" s="14"/>
     </row>
-    <row r="738">
+    <row r="738" hidden="1">
       <c r="A738" s="14"/>
       <c r="B738" s="14"/>
       <c r="C738" s="14"/>
@@ -32896,7 +32896,7 @@
       <c r="AI738" s="14"/>
       <c r="AJ738" s="14"/>
     </row>
-    <row r="739">
+    <row r="739" hidden="1">
       <c r="A739" s="14"/>
       <c r="B739" s="14"/>
       <c r="C739" s="14"/>
@@ -32934,7 +32934,7 @@
       <c r="AI739" s="14"/>
       <c r="AJ739" s="14"/>
     </row>
-    <row r="740">
+    <row r="740" hidden="1">
       <c r="A740" s="14"/>
       <c r="B740" s="14"/>
       <c r="C740" s="14"/>
@@ -32972,7 +32972,7 @@
       <c r="AI740" s="14"/>
       <c r="AJ740" s="14"/>
     </row>
-    <row r="741">
+    <row r="741" hidden="1">
       <c r="A741" s="14"/>
       <c r="B741" s="14"/>
       <c r="C741" s="14"/>
@@ -33010,7 +33010,7 @@
       <c r="AI741" s="14"/>
       <c r="AJ741" s="14"/>
     </row>
-    <row r="742">
+    <row r="742" hidden="1">
       <c r="A742" s="14"/>
       <c r="B742" s="14"/>
       <c r="C742" s="14"/>
@@ -33048,7 +33048,7 @@
       <c r="AI742" s="14"/>
       <c r="AJ742" s="14"/>
     </row>
-    <row r="743">
+    <row r="743" hidden="1">
       <c r="A743" s="14"/>
       <c r="B743" s="14"/>
       <c r="C743" s="14"/>
@@ -33086,7 +33086,7 @@
       <c r="AI743" s="14"/>
       <c r="AJ743" s="14"/>
     </row>
-    <row r="744">
+    <row r="744" hidden="1">
       <c r="A744" s="14"/>
       <c r="B744" s="14"/>
       <c r="C744" s="14"/>
@@ -33124,7 +33124,7 @@
       <c r="AI744" s="14"/>
       <c r="AJ744" s="14"/>
     </row>
-    <row r="745">
+    <row r="745" hidden="1">
       <c r="A745" s="14"/>
       <c r="B745" s="14"/>
       <c r="C745" s="14"/>
@@ -33162,7 +33162,7 @@
       <c r="AI745" s="14"/>
       <c r="AJ745" s="14"/>
     </row>
-    <row r="746">
+    <row r="746" hidden="1">
       <c r="A746" s="14"/>
       <c r="B746" s="14"/>
       <c r="C746" s="14"/>
@@ -33200,7 +33200,7 @@
       <c r="AI746" s="14"/>
       <c r="AJ746" s="14"/>
     </row>
-    <row r="747">
+    <row r="747" hidden="1">
       <c r="A747" s="14"/>
       <c r="B747" s="14"/>
       <c r="C747" s="14"/>
@@ -33238,7 +33238,7 @@
       <c r="AI747" s="14"/>
       <c r="AJ747" s="14"/>
     </row>
-    <row r="748">
+    <row r="748" hidden="1">
       <c r="A748" s="14"/>
       <c r="B748" s="14"/>
       <c r="C748" s="14"/>
@@ -33276,7 +33276,7 @@
       <c r="AI748" s="14"/>
       <c r="AJ748" s="14"/>
     </row>
-    <row r="749">
+    <row r="749" hidden="1">
       <c r="A749" s="14"/>
       <c r="B749" s="14"/>
       <c r="C749" s="14"/>
@@ -33314,7 +33314,7 @@
       <c r="AI749" s="14"/>
       <c r="AJ749" s="14"/>
     </row>
-    <row r="750">
+    <row r="750" hidden="1">
       <c r="A750" s="14"/>
       <c r="B750" s="14"/>
       <c r="C750" s="14"/>
@@ -33352,7 +33352,7 @@
       <c r="AI750" s="14"/>
       <c r="AJ750" s="14"/>
     </row>
-    <row r="751">
+    <row r="751" hidden="1">
       <c r="A751" s="14"/>
       <c r="B751" s="14"/>
       <c r="C751" s="14"/>
@@ -33390,7 +33390,7 @@
       <c r="AI751" s="14"/>
       <c r="AJ751" s="14"/>
     </row>
-    <row r="752">
+    <row r="752" hidden="1">
       <c r="A752" s="14"/>
       <c r="B752" s="14"/>
       <c r="C752" s="14"/>
@@ -33428,7 +33428,7 @@
       <c r="AI752" s="14"/>
       <c r="AJ752" s="14"/>
     </row>
-    <row r="753">
+    <row r="753" hidden="1">
       <c r="A753" s="14"/>
       <c r="B753" s="14"/>
       <c r="C753" s="14"/>
@@ -33466,7 +33466,7 @@
       <c r="AI753" s="14"/>
       <c r="AJ753" s="14"/>
     </row>
-    <row r="754">
+    <row r="754" hidden="1">
       <c r="A754" s="14"/>
       <c r="B754" s="14"/>
       <c r="C754" s="14"/>
@@ -33504,7 +33504,7 @@
       <c r="AI754" s="14"/>
       <c r="AJ754" s="14"/>
     </row>
-    <row r="755">
+    <row r="755" hidden="1">
       <c r="A755" s="14"/>
       <c r="B755" s="14"/>
       <c r="C755" s="14"/>
@@ -33542,7 +33542,7 @@
       <c r="AI755" s="14"/>
       <c r="AJ755" s="14"/>
     </row>
-    <row r="756">
+    <row r="756" hidden="1">
       <c r="A756" s="14"/>
       <c r="B756" s="14"/>
       <c r="C756" s="14"/>
@@ -33580,7 +33580,7 @@
       <c r="AI756" s="14"/>
       <c r="AJ756" s="14"/>
     </row>
-    <row r="757">
+    <row r="757" hidden="1">
       <c r="A757" s="14"/>
       <c r="B757" s="14"/>
       <c r="C757" s="14"/>
@@ -33618,7 +33618,7 @@
       <c r="AI757" s="14"/>
       <c r="AJ757" s="14"/>
     </row>
-    <row r="758">
+    <row r="758" hidden="1">
       <c r="A758" s="14"/>
       <c r="B758" s="14"/>
       <c r="C758" s="14"/>
@@ -33656,7 +33656,7 @@
       <c r="AI758" s="14"/>
       <c r="AJ758" s="14"/>
     </row>
-    <row r="759">
+    <row r="759" hidden="1">
       <c r="A759" s="14"/>
       <c r="B759" s="14"/>
       <c r="C759" s="14"/>
@@ -33694,7 +33694,7 @@
       <c r="AI759" s="14"/>
       <c r="AJ759" s="14"/>
     </row>
-    <row r="760">
+    <row r="760" hidden="1">
       <c r="A760" s="14"/>
       <c r="B760" s="14"/>
       <c r="C760" s="14"/>
@@ -33732,7 +33732,7 @@
       <c r="AI760" s="14"/>
       <c r="AJ760" s="14"/>
     </row>
-    <row r="761">
+    <row r="761" hidden="1">
       <c r="A761" s="14"/>
       <c r="B761" s="14"/>
       <c r="C761" s="14"/>
@@ -33770,7 +33770,7 @@
       <c r="AI761" s="14"/>
       <c r="AJ761" s="14"/>
     </row>
-    <row r="762">
+    <row r="762" hidden="1">
       <c r="A762" s="14"/>
       <c r="B762" s="14"/>
       <c r="C762" s="14"/>
@@ -33808,7 +33808,7 @@
       <c r="AI762" s="14"/>
       <c r="AJ762" s="14"/>
     </row>
-    <row r="763">
+    <row r="763" hidden="1">
       <c r="A763" s="14"/>
       <c r="B763" s="14"/>
       <c r="C763" s="14"/>
@@ -33846,7 +33846,7 @@
       <c r="AI763" s="14"/>
       <c r="AJ763" s="14"/>
     </row>
-    <row r="764">
+    <row r="764" hidden="1">
       <c r="A764" s="14"/>
       <c r="B764" s="14"/>
       <c r="C764" s="14"/>
@@ -33884,7 +33884,7 @@
       <c r="AI764" s="14"/>
       <c r="AJ764" s="14"/>
     </row>
-    <row r="765">
+    <row r="765" hidden="1">
       <c r="A765" s="14"/>
       <c r="B765" s="14"/>
       <c r="C765" s="14"/>
@@ -33922,7 +33922,7 @@
       <c r="AI765" s="14"/>
       <c r="AJ765" s="14"/>
     </row>
-    <row r="766">
+    <row r="766" hidden="1">
       <c r="A766" s="14"/>
       <c r="B766" s="14"/>
       <c r="C766" s="14"/>
@@ -33960,7 +33960,7 @@
       <c r="AI766" s="14"/>
       <c r="AJ766" s="14"/>
     </row>
-    <row r="767">
+    <row r="767" hidden="1">
       <c r="A767" s="14"/>
       <c r="B767" s="14"/>
       <c r="C767" s="14"/>
@@ -33998,7 +33998,7 @@
       <c r="AI767" s="14"/>
       <c r="AJ767" s="14"/>
     </row>
-    <row r="768">
+    <row r="768" hidden="1">
       <c r="A768" s="14"/>
       <c r="B768" s="14"/>
       <c r="C768" s="14"/>
@@ -34036,7 +34036,7 @@
       <c r="AI768" s="14"/>
       <c r="AJ768" s="14"/>
     </row>
-    <row r="769">
+    <row r="769" hidden="1">
       <c r="A769" s="14"/>
       <c r="B769" s="14"/>
       <c r="C769" s="14"/>
@@ -34074,7 +34074,7 @@
       <c r="AI769" s="14"/>
       <c r="AJ769" s="14"/>
     </row>
-    <row r="770">
+    <row r="770" hidden="1">
       <c r="A770" s="14"/>
       <c r="B770" s="14"/>
       <c r="C770" s="14"/>
@@ -34112,7 +34112,7 @@
       <c r="AI770" s="14"/>
       <c r="AJ770" s="14"/>
     </row>
-    <row r="771">
+    <row r="771" hidden="1">
       <c r="A771" s="14"/>
       <c r="B771" s="14"/>
       <c r="C771" s="14"/>
@@ -34150,7 +34150,7 @@
       <c r="AI771" s="14"/>
       <c r="AJ771" s="14"/>
     </row>
-    <row r="772">
+    <row r="772" hidden="1">
       <c r="A772" s="14"/>
       <c r="B772" s="14"/>
       <c r="C772" s="14"/>
@@ -34188,7 +34188,7 @@
       <c r="AI772" s="14"/>
       <c r="AJ772" s="14"/>
     </row>
-    <row r="773">
+    <row r="773" hidden="1">
       <c r="A773" s="14"/>
       <c r="B773" s="14"/>
       <c r="C773" s="14"/>
@@ -34226,7 +34226,7 @@
       <c r="AI773" s="14"/>
       <c r="AJ773" s="14"/>
     </row>
-    <row r="774">
+    <row r="774" hidden="1">
       <c r="A774" s="14"/>
       <c r="B774" s="14"/>
       <c r="C774" s="14"/>
@@ -34264,7 +34264,7 @@
       <c r="AI774" s="14"/>
       <c r="AJ774" s="14"/>
     </row>
-    <row r="775">
+    <row r="775" hidden="1">
       <c r="A775" s="14"/>
       <c r="B775" s="14"/>
       <c r="C775" s="14"/>
@@ -34302,7 +34302,7 @@
       <c r="AI775" s="14"/>
       <c r="AJ775" s="14"/>
     </row>
-    <row r="776">
+    <row r="776" hidden="1">
       <c r="A776" s="14"/>
       <c r="B776" s="14"/>
       <c r="C776" s="14"/>
@@ -34340,7 +34340,7 @@
       <c r="AI776" s="14"/>
       <c r="AJ776" s="14"/>
     </row>
-    <row r="777">
+    <row r="777" hidden="1">
       <c r="A777" s="14"/>
       <c r="B777" s="14"/>
       <c r="C777" s="14"/>
@@ -34378,7 +34378,7 @@
       <c r="AI777" s="14"/>
       <c r="AJ777" s="14"/>
     </row>
-    <row r="778">
+    <row r="778" hidden="1">
       <c r="A778" s="14"/>
       <c r="B778" s="14"/>
       <c r="C778" s="14"/>
@@ -34416,7 +34416,7 @@
       <c r="AI778" s="14"/>
       <c r="AJ778" s="14"/>
     </row>
-    <row r="779">
+    <row r="779" hidden="1">
       <c r="A779" s="14"/>
       <c r="B779" s="14"/>
       <c r="C779" s="14"/>
@@ -34454,7 +34454,7 @@
       <c r="AI779" s="14"/>
       <c r="AJ779" s="14"/>
     </row>
-    <row r="780">
+    <row r="780" hidden="1">
       <c r="A780" s="14"/>
       <c r="B780" s="14"/>
       <c r="C780" s="14"/>
@@ -34492,7 +34492,7 @@
       <c r="AI780" s="14"/>
       <c r="AJ780" s="14"/>
     </row>
-    <row r="781">
+    <row r="781" hidden="1">
       <c r="A781" s="14"/>
       <c r="B781" s="14"/>
       <c r="C781" s="14"/>
@@ -34530,7 +34530,7 @@
       <c r="AI781" s="14"/>
       <c r="AJ781" s="14"/>
     </row>
-    <row r="782">
+    <row r="782" hidden="1">
       <c r="A782" s="14"/>
       <c r="B782" s="14"/>
       <c r="C782" s="14"/>
@@ -34568,7 +34568,7 @@
       <c r="AI782" s="14"/>
       <c r="AJ782" s="14"/>
     </row>
-    <row r="783">
+    <row r="783" hidden="1">
       <c r="A783" s="14"/>
       <c r="B783" s="14"/>
       <c r="C783" s="14"/>
@@ -34606,7 +34606,7 @@
       <c r="AI783" s="14"/>
       <c r="AJ783" s="14"/>
     </row>
-    <row r="784">
+    <row r="784" hidden="1">
       <c r="A784" s="14"/>
       <c r="B784" s="14"/>
       <c r="C784" s="14"/>
@@ -34644,7 +34644,7 @@
       <c r="AI784" s="14"/>
       <c r="AJ784" s="14"/>
     </row>
-    <row r="785">
+    <row r="785" hidden="1">
       <c r="A785" s="14"/>
       <c r="B785" s="14"/>
       <c r="C785" s="14"/>
@@ -34682,7 +34682,7 @@
       <c r="AI785" s="14"/>
       <c r="AJ785" s="14"/>
     </row>
-    <row r="786">
+    <row r="786" hidden="1">
       <c r="A786" s="14"/>
       <c r="B786" s="14"/>
       <c r="C786" s="14"/>
@@ -34720,7 +34720,7 @@
       <c r="AI786" s="14"/>
       <c r="AJ786" s="14"/>
     </row>
-    <row r="787">
+    <row r="787" hidden="1">
       <c r="A787" s="14"/>
       <c r="B787" s="14"/>
       <c r="C787" s="14"/>
@@ -34758,7 +34758,7 @@
       <c r="AI787" s="14"/>
       <c r="AJ787" s="14"/>
     </row>
-    <row r="788">
+    <row r="788" hidden="1">
       <c r="A788" s="14"/>
       <c r="B788" s="14"/>
       <c r="C788" s="14"/>
@@ -34796,7 +34796,7 @@
       <c r="AI788" s="14"/>
       <c r="AJ788" s="14"/>
     </row>
-    <row r="789">
+    <row r="789" hidden="1">
       <c r="A789" s="14"/>
       <c r="B789" s="14"/>
       <c r="C789" s="14"/>
@@ -34834,7 +34834,7 @@
       <c r="AI789" s="14"/>
       <c r="AJ789" s="14"/>
     </row>
-    <row r="790">
+    <row r="790" hidden="1">
       <c r="A790" s="14"/>
       <c r="B790" s="14"/>
       <c r="C790" s="14"/>
@@ -34872,7 +34872,7 @@
       <c r="AI790" s="14"/>
       <c r="AJ790" s="14"/>
     </row>
-    <row r="791">
+    <row r="791" hidden="1">
       <c r="A791" s="14"/>
       <c r="B791" s="14"/>
       <c r="C791" s="14"/>
@@ -34910,7 +34910,7 @@
       <c r="AI791" s="14"/>
       <c r="AJ791" s="14"/>
     </row>
-    <row r="792">
+    <row r="792" hidden="1">
       <c r="A792" s="14"/>
       <c r="B792" s="14"/>
       <c r="C792" s="14"/>
@@ -34948,7 +34948,7 @@
       <c r="AI792" s="14"/>
       <c r="AJ792" s="14"/>
     </row>
-    <row r="793">
+    <row r="793" hidden="1">
       <c r="A793" s="14"/>
       <c r="B793" s="14"/>
       <c r="C793" s="14"/>
@@ -34986,7 +34986,7 @@
       <c r="AI793" s="14"/>
       <c r="AJ793" s="14"/>
     </row>
-    <row r="794">
+    <row r="794" hidden="1">
       <c r="A794" s="14"/>
       <c r="B794" s="14"/>
       <c r="C794" s="14"/>
@@ -35024,7 +35024,7 @@
       <c r="AI794" s="14"/>
       <c r="AJ794" s="14"/>
     </row>
-    <row r="795">
+    <row r="795" hidden="1">
       <c r="A795" s="14"/>
       <c r="B795" s="14"/>
       <c r="C795" s="14"/>
@@ -35062,7 +35062,7 @@
       <c r="AI795" s="14"/>
       <c r="AJ795" s="14"/>
     </row>
-    <row r="796">
+    <row r="796" hidden="1">
       <c r="A796" s="14"/>
       <c r="B796" s="14"/>
       <c r="C796" s="14"/>
@@ -35100,7 +35100,7 @@
       <c r="AI796" s="14"/>
       <c r="AJ796" s="14"/>
     </row>
-    <row r="797">
+    <row r="797" hidden="1">
       <c r="A797" s="14"/>
       <c r="B797" s="14"/>
       <c r="C797" s="14"/>
@@ -35138,7 +35138,7 @@
       <c r="AI797" s="14"/>
       <c r="AJ797" s="14"/>
     </row>
-    <row r="798">
+    <row r="798" hidden="1">
       <c r="A798" s="14"/>
       <c r="B798" s="14"/>
       <c r="C798" s="14"/>
@@ -35176,7 +35176,7 @@
       <c r="AI798" s="14"/>
       <c r="AJ798" s="14"/>
     </row>
-    <row r="799">
+    <row r="799" hidden="1">
       <c r="A799" s="14"/>
       <c r="B799" s="14"/>
       <c r="C799" s="14"/>
@@ -35214,7 +35214,7 @@
       <c r="AI799" s="14"/>
       <c r="AJ799" s="14"/>
     </row>
-    <row r="800">
+    <row r="800" hidden="1">
       <c r="A800" s="14"/>
       <c r="B800" s="14"/>
       <c r="C800" s="14"/>
@@ -35252,7 +35252,7 @@
       <c r="AI800" s="14"/>
       <c r="AJ800" s="14"/>
     </row>
-    <row r="801">
+    <row r="801" hidden="1">
       <c r="A801" s="14"/>
       <c r="B801" s="14"/>
       <c r="C801" s="14"/>
@@ -35290,7 +35290,7 @@
       <c r="AI801" s="14"/>
       <c r="AJ801" s="14"/>
     </row>
-    <row r="802">
+    <row r="802" hidden="1">
       <c r="A802" s="14"/>
       <c r="B802" s="14"/>
       <c r="C802" s="14"/>
@@ -35328,7 +35328,7 @@
       <c r="AI802" s="14"/>
       <c r="AJ802" s="14"/>
     </row>
-    <row r="803">
+    <row r="803" hidden="1">
       <c r="A803" s="14"/>
       <c r="B803" s="14"/>
       <c r="C803" s="14"/>
@@ -35366,7 +35366,7 @@
       <c r="AI803" s="14"/>
       <c r="AJ803" s="14"/>
     </row>
-    <row r="804">
+    <row r="804" hidden="1">
       <c r="A804" s="14"/>
       <c r="B804" s="14"/>
       <c r="C804" s="14"/>
@@ -35404,7 +35404,7 @@
       <c r="AI804" s="14"/>
       <c r="AJ804" s="14"/>
     </row>
-    <row r="805">
+    <row r="805" hidden="1">
       <c r="A805" s="14"/>
       <c r="B805" s="14"/>
       <c r="C805" s="14"/>
@@ -35442,7 +35442,7 @@
       <c r="AI805" s="14"/>
       <c r="AJ805" s="14"/>
     </row>
-    <row r="806">
+    <row r="806" hidden="1">
       <c r="A806" s="14"/>
       <c r="B806" s="14"/>
       <c r="C806" s="14"/>
@@ -35480,7 +35480,7 @@
       <c r="AI806" s="14"/>
       <c r="AJ806" s="14"/>
     </row>
-    <row r="807">
+    <row r="807" hidden="1">
       <c r="A807" s="14"/>
       <c r="B807" s="14"/>
       <c r="C807" s="14"/>
@@ -35518,7 +35518,7 @@
       <c r="AI807" s="14"/>
       <c r="AJ807" s="14"/>
     </row>
-    <row r="808">
+    <row r="808" hidden="1">
       <c r="A808" s="14"/>
       <c r="B808" s="14"/>
       <c r="C808" s="14"/>
@@ -35556,7 +35556,7 @@
       <c r="AI808" s="14"/>
       <c r="AJ808" s="14"/>
     </row>
-    <row r="809">
+    <row r="809" hidden="1">
       <c r="A809" s="14"/>
       <c r="B809" s="14"/>
       <c r="C809" s="14"/>
@@ -35594,7 +35594,7 @@
       <c r="AI809" s="14"/>
       <c r="AJ809" s="14"/>
     </row>
-    <row r="810">
+    <row r="810" hidden="1">
       <c r="A810" s="14"/>
       <c r="B810" s="14"/>
       <c r="C810" s="14"/>
@@ -35632,7 +35632,7 @@
       <c r="AI810" s="14"/>
       <c r="AJ810" s="14"/>
     </row>
-    <row r="811">
+    <row r="811" hidden="1">
       <c r="A811" s="14"/>
       <c r="B811" s="14"/>
       <c r="C811" s="14"/>
@@ -35670,7 +35670,7 @@
       <c r="AI811" s="14"/>
       <c r="AJ811" s="14"/>
     </row>
-    <row r="812">
+    <row r="812" hidden="1">
       <c r="A812" s="14"/>
       <c r="B812" s="14"/>
       <c r="C812" s="14"/>
@@ -35708,7 +35708,7 @@
       <c r="AI812" s="14"/>
       <c r="AJ812" s="14"/>
     </row>
-    <row r="813">
+    <row r="813" hidden="1">
       <c r="A813" s="14"/>
       <c r="B813" s="14"/>
       <c r="C813" s="14"/>
@@ -35746,7 +35746,7 @@
       <c r="AI813" s="14"/>
       <c r="AJ813" s="14"/>
     </row>
-    <row r="814">
+    <row r="814" hidden="1">
       <c r="A814" s="14"/>
       <c r="B814" s="14"/>
       <c r="C814" s="14"/>
@@ -35784,7 +35784,7 @@
       <c r="AI814" s="14"/>
       <c r="AJ814" s="14"/>
     </row>
-    <row r="815">
+    <row r="815" hidden="1">
       <c r="A815" s="14"/>
       <c r="B815" s="14"/>
       <c r="C815" s="14"/>
@@ -35822,7 +35822,7 @@
       <c r="AI815" s="14"/>
       <c r="AJ815" s="14"/>
     </row>
-    <row r="816">
+    <row r="816" hidden="1">
       <c r="A816" s="14"/>
       <c r="B816" s="14"/>
       <c r="C816" s="14"/>
@@ -35860,7 +35860,7 @@
       <c r="AI816" s="14"/>
       <c r="AJ816" s="14"/>
     </row>
-    <row r="817">
+    <row r="817" hidden="1">
       <c r="A817" s="14"/>
       <c r="B817" s="14"/>
       <c r="C817" s="14"/>
@@ -35898,7 +35898,7 @@
       <c r="AI817" s="14"/>
       <c r="AJ817" s="14"/>
     </row>
-    <row r="818">
+    <row r="818" hidden="1">
       <c r="A818" s="14"/>
       <c r="B818" s="14"/>
       <c r="C818" s="14"/>
@@ -35936,7 +35936,7 @@
       <c r="AI818" s="14"/>
       <c r="AJ818" s="14"/>
     </row>
-    <row r="819">
+    <row r="819" hidden="1">
       <c r="A819" s="14"/>
       <c r="B819" s="14"/>
       <c r="C819" s="14"/>
@@ -35974,7 +35974,7 @@
       <c r="AI819" s="14"/>
       <c r="AJ819" s="14"/>
     </row>
-    <row r="820">
+    <row r="820" hidden="1">
       <c r="A820" s="14"/>
       <c r="B820" s="14"/>
       <c r="C820" s="14"/>
@@ -36012,7 +36012,7 @@
       <c r="AI820" s="14"/>
       <c r="AJ820" s="14"/>
     </row>
-    <row r="821">
+    <row r="821" hidden="1">
       <c r="A821" s="14"/>
       <c r="B821" s="14"/>
       <c r="C821" s="14"/>
@@ -36050,7 +36050,7 @@
       <c r="AI821" s="14"/>
       <c r="AJ821" s="14"/>
     </row>
-    <row r="822">
+    <row r="822" hidden="1">
       <c r="A822" s="14"/>
       <c r="B822" s="14"/>
       <c r="C822" s="14"/>
@@ -36088,7 +36088,7 @@
       <c r="AI822" s="14"/>
       <c r="AJ822" s="14"/>
     </row>
-    <row r="823">
+    <row r="823" hidden="1">
       <c r="A823" s="14"/>
       <c r="B823" s="14"/>
       <c r="C823" s="14"/>
@@ -36126,7 +36126,7 @@
       <c r="AI823" s="14"/>
       <c r="AJ823" s="14"/>
     </row>
-    <row r="824">
+    <row r="824" hidden="1">
       <c r="A824" s="14"/>
       <c r="B824" s="14"/>
       <c r="C824" s="14"/>
@@ -36164,7 +36164,7 @@
       <c r="AI824" s="14"/>
       <c r="AJ824" s="14"/>
     </row>
-    <row r="825">
+    <row r="825" hidden="1">
       <c r="A825" s="14"/>
       <c r="B825" s="14"/>
       <c r="C825" s="14"/>
@@ -36202,7 +36202,7 @@
       <c r="AI825" s="14"/>
       <c r="AJ825" s="14"/>
     </row>
-    <row r="826">
+    <row r="826" hidden="1">
       <c r="A826" s="14"/>
       <c r="B826" s="14"/>
       <c r="C826" s="14"/>
@@ -36240,7 +36240,7 @@
       <c r="AI826" s="14"/>
       <c r="AJ826" s="14"/>
     </row>
-    <row r="827">
+    <row r="827" hidden="1">
       <c r="A827" s="14"/>
       <c r="B827" s="14"/>
       <c r="C827" s="14"/>
@@ -36278,7 +36278,7 @@
       <c r="AI827" s="14"/>
       <c r="AJ827" s="14"/>
     </row>
-    <row r="828">
+    <row r="828" hidden="1">
       <c r="A828" s="14"/>
       <c r="B828" s="14"/>
       <c r="C828" s="14"/>
@@ -36316,7 +36316,7 @@
       <c r="AI828" s="14"/>
       <c r="AJ828" s="14"/>
     </row>
-    <row r="829">
+    <row r="829" hidden="1">
       <c r="A829" s="14"/>
       <c r="B829" s="14"/>
       <c r="C829" s="14"/>
@@ -36354,7 +36354,7 @@
       <c r="AI829" s="14"/>
       <c r="AJ829" s="14"/>
     </row>
-    <row r="830">
+    <row r="830" hidden="1">
       <c r="A830" s="14"/>
       <c r="B830" s="14"/>
       <c r="C830" s="14"/>
@@ -36392,7 +36392,7 @@
       <c r="AI830" s="14"/>
       <c r="AJ830" s="14"/>
     </row>
-    <row r="831">
+    <row r="831" hidden="1">
       <c r="A831" s="14"/>
       <c r="B831" s="14"/>
       <c r="C831" s="14"/>
@@ -36430,7 +36430,7 @@
       <c r="AI831" s="14"/>
       <c r="AJ831" s="14"/>
     </row>
-    <row r="832">
+    <row r="832" hidden="1">
       <c r="A832" s="14"/>
       <c r="B832" s="14"/>
       <c r="C832" s="14"/>
@@ -36468,7 +36468,7 @@
       <c r="AI832" s="14"/>
       <c r="AJ832" s="14"/>
     </row>
-    <row r="833">
+    <row r="833" hidden="1">
       <c r="A833" s="14"/>
       <c r="B833" s="14"/>
       <c r="C833" s="14"/>
@@ -36506,7 +36506,7 @@
       <c r="AI833" s="14"/>
       <c r="AJ833" s="14"/>
     </row>
-    <row r="834">
+    <row r="834" hidden="1">
       <c r="A834" s="14"/>
       <c r="B834" s="14"/>
       <c r="C834" s="14"/>
@@ -36544,7 +36544,7 @@
       <c r="AI834" s="14"/>
       <c r="AJ834" s="14"/>
     </row>
-    <row r="835">
+    <row r="835" hidden="1">
       <c r="A835" s="14"/>
       <c r="B835" s="14"/>
       <c r="C835" s="14"/>
@@ -36582,7 +36582,7 @@
       <c r="AI835" s="14"/>
       <c r="AJ835" s="14"/>
     </row>
-    <row r="836">
+    <row r="836" hidden="1">
       <c r="A836" s="14"/>
       <c r="B836" s="14"/>
       <c r="C836" s="14"/>
@@ -36620,7 +36620,7 @@
       <c r="AI836" s="14"/>
       <c r="AJ836" s="14"/>
     </row>
-    <row r="837">
+    <row r="837" hidden="1">
       <c r="A837" s="14"/>
       <c r="B837" s="14"/>
       <c r="C837" s="14"/>
@@ -36658,7 +36658,7 @@
       <c r="AI837" s="14"/>
       <c r="AJ837" s="14"/>
     </row>
-    <row r="838">
+    <row r="838" hidden="1">
       <c r="A838" s="14"/>
       <c r="B838" s="14"/>
       <c r="C838" s="14"/>
@@ -36696,7 +36696,7 @@
       <c r="AI838" s="14"/>
       <c r="AJ838" s="14"/>
     </row>
-    <row r="839">
+    <row r="839" hidden="1">
       <c r="A839" s="14"/>
       <c r="B839" s="14"/>
       <c r="C839" s="14"/>
@@ -36734,7 +36734,7 @@
       <c r="AI839" s="14"/>
       <c r="AJ839" s="14"/>
     </row>
-    <row r="840">
+    <row r="840" hidden="1">
       <c r="A840" s="14"/>
       <c r="B840" s="14"/>
       <c r="C840" s="14"/>
@@ -36772,7 +36772,7 @@
       <c r="AI840" s="14"/>
       <c r="AJ840" s="14"/>
     </row>
-    <row r="841">
+    <row r="841" hidden="1">
       <c r="A841" s="14"/>
       <c r="B841" s="14"/>
       <c r="C841" s="14"/>
@@ -36810,7 +36810,7 @@
       <c r="AI841" s="14"/>
       <c r="AJ841" s="14"/>
     </row>
-    <row r="842">
+    <row r="842" hidden="1">
       <c r="A842" s="14"/>
       <c r="B842" s="14"/>
       <c r="C842" s="14"/>
@@ -36848,7 +36848,7 @@
       <c r="AI842" s="14"/>
       <c r="AJ842" s="14"/>
     </row>
-    <row r="843">
+    <row r="843" hidden="1">
       <c r="A843" s="14"/>
       <c r="B843" s="14"/>
       <c r="C843" s="14"/>
@@ -36886,7 +36886,7 @@
       <c r="AI843" s="14"/>
       <c r="AJ843" s="14"/>
     </row>
-    <row r="844">
+    <row r="844" hidden="1">
       <c r="A844" s="14"/>
       <c r="B844" s="14"/>
       <c r="C844" s="14"/>
@@ -36924,7 +36924,7 @@
       <c r="AI844" s="14"/>
       <c r="AJ844" s="14"/>
     </row>
-    <row r="845">
+    <row r="845" hidden="1">
       <c r="A845" s="14"/>
       <c r="B845" s="14"/>
       <c r="C845" s="14"/>
@@ -36962,7 +36962,7 @@
       <c r="AI845" s="14"/>
       <c r="AJ845" s="14"/>
     </row>
-    <row r="846">
+    <row r="846" hidden="1">
       <c r="A846" s="14"/>
       <c r="B846" s="14"/>
       <c r="C846" s="14"/>
@@ -37000,7 +37000,7 @@
       <c r="AI846" s="14"/>
       <c r="AJ846" s="14"/>
     </row>
-    <row r="847">
+    <row r="847" hidden="1">
       <c r="A847" s="14"/>
       <c r="B847" s="14"/>
       <c r="C847" s="14"/>
@@ -37038,7 +37038,7 @@
       <c r="AI847" s="14"/>
       <c r="AJ847" s="14"/>
     </row>
-    <row r="848">
+    <row r="848" hidden="1">
       <c r="A848" s="14"/>
       <c r="B848" s="14"/>
       <c r="C848" s="14"/>
@@ -37076,7 +37076,7 @@
       <c r="AI848" s="14"/>
       <c r="AJ848" s="14"/>
     </row>
-    <row r="849">
+    <row r="849" hidden="1">
       <c r="A849" s="14"/>
       <c r="B849" s="14"/>
       <c r="C849" s="14"/>
@@ -37114,7 +37114,7 @@
       <c r="AI849" s="14"/>
       <c r="AJ849" s="14"/>
     </row>
-    <row r="850">
+    <row r="850" hidden="1">
       <c r="A850" s="14"/>
       <c r="B850" s="14"/>
       <c r="C850" s="14"/>
@@ -37152,7 +37152,7 @@
       <c r="AI850" s="14"/>
       <c r="AJ850" s="14"/>
     </row>
-    <row r="851">
+    <row r="851" hidden="1">
       <c r="A851" s="14"/>
       <c r="B851" s="14"/>
       <c r="C851" s="14"/>
@@ -37190,7 +37190,7 @@
       <c r="AI851" s="14"/>
       <c r="AJ851" s="14"/>
     </row>
-    <row r="852">
+    <row r="852" hidden="1">
       <c r="A852" s="14"/>
       <c r="B852" s="14"/>
       <c r="C852" s="14"/>
@@ -37228,7 +37228,7 @@
       <c r="AI852" s="14"/>
       <c r="AJ852" s="14"/>
     </row>
-    <row r="853">
+    <row r="853" hidden="1">
       <c r="A853" s="14"/>
       <c r="B853" s="14"/>
       <c r="C853" s="14"/>
@@ -37266,7 +37266,7 @@
       <c r="AI853" s="14"/>
       <c r="AJ853" s="14"/>
     </row>
-    <row r="854">
+    <row r="854" hidden="1">
       <c r="A854" s="14"/>
       <c r="B854" s="14"/>
       <c r="C854" s="14"/>
@@ -37304,7 +37304,7 @@
       <c r="AI854" s="14"/>
       <c r="AJ854" s="14"/>
     </row>
-    <row r="855">
+    <row r="855" hidden="1">
       <c r="A855" s="14"/>
       <c r="B855" s="14"/>
       <c r="C855" s="14"/>
@@ -37342,7 +37342,7 @@
       <c r="AI855" s="14"/>
       <c r="AJ855" s="14"/>
     </row>
-    <row r="856">
+    <row r="856" hidden="1">
       <c r="A856" s="14"/>
       <c r="B856" s="14"/>
       <c r="C856" s="14"/>
@@ -37380,7 +37380,7 @@
       <c r="AI856" s="14"/>
       <c r="AJ856" s="14"/>
     </row>
-    <row r="857">
+    <row r="857" hidden="1">
       <c r="A857" s="14"/>
       <c r="B857" s="14"/>
       <c r="C857" s="14"/>
@@ -37418,7 +37418,7 @@
       <c r="AI857" s="14"/>
       <c r="AJ857" s="14"/>
     </row>
-    <row r="858">
+    <row r="858" hidden="1">
       <c r="A858" s="14"/>
       <c r="B858" s="14"/>
       <c r="C858" s="14"/>
@@ -37456,7 +37456,7 @@
       <c r="AI858" s="14"/>
       <c r="AJ858" s="14"/>
     </row>
-    <row r="859">
+    <row r="859" hidden="1">
       <c r="A859" s="14"/>
       <c r="B859" s="14"/>
       <c r="C859" s="14"/>
@@ -37494,7 +37494,7 @@
       <c r="AI859" s="14"/>
       <c r="AJ859" s="14"/>
     </row>
-    <row r="860">
+    <row r="860" hidden="1">
       <c r="A860" s="14"/>
       <c r="B860" s="14"/>
       <c r="C860" s="14"/>
@@ -37532,7 +37532,7 @@
       <c r="AI860" s="14"/>
       <c r="AJ860" s="14"/>
     </row>
-    <row r="861">
+    <row r="861" hidden="1">
       <c r="A861" s="14"/>
       <c r="B861" s="14"/>
       <c r="C861" s="14"/>
@@ -37570,7 +37570,7 @@
       <c r="AI861" s="14"/>
       <c r="AJ861" s="14"/>
     </row>
-    <row r="862">
+    <row r="862" hidden="1">
       <c r="A862" s="14"/>
       <c r="B862" s="14"/>
       <c r="C862" s="14"/>
@@ -37608,7 +37608,7 @@
       <c r="AI862" s="14"/>
       <c r="AJ862" s="14"/>
     </row>
-    <row r="863">
+    <row r="863" hidden="1">
       <c r="A863" s="14"/>
       <c r="B863" s="14"/>
       <c r="C863" s="14"/>
@@ -37646,7 +37646,7 @@
       <c r="AI863" s="14"/>
       <c r="AJ863" s="14"/>
     </row>
-    <row r="864">
+    <row r="864" hidden="1">
       <c r="A864" s="14"/>
       <c r="B864" s="14"/>
       <c r="C864" s="14"/>
@@ -37684,7 +37684,7 @@
       <c r="AI864" s="14"/>
       <c r="AJ864" s="14"/>
     </row>
-    <row r="865">
+    <row r="865" hidden="1">
       <c r="A865" s="14"/>
       <c r="B865" s="14"/>
       <c r="C865" s="14"/>
@@ -37722,7 +37722,7 @@
       <c r="AI865" s="14"/>
       <c r="AJ865" s="14"/>
     </row>
-    <row r="866">
+    <row r="866" hidden="1">
       <c r="A866" s="14"/>
       <c r="B866" s="14"/>
       <c r="C866" s="14"/>
@@ -37760,7 +37760,7 @@
       <c r="AI866" s="14"/>
       <c r="AJ866" s="14"/>
     </row>
-    <row r="867">
+    <row r="867" hidden="1">
       <c r="A867" s="14"/>
       <c r="B867" s="14"/>
       <c r="C867" s="14"/>
@@ -37798,7 +37798,7 @@
       <c r="AI867" s="14"/>
       <c r="AJ867" s="14"/>
     </row>
-    <row r="868">
+    <row r="868" hidden="1">
       <c r="A868" s="14"/>
       <c r="B868" s="14"/>
       <c r="C868" s="14"/>
@@ -37836,7 +37836,7 @@
       <c r="AI868" s="14"/>
       <c r="AJ868" s="14"/>
     </row>
-    <row r="869">
+    <row r="869" hidden="1">
       <c r="A869" s="14"/>
       <c r="B869" s="14"/>
       <c r="C869" s="14"/>
@@ -37874,7 +37874,7 @@
       <c r="AI869" s="14"/>
       <c r="AJ869" s="14"/>
     </row>
-    <row r="870">
+    <row r="870" hidden="1">
       <c r="A870" s="14"/>
       <c r="B870" s="14"/>
       <c r="C870" s="14"/>
@@ -37912,7 +37912,7 @@
       <c r="AI870" s="14"/>
       <c r="AJ870" s="14"/>
     </row>
-    <row r="871">
+    <row r="871" hidden="1">
       <c r="A871" s="14"/>
       <c r="B871" s="14"/>
       <c r="C871" s="14"/>
@@ -37950,7 +37950,7 @@
       <c r="AI871" s="14"/>
       <c r="AJ871" s="14"/>
     </row>
-    <row r="872">
+    <row r="872" hidden="1">
       <c r="A872" s="14"/>
       <c r="B872" s="14"/>
       <c r="C872" s="14"/>
@@ -37988,7 +37988,7 @@
       <c r="AI872" s="14"/>
       <c r="AJ872" s="14"/>
     </row>
-    <row r="873">
+    <row r="873" hidden="1">
       <c r="A873" s="14"/>
       <c r="B873" s="14"/>
       <c r="C873" s="14"/>
@@ -38026,7 +38026,7 @@
       <c r="AI873" s="14"/>
       <c r="AJ873" s="14"/>
     </row>
-    <row r="874">
+    <row r="874" hidden="1">
       <c r="A874" s="14"/>
       <c r="B874" s="14"/>
       <c r="C874" s="14"/>
@@ -38064,7 +38064,7 @@
       <c r="AI874" s="14"/>
       <c r="AJ874" s="14"/>
     </row>
-    <row r="875">
+    <row r="875" hidden="1">
       <c r="A875" s="14"/>
       <c r="B875" s="14"/>
       <c r="C875" s="14"/>
@@ -38102,7 +38102,7 @@
       <c r="AI875" s="14"/>
       <c r="AJ875" s="14"/>
     </row>
-    <row r="876">
+    <row r="876" hidden="1">
       <c r="A876" s="14"/>
       <c r="B876" s="14"/>
       <c r="C876" s="14"/>
@@ -38140,7 +38140,7 @@
       <c r="AI876" s="14"/>
       <c r="AJ876" s="14"/>
     </row>
-    <row r="877">
+    <row r="877" hidden="1">
       <c r="A877" s="14"/>
       <c r="B877" s="14"/>
       <c r="C877" s="14"/>
@@ -38178,7 +38178,7 @@
       <c r="AI877" s="14"/>
       <c r="AJ877" s="14"/>
     </row>
-    <row r="878">
+    <row r="878" hidden="1">
       <c r="A878" s="14"/>
       <c r="B878" s="14"/>
       <c r="C878" s="14"/>
@@ -38216,7 +38216,7 @@
       <c r="AI878" s="14"/>
       <c r="AJ878" s="14"/>
     </row>
-    <row r="879">
+    <row r="879" hidden="1">
       <c r="A879" s="14"/>
       <c r="B879" s="14"/>
       <c r="C879" s="14"/>
@@ -38254,7 +38254,7 @@
       <c r="AI879" s="14"/>
       <c r="AJ879" s="14"/>
     </row>
-    <row r="880">
+    <row r="880" hidden="1">
       <c r="A880" s="14"/>
       <c r="B880" s="14"/>
       <c r="C880" s="14"/>
@@ -38292,7 +38292,7 @@
       <c r="AI880" s="14"/>
       <c r="AJ880" s="14"/>
     </row>
-    <row r="881">
+    <row r="881" hidden="1">
       <c r="A881" s="14"/>
       <c r="B881" s="14"/>
       <c r="C881" s="14"/>
@@ -38330,7 +38330,7 @@
       <c r="AI881" s="14"/>
       <c r="AJ881" s="14"/>
     </row>
-    <row r="882">
+    <row r="882" hidden="1">
       <c r="A882" s="14"/>
       <c r="B882" s="14"/>
       <c r="C882" s="14"/>
@@ -38368,7 +38368,7 @@
       <c r="AI882" s="14"/>
       <c r="AJ882" s="14"/>
     </row>
-    <row r="883">
+    <row r="883" hidden="1">
       <c r="A883" s="14"/>
       <c r="B883" s="14"/>
       <c r="C883" s="14"/>
@@ -38406,7 +38406,7 @@
       <c r="AI883" s="14"/>
       <c r="AJ883" s="14"/>
     </row>
-    <row r="884">
+    <row r="884" hidden="1">
       <c r="A884" s="14"/>
       <c r="B884" s="14"/>
       <c r="C884" s="14"/>
@@ -38444,7 +38444,7 @@
       <c r="AI884" s="14"/>
       <c r="AJ884" s="14"/>
     </row>
-    <row r="885">
+    <row r="885" hidden="1">
       <c r="A885" s="14"/>
       <c r="B885" s="14"/>
       <c r="C885" s="14"/>
@@ -38482,7 +38482,7 @@
       <c r="AI885" s="14"/>
       <c r="AJ885" s="14"/>
     </row>
-    <row r="886">
+    <row r="886" hidden="1">
       <c r="A886" s="14"/>
       <c r="B886" s="14"/>
       <c r="C886" s="14"/>
@@ -38520,7 +38520,7 @@
       <c r="AI886" s="14"/>
       <c r="AJ886" s="14"/>
     </row>
-    <row r="887">
+    <row r="887" hidden="1">
       <c r="A887" s="14"/>
       <c r="B887" s="14"/>
       <c r="C887" s="14"/>
@@ -38558,7 +38558,7 @@
       <c r="AI887" s="14"/>
       <c r="AJ887" s="14"/>
     </row>
-    <row r="888">
+    <row r="888" hidden="1">
       <c r="A888" s="14"/>
       <c r="B888" s="14"/>
       <c r="C888" s="14"/>
@@ -38596,7 +38596,7 @@
       <c r="AI888" s="14"/>
       <c r="AJ888" s="14"/>
     </row>
-    <row r="889">
+    <row r="889" hidden="1">
       <c r="A889" s="14"/>
       <c r="B889" s="14"/>
       <c r="C889" s="14"/>
@@ -38634,7 +38634,7 @@
       <c r="AI889" s="14"/>
       <c r="AJ889" s="14"/>
     </row>
-    <row r="890">
+    <row r="890" hidden="1">
       <c r="A890" s="14"/>
       <c r="B890" s="14"/>
       <c r="C890" s="14"/>
@@ -38672,7 +38672,7 @@
       <c r="AI890" s="14"/>
       <c r="AJ890" s="14"/>
     </row>
-    <row r="891">
+    <row r="891" hidden="1">
       <c r="A891" s="14"/>
       <c r="B891" s="14"/>
       <c r="C891" s="14"/>
@@ -38710,7 +38710,7 @@
       <c r="AI891" s="14"/>
       <c r="AJ891" s="14"/>
     </row>
-    <row r="892">
+    <row r="892" hidden="1">
       <c r="A892" s="14"/>
       <c r="B892" s="14"/>
       <c r="C892" s="14"/>
@@ -38748,7 +38748,7 @@
       <c r="AI892" s="14"/>
       <c r="AJ892" s="14"/>
     </row>
-    <row r="893">
+    <row r="893" hidden="1">
       <c r="A893" s="14"/>
       <c r="B893" s="14"/>
       <c r="C893" s="14"/>
@@ -38786,7 +38786,7 @@
       <c r="AI893" s="14"/>
       <c r="AJ893" s="14"/>
     </row>
-    <row r="894">
+    <row r="894" hidden="1">
       <c r="A894" s="14"/>
       <c r="B894" s="14"/>
       <c r="C894" s="14"/>
@@ -38824,7 +38824,7 @@
       <c r="AI894" s="14"/>
       <c r="AJ894" s="14"/>
     </row>
-    <row r="895">
+    <row r="895" hidden="1">
       <c r="A895" s="14"/>
       <c r="B895" s="14"/>
       <c r="C895" s="14"/>
@@ -38862,7 +38862,7 @@
       <c r="AI895" s="14"/>
       <c r="AJ895" s="14"/>
     </row>
-    <row r="896">
+    <row r="896" hidden="1">
       <c r="A896" s="14"/>
       <c r="B896" s="14"/>
       <c r="C896" s="14"/>
@@ -38900,7 +38900,7 @@
       <c r="AI896" s="14"/>
       <c r="AJ896" s="14"/>
     </row>
-    <row r="897">
+    <row r="897" hidden="1">
       <c r="A897" s="14"/>
       <c r="B897" s="14"/>
       <c r="C897" s="14"/>
@@ -38938,7 +38938,7 @@
       <c r="AI897" s="14"/>
       <c r="AJ897" s="14"/>
     </row>
-    <row r="898">
+    <row r="898" hidden="1">
       <c r="A898" s="14"/>
       <c r="B898" s="14"/>
       <c r="C898" s="14"/>
@@ -38976,7 +38976,7 @@
       <c r="AI898" s="14"/>
       <c r="AJ898" s="14"/>
     </row>
-    <row r="899">
+    <row r="899" hidden="1">
       <c r="A899" s="14"/>
       <c r="B899" s="14"/>
       <c r="C899" s="14"/>
@@ -39014,7 +39014,7 @@
       <c r="AI899" s="14"/>
       <c r="AJ899" s="14"/>
     </row>
-    <row r="900">
+    <row r="900" hidden="1">
       <c r="A900" s="14"/>
       <c r="B900" s="14"/>
       <c r="C900" s="14"/>
@@ -39052,7 +39052,7 @@
       <c r="AI900" s="14"/>
       <c r="AJ900" s="14"/>
     </row>
-    <row r="901">
+    <row r="901" hidden="1">
       <c r="A901" s="14"/>
       <c r="B901" s="14"/>
       <c r="C901" s="14"/>
@@ -39090,7 +39090,7 @@
       <c r="AI901" s="14"/>
       <c r="AJ901" s="14"/>
     </row>
-    <row r="902">
+    <row r="902" hidden="1">
       <c r="A902" s="14"/>
       <c r="B902" s="14"/>
       <c r="C902" s="14"/>
@@ -39128,7 +39128,7 @@
       <c r="AI902" s="14"/>
       <c r="AJ902" s="14"/>
     </row>
-    <row r="903">
+    <row r="903" hidden="1">
       <c r="A903" s="14"/>
       <c r="B903" s="14"/>
       <c r="C903" s="14"/>
@@ -39166,7 +39166,7 @@
       <c r="AI903" s="14"/>
       <c r="AJ903" s="14"/>
     </row>
-    <row r="904">
+    <row r="904" hidden="1">
       <c r="A904" s="14"/>
       <c r="B904" s="14"/>
       <c r="C904" s="14"/>
@@ -39204,7 +39204,7 @@
       <c r="AI904" s="14"/>
       <c r="AJ904" s="14"/>
     </row>
-    <row r="905">
+    <row r="905" hidden="1">
       <c r="A905" s="14"/>
       <c r="B905" s="14"/>
       <c r="C905" s="14"/>
@@ -39242,7 +39242,7 @@
       <c r="AI905" s="14"/>
       <c r="AJ905" s="14"/>
     </row>
-    <row r="906">
+    <row r="906" hidden="1">
       <c r="A906" s="14"/>
       <c r="B906" s="14"/>
       <c r="C906" s="14"/>
@@ -39280,7 +39280,7 @@
       <c r="AI906" s="14"/>
       <c r="AJ906" s="14"/>
     </row>
-    <row r="907">
+    <row r="907" hidden="1">
       <c r="A907" s="14"/>
       <c r="B907" s="14"/>
       <c r="C907" s="14"/>
@@ -39318,7 +39318,7 @@
       <c r="AI907" s="14"/>
       <c r="AJ907" s="14"/>
     </row>
-    <row r="908">
+    <row r="908" hidden="1">
       <c r="A908" s="14"/>
       <c r="B908" s="14"/>
       <c r="C908" s="14"/>
@@ -39356,7 +39356,7 @@
       <c r="AI908" s="14"/>
       <c r="AJ908" s="14"/>
     </row>
-    <row r="909">
+    <row r="909" hidden="1">
       <c r="A909" s="14"/>
       <c r="B909" s="14"/>
       <c r="C909" s="14"/>
@@ -39394,7 +39394,7 @@
       <c r="AI909" s="14"/>
       <c r="AJ909" s="14"/>
     </row>
-    <row r="910">
+    <row r="910" hidden="1">
       <c r="A910" s="14"/>
       <c r="B910" s="14"/>
       <c r="C910" s="14"/>
@@ -39432,7 +39432,7 @@
       <c r="AI910" s="14"/>
       <c r="AJ910" s="14"/>
     </row>
-    <row r="911">
+    <row r="911" hidden="1">
       <c r="A911" s="14"/>
       <c r="B911" s="14"/>
       <c r="C911" s="14"/>
@@ -39470,7 +39470,7 @@
       <c r="AI911" s="14"/>
       <c r="AJ911" s="14"/>
     </row>
-    <row r="912">
+    <row r="912" hidden="1">
       <c r="A912" s="14"/>
       <c r="B912" s="14"/>
       <c r="C912" s="14"/>
@@ -39508,7 +39508,7 @@
       <c r="AI912" s="14"/>
       <c r="AJ912" s="14"/>
     </row>
-    <row r="913">
+    <row r="913" hidden="1">
       <c r="A913" s="14"/>
       <c r="B913" s="14"/>
       <c r="C913" s="14"/>
@@ -39546,7 +39546,7 @@
       <c r="AI913" s="14"/>
       <c r="AJ913" s="14"/>
     </row>
-    <row r="914">
+    <row r="914" hidden="1">
       <c r="A914" s="14"/>
       <c r="B914" s="14"/>
       <c r="C914" s="14"/>
@@ -39584,7 +39584,7 @@
       <c r="AI914" s="14"/>
       <c r="AJ914" s="14"/>
     </row>
-    <row r="915">
+    <row r="915" hidden="1">
       <c r="A915" s="14"/>
       <c r="B915" s="14"/>
       <c r="C915" s="14"/>
@@ -39622,7 +39622,7 @@
       <c r="AI915" s="14"/>
       <c r="AJ915" s="14"/>
     </row>
-    <row r="916">
+    <row r="916" hidden="1">
       <c r="A916" s="14"/>
       <c r="B916" s="14"/>
       <c r="C916" s="14"/>
@@ -39660,7 +39660,7 @@
       <c r="AI916" s="14"/>
       <c r="AJ916" s="14"/>
     </row>
-    <row r="917">
+    <row r="917" hidden="1">
       <c r="A917" s="14"/>
       <c r="B917" s="14"/>
       <c r="C917" s="14"/>
@@ -39698,7 +39698,7 @@
       <c r="AI917" s="14"/>
       <c r="AJ917" s="14"/>
     </row>
-    <row r="918">
+    <row r="918" hidden="1">
       <c r="A918" s="14"/>
       <c r="B918" s="14"/>
       <c r="C918" s="14"/>
@@ -39736,7 +39736,7 @@
       <c r="AI918" s="14"/>
       <c r="AJ918" s="14"/>
     </row>
-    <row r="919">
+    <row r="919" hidden="1">
       <c r="A919" s="14"/>
       <c r="B919" s="14"/>
       <c r="C919" s="14"/>
@@ -39774,7 +39774,7 @@
       <c r="AI919" s="14"/>
       <c r="AJ919" s="14"/>
     </row>
-    <row r="920">
+    <row r="920" hidden="1">
       <c r="A920" s="14"/>
       <c r="B920" s="14"/>
       <c r="C920" s="14"/>
@@ -39812,7 +39812,7 @@
       <c r="AI920" s="14"/>
       <c r="AJ920" s="14"/>
     </row>
-    <row r="921">
+    <row r="921" hidden="1">
       <c r="A921" s="14"/>
       <c r="B921" s="14"/>
       <c r="C921" s="14"/>
@@ -39850,7 +39850,7 @@
       <c r="AI921" s="14"/>
       <c r="AJ921" s="14"/>
     </row>
-    <row r="922">
+    <row r="922" hidden="1">
       <c r="A922" s="14"/>
       <c r="B922" s="14"/>
       <c r="C922" s="14"/>
@@ -39888,7 +39888,7 @@
       <c r="AI922" s="14"/>
       <c r="AJ922" s="14"/>
     </row>
-    <row r="923">
+    <row r="923" hidden="1">
       <c r="A923" s="14"/>
       <c r="B923" s="14"/>
       <c r="C923" s="14"/>
@@ -39926,7 +39926,7 @@
       <c r="AI923" s="14"/>
       <c r="AJ923" s="14"/>
     </row>
-    <row r="924">
+    <row r="924" hidden="1">
       <c r="A924" s="14"/>
       <c r="B924" s="14"/>
       <c r="C924" s="14"/>
@@ -39964,7 +39964,7 @@
       <c r="AI924" s="14"/>
       <c r="AJ924" s="14"/>
     </row>
-    <row r="925">
+    <row r="925" hidden="1">
       <c r="A925" s="14"/>
       <c r="B925" s="14"/>
       <c r="C925" s="14"/>
@@ -40002,7 +40002,7 @@
       <c r="AI925" s="14"/>
       <c r="AJ925" s="14"/>
     </row>
-    <row r="926">
+    <row r="926" hidden="1">
       <c r="A926" s="14"/>
       <c r="B926" s="14"/>
       <c r="C926" s="14"/>
@@ -40040,7 +40040,7 @@
       <c r="AI926" s="14"/>
       <c r="AJ926" s="14"/>
     </row>
-    <row r="927">
+    <row r="927" hidden="1">
       <c r="A927" s="14"/>
       <c r="B927" s="14"/>
       <c r="C927" s="14"/>
@@ -40078,7 +40078,7 @@
       <c r="AI927" s="14"/>
       <c r="AJ927" s="14"/>
     </row>
-    <row r="928">
+    <row r="928" hidden="1">
       <c r="A928" s="14"/>
       <c r="B928" s="14"/>
       <c r="C928" s="14"/>
@@ -40116,7 +40116,7 @@
       <c r="AI928" s="14"/>
       <c r="AJ928" s="14"/>
     </row>
-    <row r="929">
+    <row r="929" hidden="1">
       <c r="A929" s="14"/>
       <c r="B929" s="14"/>
       <c r="C929" s="14"/>
@@ -40154,7 +40154,7 @@
       <c r="AI929" s="14"/>
       <c r="AJ929" s="14"/>
     </row>
-    <row r="930">
+    <row r="930" hidden="1">
       <c r="A930" s="14"/>
       <c r="B930" s="14"/>
       <c r="C930" s="14"/>
@@ -40192,7 +40192,7 @@
       <c r="AI930" s="14"/>
       <c r="AJ930" s="14"/>
     </row>
-    <row r="931">
+    <row r="931" hidden="1">
       <c r="A931" s="14"/>
       <c r="B931" s="14"/>
       <c r="C931" s="14"/>
@@ -40230,7 +40230,7 @@
       <c r="AI931" s="14"/>
       <c r="AJ931" s="14"/>
     </row>
-    <row r="932">
+    <row r="932" hidden="1">
       <c r="A932" s="14"/>
       <c r="B932" s="14"/>
       <c r="C932" s="14"/>
@@ -40268,7 +40268,7 @@
       <c r="AI932" s="14"/>
       <c r="AJ932" s="14"/>
     </row>
-    <row r="933">
+    <row r="933" hidden="1">
       <c r="A933" s="14"/>
       <c r="B933" s="14"/>
       <c r="C933" s="14"/>
@@ -40306,7 +40306,7 @@
       <c r="AI933" s="14"/>
       <c r="AJ933" s="14"/>
     </row>
-    <row r="934">
+    <row r="934" hidden="1">
       <c r="A934" s="14"/>
       <c r="B934" s="14"/>
       <c r="C934" s="14"/>
@@ -40344,7 +40344,7 @@
       <c r="AI934" s="14"/>
       <c r="AJ934" s="14"/>
     </row>
-    <row r="935">
+    <row r="935" hidden="1">
       <c r="A935" s="14"/>
       <c r="B935" s="14"/>
       <c r="C935" s="14"/>
@@ -40382,7 +40382,7 @@
       <c r="AI935" s="14"/>
       <c r="AJ935" s="14"/>
     </row>
-    <row r="936">
+    <row r="936" hidden="1">
       <c r="A936" s="14"/>
       <c r="B936" s="14"/>
       <c r="C936" s="14"/>
@@ -40420,7 +40420,7 @@
       <c r="AI936" s="14"/>
       <c r="AJ936" s="14"/>
     </row>
-    <row r="937">
+    <row r="937" hidden="1">
       <c r="A937" s="14"/>
       <c r="B937" s="14"/>
       <c r="C937" s="14"/>
@@ -40458,7 +40458,7 @@
       <c r="AI937" s="14"/>
       <c r="AJ937" s="14"/>
     </row>
-    <row r="938">
+    <row r="938" hidden="1">
       <c r="A938" s="14"/>
       <c r="B938" s="14"/>
       <c r="C938" s="14"/>
@@ -40496,7 +40496,7 @@
       <c r="AI938" s="14"/>
       <c r="AJ938" s="14"/>
     </row>
-    <row r="939">
+    <row r="939" hidden="1">
       <c r="A939" s="14"/>
       <c r="B939" s="14"/>
       <c r="C939" s="14"/>
@@ -40534,7 +40534,7 @@
       <c r="AI939" s="14"/>
       <c r="AJ939" s="14"/>
     </row>
-    <row r="940">
+    <row r="940" hidden="1">
       <c r="A940" s="14"/>
       <c r="B940" s="14"/>
       <c r="C940" s="14"/>
@@ -40572,7 +40572,7 @@
       <c r="AI940" s="14"/>
       <c r="AJ940" s="14"/>
     </row>
-    <row r="941">
+    <row r="941" hidden="1">
       <c r="A941" s="14"/>
       <c r="B941" s="14"/>
       <c r="C941" s="14"/>
@@ -40610,7 +40610,7 @@
       <c r="AI941" s="14"/>
       <c r="AJ941" s="14"/>
     </row>
-    <row r="942">
+    <row r="942" hidden="1">
       <c r="A942" s="14"/>
       <c r="B942" s="14"/>
       <c r="C942" s="14"/>
@@ -40648,7 +40648,7 @@
       <c r="AI942" s="14"/>
       <c r="AJ942" s="14"/>
     </row>
-    <row r="943">
+    <row r="943" hidden="1">
       <c r="A943" s="14"/>
       <c r="B943" s="14"/>
       <c r="C943" s="14"/>
@@ -40686,7 +40686,7 @@
       <c r="AI943" s="14"/>
       <c r="AJ943" s="14"/>
     </row>
-    <row r="944">
+    <row r="944" hidden="1">
       <c r="A944" s="14"/>
       <c r="B944" s="14"/>
       <c r="C944" s="14"/>
@@ -40724,7 +40724,7 @@
       <c r="AI944" s="14"/>
       <c r="AJ944" s="14"/>
     </row>
-    <row r="945">
+    <row r="945" hidden="1">
       <c r="A945" s="14"/>
       <c r="B945" s="14"/>
       <c r="C945" s="14"/>
@@ -40762,7 +40762,7 @@
       <c r="AI945" s="14"/>
       <c r="AJ945" s="14"/>
     </row>
-    <row r="946">
+    <row r="946" hidden="1">
       <c r="A946" s="14"/>
       <c r="B946" s="14"/>
       <c r="C946" s="14"/>
@@ -40800,7 +40800,7 @@
       <c r="AI946" s="14"/>
       <c r="AJ946" s="14"/>
     </row>
-    <row r="947">
+    <row r="947" hidden="1">
       <c r="A947" s="14"/>
       <c r="B947" s="14"/>
       <c r="C947" s="14"/>
@@ -40838,7 +40838,7 @@
       <c r="AI947" s="14"/>
       <c r="AJ947" s="14"/>
     </row>
-    <row r="948">
+    <row r="948" hidden="1">
       <c r="A948" s="14"/>
       <c r="B948" s="14"/>
       <c r="C948" s="14"/>
@@ -40876,7 +40876,7 @@
       <c r="AI948" s="14"/>
       <c r="AJ948" s="14"/>
     </row>
-    <row r="949">
+    <row r="949" hidden="1">
       <c r="A949" s="14"/>
       <c r="B949" s="14"/>
       <c r="C949" s="14"/>
@@ -40914,7 +40914,7 @@
       <c r="AI949" s="14"/>
       <c r="AJ949" s="14"/>
     </row>
-    <row r="950">
+    <row r="950" hidden="1">
       <c r="A950" s="14"/>
       <c r="B950" s="14"/>
       <c r="C950" s="14"/>
@@ -40952,7 +40952,7 @@
       <c r="AI950" s="14"/>
       <c r="AJ950" s="14"/>
     </row>
-    <row r="951">
+    <row r="951" hidden="1">
       <c r="A951" s="14"/>
       <c r="B951" s="14"/>
       <c r="C951" s="14"/>
@@ -40990,7 +40990,7 @@
       <c r="AI951" s="14"/>
       <c r="AJ951" s="14"/>
     </row>
-    <row r="952">
+    <row r="952" hidden="1">
       <c r="A952" s="14"/>
       <c r="B952" s="14"/>
       <c r="C952" s="14"/>
@@ -41028,7 +41028,7 @@
       <c r="AI952" s="14"/>
       <c r="AJ952" s="14"/>
     </row>
-    <row r="953">
+    <row r="953" hidden="1">
       <c r="A953" s="14"/>
       <c r="B953" s="14"/>
       <c r="C953" s="14"/>
@@ -41066,7 +41066,7 @@
       <c r="AI953" s="14"/>
       <c r="AJ953" s="14"/>
     </row>
-    <row r="954">
+    <row r="954" hidden="1">
       <c r="A954" s="14"/>
       <c r="B954" s="14"/>
       <c r="C954" s="14"/>
@@ -41104,7 +41104,7 @@
       <c r="AI954" s="14"/>
       <c r="AJ954" s="14"/>
     </row>
-    <row r="955">
+    <row r="955" hidden="1">
       <c r="A955" s="14"/>
       <c r="B955" s="14"/>
       <c r="C955" s="14"/>
@@ -41142,7 +41142,7 @@
       <c r="AI955" s="14"/>
       <c r="AJ955" s="14"/>
     </row>
-    <row r="956">
+    <row r="956" hidden="1">
       <c r="A956" s="14"/>
       <c r="B956" s="14"/>
       <c r="C956" s="14"/>
@@ -41180,7 +41180,7 @@
       <c r="AI956" s="14"/>
       <c r="AJ956" s="14"/>
     </row>
-    <row r="957">
+    <row r="957" hidden="1">
       <c r="A957" s="14"/>
       <c r="B957" s="14"/>
       <c r="C957" s="14"/>
@@ -41218,7 +41218,7 @@
       <c r="AI957" s="14"/>
       <c r="AJ957" s="14"/>
     </row>
-    <row r="958">
+    <row r="958" hidden="1">
       <c r="A958" s="14"/>
       <c r="B958" s="14"/>
       <c r="C958" s="14"/>
@@ -41256,7 +41256,7 @@
       <c r="AI958" s="14"/>
       <c r="AJ958" s="14"/>
     </row>
-    <row r="959">
+    <row r="959" hidden="1">
       <c r="A959" s="14"/>
       <c r="B959" s="14"/>
       <c r="C959" s="14"/>
@@ -41294,7 +41294,7 @@
       <c r="AI959" s="14"/>
       <c r="AJ959" s="14"/>
     </row>
-    <row r="960">
+    <row r="960" hidden="1">
       <c r="A960" s="14"/>
       <c r="B960" s="14"/>
       <c r="C960" s="14"/>
@@ -41332,7 +41332,7 @@
       <c r="AI960" s="14"/>
       <c r="AJ960" s="14"/>
     </row>
-    <row r="961">
+    <row r="961" hidden="1">
       <c r="A961" s="14"/>
       <c r="B961" s="14"/>
       <c r="C961" s="14"/>
@@ -41370,7 +41370,7 @@
       <c r="AI961" s="14"/>
       <c r="AJ961" s="14"/>
     </row>
-    <row r="962">
+    <row r="962" hidden="1">
       <c r="A962" s="14"/>
       <c r="B962" s="14"/>
       <c r="C962" s="14"/>
@@ -41408,7 +41408,7 @@
       <c r="AI962" s="14"/>
       <c r="AJ962" s="14"/>
     </row>
-    <row r="963">
+    <row r="963" hidden="1">
       <c r="A963" s="14"/>
       <c r="B963" s="14"/>
       <c r="C963" s="14"/>
@@ -41446,7 +41446,7 @@
       <c r="AI963" s="14"/>
       <c r="AJ963" s="14"/>
     </row>
-    <row r="964">
+    <row r="964" hidden="1">
       <c r="A964" s="14"/>
       <c r="B964" s="14"/>
       <c r="C964" s="14"/>
@@ -41484,7 +41484,7 @@
       <c r="AI964" s="14"/>
       <c r="AJ964" s="14"/>
     </row>
-    <row r="965">
+    <row r="965" hidden="1">
       <c r="A965" s="14"/>
       <c r="B965" s="14"/>
       <c r="C965" s="14"/>
@@ -41522,7 +41522,7 @@
       <c r="AI965" s="14"/>
       <c r="AJ965" s="14"/>
     </row>
-    <row r="966">
+    <row r="966" hidden="1">
       <c r="A966" s="14"/>
       <c r="B966" s="14"/>
       <c r="C966" s="14"/>
@@ -41560,7 +41560,7 @@
       <c r="AI966" s="14"/>
       <c r="AJ966" s="14"/>
     </row>
-    <row r="967">
+    <row r="967" hidden="1">
       <c r="A967" s="14"/>
       <c r="B967" s="14"/>
       <c r="C967" s="14"/>
@@ -41598,7 +41598,7 @@
       <c r="AI967" s="14"/>
       <c r="AJ967" s="14"/>
     </row>
-    <row r="968">
+    <row r="968" hidden="1">
       <c r="A968" s="14"/>
       <c r="B968" s="14"/>
       <c r="C968" s="14"/>
@@ -41636,7 +41636,7 @@
       <c r="AI968" s="14"/>
       <c r="AJ968" s="14"/>
     </row>
-    <row r="969">
+    <row r="969" hidden="1">
       <c r="A969" s="14"/>
       <c r="B969" s="14"/>
       <c r="C969" s="14"/>
@@ -41674,7 +41674,7 @@
       <c r="AI969" s="14"/>
       <c r="AJ969" s="14"/>
     </row>
-    <row r="970">
+    <row r="970" hidden="1">
       <c r="A970" s="14"/>
       <c r="B970" s="14"/>
       <c r="C970" s="14"/>
@@ -41712,7 +41712,7 @@
       <c r="AI970" s="14"/>
       <c r="AJ970" s="14"/>
     </row>
-    <row r="971">
+    <row r="971" hidden="1">
       <c r="A971" s="14"/>
       <c r="B971" s="14"/>
       <c r="C971" s="14"/>
@@ -41750,7 +41750,7 @@
       <c r="AI971" s="14"/>
       <c r="AJ971" s="14"/>
     </row>
-    <row r="972">
+    <row r="972" hidden="1">
       <c r="A972" s="14"/>
       <c r="B972" s="14"/>
       <c r="C972" s="14"/>
@@ -41788,7 +41788,7 @@
       <c r="AI972" s="14"/>
       <c r="AJ972" s="14"/>
     </row>
-    <row r="973">
+    <row r="973" hidden="1">
       <c r="A973" s="14"/>
       <c r="B973" s="14"/>
       <c r="C973" s="14"/>
@@ -41826,7 +41826,7 @@
       <c r="AI973" s="14"/>
       <c r="AJ973" s="14"/>
     </row>
-    <row r="974">
+    <row r="974" hidden="1">
       <c r="A974" s="14"/>
       <c r="B974" s="14"/>
       <c r="C974" s="14"/>
@@ -41864,7 +41864,7 @@
       <c r="AI974" s="14"/>
       <c r="AJ974" s="14"/>
     </row>
-    <row r="975">
+    <row r="975" hidden="1">
       <c r="A975" s="14"/>
       <c r="B975" s="14"/>
       <c r="C975" s="14"/>
@@ -41902,7 +41902,7 @@
       <c r="AI975" s="14"/>
       <c r="AJ975" s="14"/>
     </row>
-    <row r="976">
+    <row r="976" hidden="1">
       <c r="A976" s="14"/>
       <c r="B976" s="14"/>
       <c r="C976" s="14"/>
@@ -41940,7 +41940,7 @@
       <c r="AI976" s="14"/>
       <c r="AJ976" s="14"/>
     </row>
-    <row r="977">
+    <row r="977" hidden="1">
       <c r="A977" s="14"/>
       <c r="B977" s="14"/>
       <c r="C977" s="14"/>
@@ -41978,7 +41978,7 @@
       <c r="AI977" s="14"/>
       <c r="AJ977" s="14"/>
     </row>
-    <row r="978">
+    <row r="978" hidden="1">
       <c r="A978" s="14"/>
       <c r="B978" s="14"/>
       <c r="C978" s="14"/>
@@ -42016,7 +42016,7 @@
       <c r="AI978" s="14"/>
       <c r="AJ978" s="14"/>
     </row>
-    <row r="979">
+    <row r="979" hidden="1">
       <c r="A979" s="14"/>
       <c r="B979" s="14"/>
       <c r="C979" s="14"/>
@@ -42054,7 +42054,7 @@
       <c r="AI979" s="14"/>
       <c r="AJ979" s="14"/>
     </row>
-    <row r="980">
+    <row r="980" hidden="1">
       <c r="A980" s="14"/>
       <c r="B980" s="14"/>
       <c r="C980" s="14"/>
@@ -42092,7 +42092,7 @@
       <c r="AI980" s="14"/>
       <c r="AJ980" s="14"/>
     </row>
-    <row r="981">
+    <row r="981" hidden="1">
       <c r="A981" s="14"/>
       <c r="B981" s="14"/>
       <c r="C981" s="14"/>
@@ -42130,7 +42130,7 @@
       <c r="AI981" s="14"/>
       <c r="AJ981" s="14"/>
     </row>
-    <row r="982">
+    <row r="982" hidden="1">
       <c r="A982" s="14"/>
       <c r="B982" s="14"/>
       <c r="C982" s="14"/>
@@ -42168,7 +42168,7 @@
       <c r="AI982" s="14"/>
       <c r="AJ982" s="14"/>
     </row>
-    <row r="983">
+    <row r="983" hidden="1">
       <c r="A983" s="14"/>
       <c r="B983" s="14"/>
       <c r="C983" s="14"/>
@@ -42206,7 +42206,7 @@
       <c r="AI983" s="14"/>
       <c r="AJ983" s="14"/>
     </row>
-    <row r="984">
+    <row r="984" hidden="1">
       <c r="A984" s="14"/>
       <c r="B984" s="14"/>
       <c r="C984" s="14"/>
@@ -42244,7 +42244,7 @@
       <c r="AI984" s="14"/>
       <c r="AJ984" s="14"/>
     </row>
-    <row r="985">
+    <row r="985" hidden="1">
       <c r="A985" s="14"/>
       <c r="B985" s="14"/>
       <c r="C985" s="14"/>
@@ -42282,7 +42282,7 @@
       <c r="AI985" s="14"/>
       <c r="AJ985" s="14"/>
     </row>
-    <row r="986">
+    <row r="986" hidden="1">
       <c r="A986" s="14"/>
       <c r="B986" s="14"/>
       <c r="C986" s="14"/>
@@ -42320,7 +42320,7 @@
       <c r="AI986" s="14"/>
       <c r="AJ986" s="14"/>
     </row>
-    <row r="987">
+    <row r="987" hidden="1">
       <c r="A987" s="14"/>
       <c r="B987" s="14"/>
       <c r="C987" s="14"/>
@@ -42358,7 +42358,7 @@
       <c r="AI987" s="14"/>
       <c r="AJ987" s="14"/>
     </row>
-    <row r="988">
+    <row r="988" hidden="1">
       <c r="A988" s="14"/>
       <c r="B988" s="14"/>
       <c r="C988" s="14"/>
@@ -42396,7 +42396,7 @@
       <c r="AI988" s="14"/>
       <c r="AJ988" s="14"/>
     </row>
-    <row r="989">
+    <row r="989" hidden="1">
       <c r="A989" s="14"/>
       <c r="B989" s="14"/>
       <c r="C989" s="14"/>
@@ -42434,7 +42434,7 @@
       <c r="AI989" s="14"/>
       <c r="AJ989" s="14"/>
     </row>
-    <row r="990">
+    <row r="990" hidden="1">
       <c r="A990" s="14"/>
       <c r="B990" s="14"/>
       <c r="C990" s="14"/>
@@ -42472,7 +42472,7 @@
       <c r="AI990" s="14"/>
       <c r="AJ990" s="14"/>
     </row>
-    <row r="991">
+    <row r="991" hidden="1">
       <c r="A991" s="14"/>
       <c r="B991" s="14"/>
       <c r="C991" s="14"/>
@@ -42510,7 +42510,7 @@
       <c r="AI991" s="14"/>
       <c r="AJ991" s="14"/>
     </row>
-    <row r="992">
+    <row r="992" hidden="1">
       <c r="A992" s="14"/>
       <c r="B992" s="14"/>
       <c r="C992" s="14"/>
@@ -42548,7 +42548,7 @@
       <c r="AI992" s="14"/>
       <c r="AJ992" s="14"/>
     </row>
-    <row r="993">
+    <row r="993" hidden="1">
       <c r="A993" s="14"/>
       <c r="B993" s="14"/>
       <c r="C993" s="14"/>
@@ -42586,7 +42586,7 @@
       <c r="AI993" s="14"/>
       <c r="AJ993" s="14"/>
     </row>
-    <row r="994">
+    <row r="994" hidden="1">
       <c r="A994" s="14"/>
       <c r="B994" s="14"/>
       <c r="C994" s="14"/>
@@ -42624,7 +42624,7 @@
       <c r="AI994" s="14"/>
       <c r="AJ994" s="14"/>
     </row>
-    <row r="995">
+    <row r="995" hidden="1">
       <c r="A995" s="14"/>
       <c r="B995" s="14"/>
       <c r="C995" s="14"/>
@@ -42662,7 +42662,7 @@
       <c r="AI995" s="14"/>
       <c r="AJ995" s="14"/>
     </row>
-    <row r="996">
+    <row r="996" hidden="1">
       <c r="A996" s="14"/>
       <c r="B996" s="14"/>
       <c r="C996" s="14"/>
@@ -42700,7 +42700,7 @@
       <c r="AI996" s="14"/>
       <c r="AJ996" s="14"/>
     </row>
-    <row r="997">
+    <row r="997" hidden="1">
       <c r="A997" s="14"/>
       <c r="B997" s="14"/>
       <c r="C997" s="14"/>
@@ -42738,7 +42738,7 @@
       <c r="AI997" s="14"/>
       <c r="AJ997" s="14"/>
     </row>
-    <row r="998">
+    <row r="998" hidden="1">
       <c r="A998" s="14"/>
       <c r="B998" s="14"/>
       <c r="C998" s="14"/>
@@ -42776,7 +42776,7 @@
       <c r="AI998" s="14"/>
       <c r="AJ998" s="14"/>
     </row>
-    <row r="999">
+    <row r="999" hidden="1">
       <c r="A999" s="14"/>
       <c r="B999" s="14"/>
       <c r="C999" s="9"/>
@@ -42816,6 +42816,11 @@
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$AJ$999">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="HR vs LR"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A1:AJ999">
       <sortCondition ref="B1:B999"/>
       <sortCondition ref="J1:J999"/>
